--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -558,31 +558,31 @@
     <t>1002</t>
   </si>
   <si>
-    <t>刺杀剑术·系数</t>
+    <t>穿刺剑术·系数</t>
   </si>
   <si>
     <t>10007</t>
   </si>
   <si>
-    <t>刺杀剑术·固伤</t>
+    <t>穿刺剑术·固伤</t>
   </si>
   <si>
     <t>10008</t>
   </si>
   <si>
-    <t>刺杀剑术·暴击</t>
+    <t>穿刺剑术·暴击</t>
   </si>
   <si>
     <t>10009</t>
   </si>
   <si>
-    <t>刺杀剑术·暴伤</t>
+    <t>穿刺剑术·暴伤</t>
   </si>
   <si>
     <t>10010</t>
   </si>
   <si>
-    <t>刺杀剑术·易伤</t>
+    <t>穿刺剑术·易伤</t>
   </si>
   <si>
     <t>10011</t>
@@ -591,31 +591,31 @@
     <t>1003</t>
   </si>
   <si>
-    <t>半月弯刀·系数</t>
+    <t>圆月弯刀·系数</t>
   </si>
   <si>
     <t>10012</t>
   </si>
   <si>
-    <t>半月弯刀·固伤</t>
+    <t>圆月弯刀·固伤</t>
   </si>
   <si>
     <t>10013</t>
   </si>
   <si>
-    <t>半月弯刀·暴击</t>
+    <t>圆月弯刀·暴击</t>
   </si>
   <si>
     <t>10014</t>
   </si>
   <si>
-    <t>半月弯刀·暴伤</t>
+    <t>圆月弯刀·暴伤</t>
   </si>
   <si>
     <t>10015</t>
   </si>
   <si>
-    <t>半月弯刀·易伤</t>
+    <t>圆月弯刀·易伤</t>
   </si>
   <si>
     <t>10016</t>
@@ -624,31 +624,31 @@
     <t>1004</t>
   </si>
   <si>
-    <t>野蛮撞击·系数</t>
+    <t>蛮力撞击·系数</t>
   </si>
   <si>
     <t>10017</t>
   </si>
   <si>
-    <t>野蛮撞击·固伤</t>
+    <t>蛮力撞击·固伤</t>
   </si>
   <si>
     <t>10018</t>
   </si>
   <si>
-    <t>野蛮撞击·暴击</t>
+    <t>蛮力撞击·暴击</t>
   </si>
   <si>
     <t>10019</t>
   </si>
   <si>
-    <t>野蛮撞击·暴伤</t>
+    <t>蛮力撞击·暴伤</t>
   </si>
   <si>
     <t>10020</t>
   </si>
   <si>
-    <t>野蛮撞击·易伤</t>
+    <t>蛮力撞击·易伤</t>
   </si>
   <si>
     <t>10021</t>
@@ -681,31 +681,31 @@
     <t>1007</t>
   </si>
   <si>
-    <t>烈火剑法·系数</t>
+    <t>火焰剑法·系数</t>
   </si>
   <si>
     <t>10024</t>
   </si>
   <si>
-    <t>烈火剑法·固伤</t>
+    <t>火焰剑法·固伤</t>
   </si>
   <si>
     <t>10025</t>
   </si>
   <si>
-    <t>烈火剑法·暴击</t>
+    <t>火焰剑法·暴击</t>
   </si>
   <si>
     <t>10026</t>
   </si>
   <si>
-    <t>烈火剑法·暴伤</t>
+    <t>火焰剑法·暴伤</t>
   </si>
   <si>
     <t>10027</t>
   </si>
   <si>
-    <t>烈火剑法·易伤</t>
+    <t>火焰剑法·易伤</t>
   </si>
   <si>
     <t>10028</t>
@@ -714,31 +714,31 @@
     <t>2001</t>
   </si>
   <si>
-    <t>小火球·系数</t>
+    <t>火球术·系数</t>
   </si>
   <si>
     <t>10029</t>
   </si>
   <si>
-    <t>小火球·固伤</t>
+    <t>火球术·固伤</t>
   </si>
   <si>
     <t>10030</t>
   </si>
   <si>
-    <t>小火球·暴击</t>
+    <t>火球术·暴击</t>
   </si>
   <si>
     <t>10031</t>
   </si>
   <si>
-    <t>小火球·暴伤</t>
+    <t>火球术·暴伤</t>
   </si>
   <si>
     <t>10032</t>
   </si>
   <si>
-    <t>小火球·易伤</t>
+    <t>火球术·易伤</t>
   </si>
   <si>
     <t>10033</t>
@@ -747,31 +747,31 @@
     <t>2002</t>
   </si>
   <si>
-    <t>雷电术·系数</t>
+    <t>神雷术·系数</t>
   </si>
   <si>
     <t>10034</t>
   </si>
   <si>
-    <t>雷电术·固伤</t>
+    <t>神雷术·固伤</t>
   </si>
   <si>
     <t>10035</t>
   </si>
   <si>
-    <t>雷电术·暴击</t>
+    <t>神雷术·暴击</t>
   </si>
   <si>
     <t>10036</t>
   </si>
   <si>
-    <t>雷电术·暴伤</t>
+    <t>神雷术·暴伤</t>
   </si>
   <si>
     <t>10037</t>
   </si>
   <si>
-    <t>雷电术·易伤</t>
+    <t>神雷术·易伤</t>
   </si>
   <si>
     <t>10038</t>
@@ -813,31 +813,31 @@
     <t>2004</t>
   </si>
   <si>
-    <t>爆裂火焰·系数</t>
+    <t>火焰术·系数</t>
   </si>
   <si>
     <t>10044</t>
   </si>
   <si>
-    <t>爆裂火焰·固伤</t>
+    <t>火焰术·固伤</t>
   </si>
   <si>
     <t>10045</t>
   </si>
   <si>
-    <t>爆裂火焰·暴击</t>
+    <t>火焰术·暴击</t>
   </si>
   <si>
     <t>10046</t>
   </si>
   <si>
-    <t>爆裂火焰·暴伤</t>
+    <t>火焰术·暴伤</t>
   </si>
   <si>
     <t>10047</t>
   </si>
   <si>
-    <t>爆裂火焰·易伤</t>
+    <t>火焰术·易伤</t>
   </si>
   <si>
     <t>10048</t>
@@ -864,31 +864,31 @@
     <t>2007</t>
   </si>
   <si>
-    <t>冰咆哮·系数</t>
+    <t>冰冻术·系数</t>
   </si>
   <si>
     <t>10051</t>
   </si>
   <si>
-    <t>冰咆哮·固伤</t>
+    <t>冰冻术·固伤</t>
   </si>
   <si>
     <t>10052</t>
   </si>
   <si>
-    <t>冰咆哮·暴击</t>
+    <t>冰冻术·暴击</t>
   </si>
   <si>
     <t>10053</t>
   </si>
   <si>
-    <t>冰咆哮·暴伤</t>
+    <t>冰冻术·暴伤</t>
   </si>
   <si>
     <t>10054</t>
   </si>
   <si>
-    <t>冰咆哮·易伤</t>
+    <t>冰冻术·易伤</t>
   </si>
   <si>
     <t>10055</t>
@@ -897,7 +897,7 @@
     <t>3001</t>
   </si>
   <si>
-    <t>治疗术·系数</t>
+    <t>治疗道法·系数</t>
   </si>
   <si>
     <t>10056</t>
@@ -906,7 +906,7 @@
     <t>3002</t>
   </si>
   <si>
-    <t>火符术·系数</t>
+    <t>火符道法·系数</t>
   </si>
   <si>
     <t>10057</t>
@@ -915,31 +915,31 @@
     <t>3003</t>
   </si>
   <si>
-    <t>施毒术·系数</t>
+    <t>毒咒道法·系数</t>
   </si>
   <si>
     <t>10058</t>
   </si>
   <si>
-    <t>施毒术·固伤</t>
+    <t>毒咒道法·固伤</t>
   </si>
   <si>
     <t>10059</t>
   </si>
   <si>
-    <t>施毒术·暴击</t>
+    <t>毒咒道法·暴击</t>
   </si>
   <si>
     <t>10060</t>
   </si>
   <si>
-    <t>施毒术·暴伤</t>
+    <t>毒咒道法·暴伤</t>
   </si>
   <si>
     <t>10061</t>
   </si>
   <si>
-    <t>施毒术·易伤</t>
+    <t>毒咒道法·易伤</t>
   </si>
   <si>
     <t>10062</t>
@@ -948,7 +948,7 @@
     <t>3004</t>
   </si>
   <si>
-    <t>召唤骷髅·系数</t>
+    <t>召唤金刚·系数</t>
   </si>
   <si>
     <t>10063</t>
@@ -975,7 +975,7 @@
     <t>3007</t>
   </si>
   <si>
-    <t>召唤神兽·系数</t>
+    <t>召唤魔兽·系数</t>
   </si>
   <si>
     <t>10066</t>
@@ -1008,19 +1008,19 @@
     <t>10070</t>
   </si>
   <si>
-    <t>治疗术·固伤</t>
+    <t>治疗道法·固伤</t>
   </si>
   <si>
     <t>10071</t>
   </si>
   <si>
-    <t>火符术·固伤</t>
+    <t>火符道法·固伤</t>
   </si>
   <si>
     <t>10072</t>
   </si>
   <si>
-    <t>召唤骷髅·固伤</t>
+    <t>召唤金刚·固伤</t>
   </si>
   <si>
     <t>10073</t>
@@ -1038,7 +1038,7 @@
     <t>10075</t>
   </si>
   <si>
-    <t>召唤神兽·固伤</t>
+    <t>召唤魔兽·固伤</t>
   </si>
   <si>
     <t>火墙·大大大</t>
@@ -1053,52 +1053,52 @@
     <t>此词条废弃了</t>
   </si>
   <si>
-    <t>爆裂火焰·大大大</t>
-  </si>
-  <si>
-    <t>爆裂火焰·废弃</t>
-  </si>
-  <si>
-    <t>冰咆哮·大大大</t>
-  </si>
-  <si>
-    <t>冰咆哮·废弃</t>
-  </si>
-  <si>
-    <t>小火球·多重</t>
+    <t>火焰术·大大大</t>
+  </si>
+  <si>
+    <t>火焰术·废弃</t>
+  </si>
+  <si>
+    <t>冰冻术·大大大</t>
+  </si>
+  <si>
+    <t>冰冻术·废弃</t>
+  </si>
+  <si>
+    <t>火球术·多重</t>
   </si>
   <si>
     <t>增加一个攻击目标</t>
   </si>
   <si>
-    <t>雷电术·多重</t>
-  </si>
-  <si>
-    <t>刺杀·远攻</t>
+    <t>神雷术·多重</t>
+  </si>
+  <si>
+    <t>穿刺·远攻</t>
   </si>
   <si>
     <t>增加一格攻击范围</t>
   </si>
   <si>
-    <t>召唤骷髅·复制</t>
+    <t>召唤金刚·复制</t>
   </si>
   <si>
     <t>多召唤一个骷髅</t>
   </si>
   <si>
-    <t>召唤神兽·复制</t>
+    <t>召唤魔兽·复制</t>
   </si>
   <si>
     <t>多召唤一只神兽</t>
   </si>
   <si>
-    <t>雷电术·鹰眼</t>
+    <t>神雷术·鹰眼</t>
   </si>
   <si>
     <t>增加一格攻击距离</t>
   </si>
   <si>
-    <t>小火球·鹰眼</t>
+    <t>火球术·鹰眼</t>
   </si>
   <si>
     <t>武力盾·持久</t>
@@ -1113,19 +1113,19 @@
     <t>道力盾·持久</t>
   </si>
   <si>
-    <t>召唤神兽·继承</t>
+    <t>召唤魔兽·继承</t>
   </si>
   <si>
     <t>召唤物增加5%高级属性继承</t>
   </si>
   <si>
-    <t>冰咆哮·霜寒</t>
+    <t>冰冻术·霜寒</t>
   </si>
   <si>
     <t>增加20%最终技能伤害</t>
   </si>
   <si>
-    <t>烈火剑法·噬骨</t>
+    <t>火焰剑法·噬骨</t>
   </si>
   <si>
     <t>增加点燃系数10%</t>
@@ -1140,13 +1140,13 @@
     <t>物理伤害系数增加10%</t>
   </si>
   <si>
-    <t>瞬息移动·法力</t>
+    <t>闪烁术·法力</t>
   </si>
   <si>
     <t>法术伤害系数增加10%</t>
   </si>
   <si>
-    <t>隐身术·御兽</t>
+    <t>隐身道法·御兽</t>
   </si>
   <si>
     <t>宠物攻击系数增加10%</t>
@@ -1158,19 +1158,19 @@
     <t>火符·暴伤</t>
   </si>
   <si>
-    <t>开天斩·急速</t>
+    <t>开天辟地·急速</t>
   </si>
   <si>
     <t>CD时间-3s</t>
   </si>
   <si>
-    <t>流星火雨·大大大</t>
+    <t>火雨术·大大大</t>
   </si>
   <si>
     <t>攻击范围行列+1</t>
   </si>
   <si>
-    <t>召唤月灵·系数</t>
+    <t>召唤护法·系数</t>
   </si>
   <si>
     <t>技能系数增加50%</t>
@@ -1197,13 +1197,13 @@
     <t>提高此技能系数10%倍率</t>
   </si>
   <si>
-    <t>刺杀剑术·精通</t>
-  </si>
-  <si>
-    <t>半月弯刀·精通</t>
-  </si>
-  <si>
-    <t>野蛮撞击·精通</t>
+    <t>穿刺剑术·精通</t>
+  </si>
+  <si>
+    <t>圆月弯刀·精通</t>
+  </si>
+  <si>
+    <t>蛮力撞击·精通</t>
   </si>
   <si>
     <t>武力盾·精通</t>
@@ -1212,16 +1212,16 @@
     <t>武力精通·精通</t>
   </si>
   <si>
-    <t>烈火剑法·精通</t>
+    <t>火焰剑法·精通</t>
   </si>
   <si>
     <t>护体神盾·精通</t>
   </si>
   <si>
-    <t>开天斩·精通</t>
-  </si>
-  <si>
-    <t>彻地钉·精通</t>
+    <t>开天辟地·精通</t>
+  </si>
+  <si>
+    <t>地刺术·精通</t>
   </si>
   <si>
     <t>#</t>
@@ -1230,16 +1230,16 @@
     <t>战士之魂·精通</t>
   </si>
   <si>
-    <t>小火球·精通</t>
-  </si>
-  <si>
-    <t>雷电术·精通</t>
+    <t>火球术·精通</t>
+  </si>
+  <si>
+    <t>神雷术·精通</t>
   </si>
   <si>
     <t>火墙·精通</t>
   </si>
   <si>
-    <t>爆裂火焰·精通</t>
+    <t>火焰术·精通</t>
   </si>
   <si>
     <t>魔法盾·精通</t>
@@ -1248,13 +1248,13 @@
     <t>法术精通·精通</t>
   </si>
   <si>
-    <t>冰咆哮·精通</t>
-  </si>
-  <si>
-    <t>瞬息移动·精通</t>
-  </si>
-  <si>
-    <t>流星火雨·精通</t>
+    <t>冰冻术·精通</t>
+  </si>
+  <si>
+    <t>闪烁术·精通</t>
+  </si>
+  <si>
+    <t>火雨术·精通</t>
   </si>
   <si>
     <t>分身术·精通</t>
@@ -1263,16 +1263,16 @@
     <t>法师之魂·精通</t>
   </si>
   <si>
-    <t>治疗术·精通</t>
-  </si>
-  <si>
-    <t>火符术·精通</t>
-  </si>
-  <si>
-    <t>施毒术·精通</t>
-  </si>
-  <si>
-    <t>召唤骷髅·精通</t>
+    <t>治疗道法·精通</t>
+  </si>
+  <si>
+    <t>火符道法·精通</t>
+  </si>
+  <si>
+    <t>毒咒道法·精通</t>
+  </si>
+  <si>
+    <t>召唤金刚·精通</t>
   </si>
   <si>
     <t>道力盾·精通</t>
@@ -1281,13 +1281,13 @@
     <t>道力精通·精通</t>
   </si>
   <si>
-    <t>召唤神兽·精通</t>
-  </si>
-  <si>
-    <t>隐身术·精通</t>
-  </si>
-  <si>
-    <t>召唤月灵·精通</t>
+    <t>召唤魔兽·精通</t>
+  </si>
+  <si>
+    <t>隐身道法·精通</t>
+  </si>
+  <si>
+    <t>召唤护法·精通</t>
   </si>
   <si>
     <t>无极道体·精通</t>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -948,7 +948,7 @@
     <t>3004</t>
   </si>
   <si>
-    <t>召唤金刚·系数</t>
+    <t>召唤小兵·系数</t>
   </si>
   <si>
     <t>10063</t>
@@ -1020,7 +1020,7 @@
     <t>10072</t>
   </si>
   <si>
-    <t>召唤金刚·固伤</t>
+    <t>召唤小兵·固伤</t>
   </si>
   <si>
     <t>10073</t>
@@ -1080,7 +1080,7 @@
     <t>增加一格攻击范围</t>
   </si>
   <si>
-    <t>召唤金刚·复制</t>
+    <t>召唤小兵·复制</t>
   </si>
   <si>
     <t>多召唤一个骷髅</t>
@@ -1170,7 +1170,7 @@
     <t>攻击范围行列+1</t>
   </si>
   <si>
-    <t>召唤护法·系数</t>
+    <t>召唤月神·系数</t>
   </si>
   <si>
     <t>技能系数增加50%</t>
@@ -1272,7 +1272,7 @@
     <t>毒咒道法·精通</t>
   </si>
   <si>
-    <t>召唤金刚·精通</t>
+    <t>召唤小兵·精通</t>
   </si>
   <si>
     <t>道力盾·精通</t>
@@ -1287,7 +1287,7 @@
     <t>隐身道法·精通</t>
   </si>
   <si>
-    <t>召唤护法·精通</t>
+    <t>召唤月神·精通</t>
   </si>
   <si>
     <t>无极道体·精通</t>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -846,7 +846,7 @@
     <t>2005</t>
   </si>
   <si>
-    <t>魔法盾·系数</t>
+    <t>法力盾·系数</t>
   </si>
   <si>
     <t>10049</t>
@@ -1107,7 +1107,7 @@
     <t>增加10s持续时间</t>
   </si>
   <si>
-    <t>魔法盾·持久</t>
+    <t>法力盾·持久</t>
   </si>
   <si>
     <t>道力盾·持久</t>
@@ -1140,7 +1140,7 @@
     <t>物理伤害系数增加10%</t>
   </si>
   <si>
-    <t>闪烁术·法力</t>
+    <t>瞬移术·法力</t>
   </si>
   <si>
     <t>法术伤害系数增加10%</t>
@@ -1242,13 +1242,13 @@
     <t>火焰术·精通</t>
   </si>
   <si>
-    <t>魔法盾·精通</t>
+    <t>法力盾·精通</t>
   </si>
   <si>
     <t>法术精通·精通</t>
   </si>
   <si>
-    <t>冰冻术·精通</t>
+    <t>瞬移术·精通</t>
   </si>
   <si>
     <t>闪烁术·精通</t>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -558,31 +558,31 @@
     <t>1002</t>
   </si>
   <si>
-    <t>穿刺剑术·系数</t>
+    <t>流光剑法·系数</t>
   </si>
   <si>
     <t>10007</t>
   </si>
   <si>
-    <t>穿刺剑术·固伤</t>
+    <t>流光剑法·固伤</t>
   </si>
   <si>
     <t>10008</t>
   </si>
   <si>
-    <t>穿刺剑术·暴击</t>
+    <t>流光剑法·暴击</t>
   </si>
   <si>
     <t>10009</t>
   </si>
   <si>
-    <t>穿刺剑术·暴伤</t>
+    <t>流光剑法·暴伤</t>
   </si>
   <si>
     <t>10010</t>
   </si>
   <si>
-    <t>穿刺剑术·易伤</t>
+    <t>流光剑法·易伤</t>
   </si>
   <si>
     <t>10011</t>
@@ -591,31 +591,31 @@
     <t>1003</t>
   </si>
   <si>
-    <t>圆月弯刀·系数</t>
+    <t>旋风斩·系数</t>
   </si>
   <si>
     <t>10012</t>
   </si>
   <si>
-    <t>圆月弯刀·固伤</t>
+    <t>旋风斩·固伤</t>
   </si>
   <si>
     <t>10013</t>
   </si>
   <si>
-    <t>圆月弯刀·暴击</t>
+    <t>旋风斩·暴击</t>
   </si>
   <si>
     <t>10014</t>
   </si>
   <si>
-    <t>圆月弯刀·暴伤</t>
+    <t>旋风斩·暴伤</t>
   </si>
   <si>
     <t>10015</t>
   </si>
   <si>
-    <t>圆月弯刀·易伤</t>
+    <t>旋风斩·易伤</t>
   </si>
   <si>
     <t>10016</t>
@@ -657,7 +657,7 @@
     <t>1005</t>
   </si>
   <si>
-    <t>武力盾·系数</t>
+    <t>武神盾·系数</t>
   </si>
   <si>
     <t>增加10%技能系数</t>
@@ -681,31 +681,31 @@
     <t>1007</t>
   </si>
   <si>
-    <t>火焰剑法·系数</t>
+    <t>烈焰斩·系数</t>
   </si>
   <si>
     <t>10024</t>
   </si>
   <si>
-    <t>火焰剑法·固伤</t>
+    <t>烈焰斩·固伤</t>
   </si>
   <si>
     <t>10025</t>
   </si>
   <si>
-    <t>火焰剑法·暴击</t>
+    <t>烈焰斩·暴击</t>
   </si>
   <si>
     <t>10026</t>
   </si>
   <si>
-    <t>火焰剑法·暴伤</t>
+    <t>烈焰斩·暴伤</t>
   </si>
   <si>
     <t>10027</t>
   </si>
   <si>
-    <t>火焰剑法·易伤</t>
+    <t>烈焰斩·易伤</t>
   </si>
   <si>
     <t>10028</t>
@@ -747,31 +747,31 @@
     <t>2002</t>
   </si>
   <si>
-    <t>神雷术·系数</t>
+    <t>落雷术·系数</t>
   </si>
   <si>
     <t>10034</t>
   </si>
   <si>
-    <t>神雷术·固伤</t>
+    <t>落雷术·固伤</t>
   </si>
   <si>
     <t>10035</t>
   </si>
   <si>
-    <t>神雷术·暴击</t>
+    <t>落雷术·暴击</t>
   </si>
   <si>
     <t>10036</t>
   </si>
   <si>
-    <t>神雷术·暴伤</t>
+    <t>落雷术·暴伤</t>
   </si>
   <si>
     <t>10037</t>
   </si>
   <si>
-    <t>神雷术·易伤</t>
+    <t>落雷术·易伤</t>
   </si>
   <si>
     <t>10038</t>
@@ -780,31 +780,31 @@
     <t>2003</t>
   </si>
   <si>
-    <t>火墙·系数</t>
+    <t>火焰墙·系数</t>
   </si>
   <si>
     <t>10039</t>
   </si>
   <si>
-    <t>火墙·固伤</t>
+    <t>火焰墙·固伤</t>
   </si>
   <si>
     <t>10040</t>
   </si>
   <si>
-    <t>火墙·暴击</t>
+    <t>火焰墙·暴击</t>
   </si>
   <si>
     <t>10041</t>
   </si>
   <si>
-    <t>火墙·暴伤</t>
+    <t>火焰墙·暴伤</t>
   </si>
   <si>
     <t>10042</t>
   </si>
   <si>
-    <t>火墙·易伤</t>
+    <t>火焰墙·易伤</t>
   </si>
   <si>
     <t>10043</t>
@@ -813,31 +813,31 @@
     <t>2004</t>
   </si>
   <si>
-    <t>火焰术·系数</t>
+    <t>烈焰环·系数</t>
   </si>
   <si>
     <t>10044</t>
   </si>
   <si>
-    <t>火焰术·固伤</t>
+    <t>烈焰环·固伤</t>
   </si>
   <si>
     <t>10045</t>
   </si>
   <si>
-    <t>火焰术·暴击</t>
+    <t>烈焰环·暴击</t>
   </si>
   <si>
     <t>10046</t>
   </si>
   <si>
-    <t>火焰术·暴伤</t>
+    <t>烈焰环·暴伤</t>
   </si>
   <si>
     <t>10047</t>
   </si>
   <si>
-    <t>火焰术·易伤</t>
+    <t>烈焰环·易伤</t>
   </si>
   <si>
     <t>10048</t>
@@ -864,31 +864,31 @@
     <t>2007</t>
   </si>
   <si>
-    <t>冰冻术·系数</t>
+    <t>冰爆术·系数</t>
   </si>
   <si>
     <t>10051</t>
   </si>
   <si>
-    <t>冰冻术·固伤</t>
+    <t>冰爆术·固伤</t>
   </si>
   <si>
     <t>10052</t>
   </si>
   <si>
-    <t>冰冻术·暴击</t>
+    <t>冰爆术·暴击</t>
   </si>
   <si>
     <t>10053</t>
   </si>
   <si>
-    <t>冰冻术·暴伤</t>
+    <t>冰爆术·暴伤</t>
   </si>
   <si>
     <t>10054</t>
   </si>
   <si>
-    <t>冰冻术·易伤</t>
+    <t>冰爆术·易伤</t>
   </si>
   <si>
     <t>10055</t>
@@ -897,7 +897,7 @@
     <t>3001</t>
   </si>
   <si>
-    <t>治疗道法·系数</t>
+    <t>疗伤术·系数</t>
   </si>
   <si>
     <t>10056</t>
@@ -906,7 +906,7 @@
     <t>3002</t>
   </si>
   <si>
-    <t>火符道法·系数</t>
+    <t>驱魔符·系数</t>
   </si>
   <si>
     <t>10057</t>
@@ -981,7 +981,7 @@
     <t>10066</t>
   </si>
   <si>
-    <t>武力盾·固伤</t>
+    <t>武神盾·固伤</t>
   </si>
   <si>
     <t>增加2000*技能等级点固定系数</t>
@@ -1008,13 +1008,13 @@
     <t>10070</t>
   </si>
   <si>
-    <t>治疗道法·固伤</t>
+    <t>疗伤术·固伤</t>
   </si>
   <si>
     <t>10071</t>
   </si>
   <si>
-    <t>火符道法·固伤</t>
+    <t>驱魔符·固伤</t>
   </si>
   <si>
     <t>10072</t>
@@ -1041,28 +1041,28 @@
     <t>召唤魔兽·固伤</t>
   </si>
   <si>
-    <t>火墙·大大大</t>
+    <t>火焰墙·大大大</t>
   </si>
   <si>
     <t>增加一行一列范围</t>
   </si>
   <si>
-    <t>火墙·废弃</t>
+    <t>火焰墙·废弃</t>
   </si>
   <si>
     <t>此词条废弃了</t>
   </si>
   <si>
-    <t>火焰术·大大大</t>
-  </si>
-  <si>
-    <t>火焰术·废弃</t>
-  </si>
-  <si>
-    <t>冰冻术·大大大</t>
-  </si>
-  <si>
-    <t>冰冻术·废弃</t>
+    <t>烈焰环·大大大</t>
+  </si>
+  <si>
+    <t>烈焰环·废弃</t>
+  </si>
+  <si>
+    <t>冰爆术·大大大</t>
+  </si>
+  <si>
+    <t>冰爆术·废弃</t>
   </si>
   <si>
     <t>火球术·多重</t>
@@ -1071,7 +1071,7 @@
     <t>增加一个攻击目标</t>
   </si>
   <si>
-    <t>神雷术·多重</t>
+    <t>落雷术·多重</t>
   </si>
   <si>
     <t>穿刺·远攻</t>
@@ -1092,7 +1092,7 @@
     <t>多召唤一只神兽</t>
   </si>
   <si>
-    <t>神雷术·鹰眼</t>
+    <t>落雷术·鹰眼</t>
   </si>
   <si>
     <t>增加一格攻击距离</t>
@@ -1101,7 +1101,7 @@
     <t>火球术·鹰眼</t>
   </si>
   <si>
-    <t>武力盾·持久</t>
+    <t>武神盾·持久</t>
   </si>
   <si>
     <t>增加10s持续时间</t>
@@ -1119,13 +1119,13 @@
     <t>召唤物增加5%高级属性继承</t>
   </si>
   <si>
-    <t>冰冻术·霜寒</t>
+    <t>冰爆术·霜寒</t>
   </si>
   <si>
     <t>增加20%最终技能伤害</t>
   </si>
   <si>
-    <t>火焰剑法·噬骨</t>
+    <t>烈焰斩·噬骨</t>
   </si>
   <si>
     <t>增加点燃系数10%</t>
@@ -1134,13 +1134,13 @@
     <t>火符·鹰眼</t>
   </si>
   <si>
-    <t>护体神盾·武力</t>
+    <t>战吼·武力</t>
   </si>
   <si>
     <t>物理伤害系数增加10%</t>
   </si>
   <si>
-    <t>瞬移术·法力</t>
+    <t>心灵传送·法力</t>
   </si>
   <si>
     <t>法术伤害系数增加10%</t>
@@ -1158,13 +1158,13 @@
     <t>火符·暴伤</t>
   </si>
   <si>
-    <t>开天辟地·急速</t>
+    <t>裂天斩·急速</t>
   </si>
   <si>
     <t>CD时间-3s</t>
   </si>
   <si>
-    <t>火雨术·大大大</t>
+    <t>毁灭流星·大大大</t>
   </si>
   <si>
     <t>攻击范围行列+1</t>
@@ -1197,31 +1197,31 @@
     <t>提高此技能系数10%倍率</t>
   </si>
   <si>
-    <t>穿刺剑术·精通</t>
-  </si>
-  <si>
-    <t>圆月弯刀·精通</t>
+    <t>流光剑法·精通</t>
+  </si>
+  <si>
+    <t>旋风斩·精通</t>
   </si>
   <si>
     <t>蛮力撞击·精通</t>
   </si>
   <si>
-    <t>武力盾·精通</t>
+    <t>武神盾·精通</t>
   </si>
   <si>
     <t>武力精通·精通</t>
   </si>
   <si>
-    <t>火焰剑法·精通</t>
-  </si>
-  <si>
-    <t>护体神盾·精通</t>
-  </si>
-  <si>
-    <t>开天辟地·精通</t>
-  </si>
-  <si>
-    <t>地刺术·精通</t>
+    <t>烈焰斩·精通</t>
+  </si>
+  <si>
+    <t>战吼·精通</t>
+  </si>
+  <si>
+    <t>裂天斩·精通</t>
+  </si>
+  <si>
+    <t>裂地斩·精通</t>
   </si>
   <si>
     <t>#</t>
@@ -1233,13 +1233,13 @@
     <t>火球术·精通</t>
   </si>
   <si>
-    <t>神雷术·精通</t>
-  </si>
-  <si>
-    <t>火墙·精通</t>
-  </si>
-  <si>
-    <t>火焰术·精通</t>
+    <t>落雷术·精通</t>
+  </si>
+  <si>
+    <t>火焰墙·精通</t>
+  </si>
+  <si>
+    <t>烈焰环·精通</t>
   </si>
   <si>
     <t>法力盾·精通</t>
@@ -1248,13 +1248,13 @@
     <t>法术精通·精通</t>
   </si>
   <si>
-    <t>瞬移术·精通</t>
+    <t>心灵传送·精通</t>
   </si>
   <si>
     <t>闪烁术·精通</t>
   </si>
   <si>
-    <t>火雨术·精通</t>
+    <t>毁灭流星·精通</t>
   </si>
   <si>
     <t>分身术·精通</t>
@@ -1263,10 +1263,10 @@
     <t>法师之魂·精通</t>
   </si>
   <si>
-    <t>治疗道法·精通</t>
-  </si>
-  <si>
-    <t>火符道法·精通</t>
+    <t>疗伤术·精通</t>
+  </si>
+  <si>
+    <t>驱魔符·精通</t>
   </si>
   <si>
     <t>毒咒道法·精通</t>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -1074,7 +1074,7 @@
     <t>落雷术·多重</t>
   </si>
   <si>
-    <t>穿刺·远攻</t>
+    <t>裂地斩·远攻</t>
   </si>
   <si>
     <t>增加一格攻击范围</t>
@@ -1131,7 +1131,7 @@
     <t>增加点燃系数10%</t>
   </si>
   <si>
-    <t>火符·鹰眼</t>
+    <t>驱魔符·鹰眼</t>
   </si>
   <si>
     <t>战吼·武力</t>
@@ -1152,10 +1152,10 @@
     <t>宠物攻击系数增加10%</t>
   </si>
   <si>
-    <t>火符·暴击</t>
-  </si>
-  <si>
-    <t>火符·暴伤</t>
+    <t>驱魔符·暴击</t>
+  </si>
+  <si>
+    <t>驱魔符·暴伤</t>
   </si>
   <si>
     <t>裂天斩·急速</t>
@@ -1176,7 +1176,7 @@
     <t>技能系数增加50%</t>
   </si>
   <si>
-    <t>火符·易伤</t>
+    <t>驱魔符·易伤</t>
   </si>
   <si>
     <t>此技能ID</t>
@@ -1478,12 +1478,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -1248,10 +1248,10 @@
     <t>法术精通·精通</t>
   </si>
   <si>
+    <t>冰爆术·精通</t>
+  </si>
+  <si>
     <t>心灵传送·精通</t>
-  </si>
-  <si>
-    <t>闪烁术·精通</t>
   </si>
   <si>
     <t>毁灭流星·精通</t>
@@ -1478,12 +1478,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -1074,7 +1074,7 @@
     <t>落雷术·多重</t>
   </si>
   <si>
-    <t>裂地斩·远攻</t>
+    <t>流光剑法·远攻</t>
   </si>
   <si>
     <t>增加一格攻击范围</t>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -1194,7 +1194,7 @@
     <t>基础剑术·精通</t>
   </si>
   <si>
-    <t>提高此技能系数10%倍率</t>
+    <t>提高此技能系数10%系数增幅</t>
   </si>
   <si>
     <t>流光剑法·精通</t>
@@ -1478,12 +1478,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
     <sheet name="手动配置" sheetId="2" r:id="rId2"/>
     <sheet name="金装" sheetId="3" r:id="rId3"/>
+    <sheet name="暗金" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -339,8 +340,63 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+ID* 10 + level
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+攻击力系数（百分比），额外附加固定伤害值</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="341">
   <si>
     <t>_ID</t>
   </si>
@@ -1294,6 +1350,75 @@
   </si>
   <si>
     <t>道士之魂·精通</t>
+  </si>
+  <si>
+    <t>SkillLayer</t>
+  </si>
+  <si>
+    <t>一阶·精通</t>
+  </si>
+  <si>
+    <t>提高一阶全系技能系数10%系数增幅</t>
+  </si>
+  <si>
+    <t>二阶·精通</t>
+  </si>
+  <si>
+    <t>提高二阶全系技能系数10%系数增幅</t>
+  </si>
+  <si>
+    <t>三阶·精通</t>
+  </si>
+  <si>
+    <t>提高三阶全系技能系数10%系数增幅</t>
+  </si>
+  <si>
+    <t>四阶·精通</t>
+  </si>
+  <si>
+    <t>提高四阶全系技能系数10%系数增幅</t>
+  </si>
+  <si>
+    <t>五阶·精通</t>
+  </si>
+  <si>
+    <t>提高五阶全系技能系数10%系数增幅</t>
+  </si>
+  <si>
+    <t>六阶·精通</t>
+  </si>
+  <si>
+    <t>提高六阶全系技能系数10%系数增幅</t>
+  </si>
+  <si>
+    <t>七阶·精通</t>
+  </si>
+  <si>
+    <t>提高七阶全系技能系数10%系数增幅</t>
+  </si>
+  <si>
+    <t>八阶·精通</t>
+  </si>
+  <si>
+    <t>提高八阶全系技能系数10%系数增幅</t>
+  </si>
+  <si>
+    <t>九阶·精通</t>
+  </si>
+  <si>
+    <t>提高九阶全系技能系数10%系数增幅</t>
+  </si>
+  <si>
+    <t>十阶·精通</t>
+  </si>
+  <si>
+    <t>提高十阶全系技能系数10%系数增幅</t>
+  </si>
+  <si>
+    <t>十一阶·精通</t>
+  </si>
+  <si>
+    <t>提高十一阶全系技能系数10%系数增幅</t>
   </si>
 </sst>
 </file>
@@ -1478,12 +1603,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -12194,4 +12319,515 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C3:U16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="7" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="15.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="25.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.25" style="1" customWidth="1"/>
+    <col min="13" max="14" width="7.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.5" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.625" style="1" customWidth="1"/>
+    <col min="18" max="20" width="13" style="1" customWidth="1"/>
+    <col min="21" max="21" width="7.375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C6" s="1">
+        <v>21001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>200</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="K6" s="1">
+        <v>10</v>
+      </c>
+      <c r="L6" s="1">
+        <v>10</v>
+      </c>
+      <c r="R6" s="5"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C7" s="1">
+        <v>21002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>200</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K7" s="1">
+        <v>10</v>
+      </c>
+      <c r="L7" s="1">
+        <v>10</v>
+      </c>
+      <c r="R7" s="5"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C8" s="1">
+        <v>21003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>100</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="K8" s="1">
+        <v>10</v>
+      </c>
+      <c r="L8" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C9" s="1">
+        <v>21004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>100</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="K9" s="1">
+        <v>10</v>
+      </c>
+      <c r="L9" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C10" s="1">
+        <v>21005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>100</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="K10" s="1">
+        <v>8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C11" s="1">
+        <v>21006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>100</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>6</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="K11" s="1">
+        <v>7</v>
+      </c>
+      <c r="L11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C12" s="1">
+        <v>21007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>50</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>7</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C13" s="1">
+        <v>21008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>50</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>8</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="K13" s="1">
+        <v>5</v>
+      </c>
+      <c r="L13" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C14" s="1">
+        <v>21009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>50</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>9</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="K14" s="1">
+        <v>4</v>
+      </c>
+      <c r="L14" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C15" s="1">
+        <v>21010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>10</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="K15" s="1">
+        <v>3</v>
+      </c>
+      <c r="L15" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C16" s="1">
+        <v>21011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>5</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>11</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="K16" s="1">
+        <v>2</v>
+      </c>
+      <c r="L16" s="1">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -1603,12 +1603,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -12477,7 +12477,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -12510,7 +12510,7 @@
         <v>200</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -12543,7 +12543,7 @@
         <v>100</v>
       </c>
       <c r="F8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -12575,7 +12575,7 @@
         <v>100</v>
       </c>
       <c r="F9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -12639,7 +12639,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -12671,7 +12671,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -12703,7 +12703,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -12735,7 +12735,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -12767,7 +12767,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -12799,7 +12799,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -1355,67 +1355,67 @@
     <t>SkillLayer</t>
   </si>
   <si>
-    <t>一阶·精通</t>
+    <t>一阶·专精</t>
   </si>
   <si>
     <t>提高一阶全系技能系数10%系数增幅</t>
   </si>
   <si>
-    <t>二阶·精通</t>
+    <t>二阶·专精</t>
   </si>
   <si>
     <t>提高二阶全系技能系数10%系数增幅</t>
   </si>
   <si>
-    <t>三阶·精通</t>
+    <t>三阶·专精</t>
   </si>
   <si>
     <t>提高三阶全系技能系数10%系数增幅</t>
   </si>
   <si>
-    <t>四阶·精通</t>
+    <t>四阶·专精</t>
   </si>
   <si>
     <t>提高四阶全系技能系数10%系数增幅</t>
   </si>
   <si>
-    <t>五阶·精通</t>
+    <t>五阶·专精</t>
   </si>
   <si>
     <t>提高五阶全系技能系数10%系数增幅</t>
   </si>
   <si>
-    <t>六阶·精通</t>
+    <t>六阶·专精</t>
   </si>
   <si>
     <t>提高六阶全系技能系数10%系数增幅</t>
   </si>
   <si>
-    <t>七阶·精通</t>
+    <t>七阶·专精</t>
   </si>
   <si>
     <t>提高七阶全系技能系数10%系数增幅</t>
   </si>
   <si>
-    <t>八阶·精通</t>
+    <t>八阶·专精</t>
   </si>
   <si>
     <t>提高八阶全系技能系数10%系数增幅</t>
   </si>
   <si>
-    <t>九阶·精通</t>
+    <t>九阶·专精</t>
   </si>
   <si>
     <t>提高九阶全系技能系数10%系数增幅</t>
   </si>
   <si>
-    <t>十阶·精通</t>
+    <t>十阶·专精</t>
   </si>
   <si>
     <t>提高十阶全系技能系数10%系数增幅</t>
   </si>
   <si>
-    <t>十一阶·精通</t>
+    <t>十一阶·专精</t>
   </si>
   <si>
     <t>提高十一阶全系技能系数10%系数增幅</t>
@@ -1603,12 +1603,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -12796,7 +12796,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -12492,7 +12492,7 @@
         <v>320</v>
       </c>
       <c r="K6" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L6" s="1">
         <v>10</v>
@@ -12525,7 +12525,7 @@
         <v>322</v>
       </c>
       <c r="K7" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L7" s="1">
         <v>10</v>
@@ -12558,7 +12558,7 @@
         <v>324</v>
       </c>
       <c r="K8" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L8" s="1">
         <v>10</v>
@@ -12590,7 +12590,7 @@
         <v>326</v>
       </c>
       <c r="K9" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L9" s="1">
         <v>10</v>
@@ -12622,7 +12622,7 @@
         <v>328</v>
       </c>
       <c r="K10" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L10" s="1">
         <v>10</v>
@@ -12654,7 +12654,7 @@
         <v>330</v>
       </c>
       <c r="K11" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L11" s="1">
         <v>10</v>
@@ -12686,7 +12686,7 @@
         <v>332</v>
       </c>
       <c r="K12" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L12" s="1">
         <v>10</v>
@@ -12718,7 +12718,7 @@
         <v>334</v>
       </c>
       <c r="K13" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L13" s="1">
         <v>10</v>
@@ -12750,7 +12750,7 @@
         <v>336</v>
       </c>
       <c r="K14" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L14" s="1">
         <v>10</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="3"/>
+    <workbookView windowWidth="27952" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -2408,19 +2408,19 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="17.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="28.625" style="1" customWidth="1"/>
-    <col min="10" max="12" width="10.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="11.75" style="1" customWidth="1"/>
-    <col min="14" max="15" width="10.375" style="1" customWidth="1"/>
-    <col min="16" max="18" width="13.75" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.375" style="1" customWidth="1"/>
-    <col min="20" max="21" width="7.75" style="1" customWidth="1"/>
-    <col min="22" max="22" width="7.5" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="12.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5044247787611" style="1" customWidth="1"/>
+    <col min="9" max="9" width="28.6283185840708" style="1" customWidth="1"/>
+    <col min="10" max="12" width="10.3716814159292" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7522123893805" style="1" customWidth="1"/>
+    <col min="14" max="15" width="10.3716814159292" style="1" customWidth="1"/>
+    <col min="16" max="18" width="13.7522123893805" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.3716814159292" style="1" customWidth="1"/>
+    <col min="20" max="21" width="7.75221238938053" style="1" customWidth="1"/>
+    <col min="22" max="22" width="7.50442477876106" style="1" customWidth="1"/>
+    <col min="23" max="23" width="10.6283185840708" style="1" customWidth="1"/>
+    <col min="24" max="24" width="12.6283185840708" style="1" customWidth="1"/>
     <col min="25" max="27" width="13" style="1" customWidth="1"/>
-    <col min="28" max="28" width="7.375" style="1" customWidth="1"/>
+    <col min="28" max="28" width="7.3716814159292" style="1" customWidth="1"/>
     <col min="29" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -8685,20 +8685,20 @@
   <cols>
     <col min="1" max="7" width="9" style="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5" style="1" customWidth="1"/>
-    <col min="14" max="15" width="10.375" style="1" customWidth="1"/>
-    <col min="16" max="18" width="13.75" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.375" style="1" customWidth="1"/>
-    <col min="20" max="21" width="7.75" style="1" customWidth="1"/>
-    <col min="22" max="22" width="7.5" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="12.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.1238938053097" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.3716814159292" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.3716814159292" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6283185840708" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5044247787611" style="1" customWidth="1"/>
+    <col min="14" max="15" width="10.3716814159292" style="1" customWidth="1"/>
+    <col min="16" max="18" width="13.7522123893805" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.3716814159292" style="1" customWidth="1"/>
+    <col min="20" max="21" width="7.75221238938053" style="1" customWidth="1"/>
+    <col min="22" max="22" width="7.50442477876106" style="1" customWidth="1"/>
+    <col min="23" max="23" width="10.6283185840708" style="1" customWidth="1"/>
+    <col min="24" max="24" width="12.6283185840708" style="1" customWidth="1"/>
     <col min="25" max="27" width="13" style="1" customWidth="1"/>
-    <col min="28" max="28" width="7.375" style="1" customWidth="1"/>
+    <col min="28" max="28" width="7.3716814159292" style="1" customWidth="1"/>
     <col min="29" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -11203,18 +11203,18 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="10.8761061946903" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="15.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.25" style="1" customWidth="1"/>
-    <col min="12" max="13" width="7.75" style="1" customWidth="1"/>
-    <col min="14" max="14" width="7.5" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6283185840708" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.1238938053097" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.3716814159292" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.2477876106195" style="1" customWidth="1"/>
+    <col min="12" max="13" width="7.75221238938053" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.50442477876106" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.6283185840708" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.6283185840708" style="1" customWidth="1"/>
     <col min="17" max="19" width="13" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.3716814159292" style="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -11603,7 +11603,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -11928,7 +11928,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F27" s="1">
         <v>2</v>
@@ -12253,7 +12253,7 @@
         <v>2</v>
       </c>
       <c r="E39" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F39" s="1">
         <v>3</v>
@@ -12328,18 +12328,18 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="10.8761061946903" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1"/>
-    <col min="9" max="9" width="15.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="25.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.25" style="1" customWidth="1"/>
-    <col min="13" max="14" width="7.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.5" style="1" customWidth="1"/>
-    <col min="16" max="16" width="10.625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6283185840708" style="1" customWidth="1"/>
+    <col min="10" max="10" width="25.6283185840708" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.3716814159292" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.2477876106195" style="1" customWidth="1"/>
+    <col min="13" max="14" width="7.75221238938053" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.50442477876106" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6283185840708" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.6283185840708" style="1" customWidth="1"/>
     <col min="18" max="20" width="13" style="1" customWidth="1"/>
-    <col min="21" max="21" width="7.375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="7.3716814159292" style="1" customWidth="1"/>
     <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -452,7 +452,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="395">
   <si>
     <t>_ID</t>
   </si>
@@ -1532,9 +1532,6 @@
   </si>
   <si>
     <t>剑二十三·天目</t>
-  </si>
-  <si>
-    <t>战吼·迷踪</t>
   </si>
   <si>
     <t>火球术·大师</t>
@@ -14362,7 +14359,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:V60"/>
+  <dimension ref="C3:V59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -14537,7 +14534,7 @@
         <v>31001</v>
       </c>
       <c r="D6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1">
         <v>500</v>
@@ -14567,10 +14564,10 @@
         <v>15</v>
       </c>
       <c r="N6" s="1">
+        <v>7</v>
+      </c>
+      <c r="O6" s="1">
         <v>9</v>
-      </c>
-      <c r="O6" s="1">
-        <v>10</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
@@ -14582,7 +14579,7 @@
         <v>31002</v>
       </c>
       <c r="D7" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1">
         <v>100</v>
@@ -14612,10 +14609,10 @@
         <v>15</v>
       </c>
       <c r="N7" s="1">
+        <v>7</v>
+      </c>
+      <c r="O7" s="1">
         <v>9</v>
-      </c>
-      <c r="O7" s="1">
-        <v>10</v>
       </c>
       <c r="P7" s="1">
         <v>0</v>
@@ -14627,7 +14624,7 @@
         <v>31003</v>
       </c>
       <c r="D8" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1">
         <v>500</v>
@@ -14657,10 +14654,10 @@
         <v>15</v>
       </c>
       <c r="N8" s="1">
+        <v>7</v>
+      </c>
+      <c r="O8" s="1">
         <v>9</v>
-      </c>
-      <c r="O8" s="1">
-        <v>10</v>
       </c>
       <c r="P8" s="1">
         <v>0</v>
@@ -14671,7 +14668,7 @@
         <v>31004</v>
       </c>
       <c r="D9" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1">
         <v>500</v>
@@ -14701,10 +14698,10 @@
         <v>15</v>
       </c>
       <c r="N9" s="1">
+        <v>7</v>
+      </c>
+      <c r="O9" s="1">
         <v>9</v>
-      </c>
-      <c r="O9" s="1">
-        <v>10</v>
       </c>
       <c r="P9" s="1">
         <v>0</v>
@@ -14715,7 +14712,7 @@
         <v>31005</v>
       </c>
       <c r="D10" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
@@ -14745,10 +14742,10 @@
         <v>15</v>
       </c>
       <c r="N10" s="1">
+        <v>7</v>
+      </c>
+      <c r="O10" s="1">
         <v>9</v>
-      </c>
-      <c r="O10" s="1">
-        <v>10</v>
       </c>
       <c r="P10" s="1">
         <v>0</v>
@@ -14759,7 +14756,7 @@
         <v>31006</v>
       </c>
       <c r="D11" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
@@ -14789,10 +14786,10 @@
         <v>15</v>
       </c>
       <c r="N11" s="1">
+        <v>7</v>
+      </c>
+      <c r="O11" s="1">
         <v>9</v>
-      </c>
-      <c r="O11" s="1">
-        <v>10</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
@@ -14803,7 +14800,7 @@
         <v>31007</v>
       </c>
       <c r="D12" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1">
         <v>500</v>
@@ -14833,10 +14830,10 @@
         <v>15</v>
       </c>
       <c r="N12" s="1">
+        <v>7</v>
+      </c>
+      <c r="O12" s="1">
         <v>9</v>
-      </c>
-      <c r="O12" s="1">
-        <v>10</v>
       </c>
       <c r="P12" s="1">
         <v>0</v>
@@ -14847,7 +14844,7 @@
         <v>31008</v>
       </c>
       <c r="D13" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1">
         <v>20</v>
@@ -14877,10 +14874,10 @@
         <v>15</v>
       </c>
       <c r="N13" s="1">
+        <v>7</v>
+      </c>
+      <c r="O13" s="1">
         <v>9</v>
-      </c>
-      <c r="O13" s="1">
-        <v>10</v>
       </c>
       <c r="P13" s="1">
         <v>0</v>
@@ -14891,7 +14888,7 @@
         <v>31009</v>
       </c>
       <c r="D14" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1">
         <v>30</v>
@@ -14921,10 +14918,10 @@
         <v>15</v>
       </c>
       <c r="N14" s="1">
+        <v>7</v>
+      </c>
+      <c r="O14" s="1">
         <v>9</v>
-      </c>
-      <c r="O14" s="1">
-        <v>10</v>
       </c>
       <c r="P14" s="1">
         <v>0</v>
@@ -14935,7 +14932,7 @@
         <v>31010</v>
       </c>
       <c r="D15" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="1">
         <v>10</v>
@@ -14965,10 +14962,10 @@
         <v>15</v>
       </c>
       <c r="N15" s="1">
+        <v>7</v>
+      </c>
+      <c r="O15" s="1">
         <v>9</v>
-      </c>
-      <c r="O15" s="1">
-        <v>10</v>
       </c>
       <c r="P15" s="1">
         <v>0</v>
@@ -14979,7 +14976,7 @@
         <v>31011</v>
       </c>
       <c r="D16" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="1">
         <v>10</v>
@@ -15009,10 +15006,10 @@
         <v>15</v>
       </c>
       <c r="N16" s="1">
+        <v>7</v>
+      </c>
+      <c r="O16" s="1">
         <v>9</v>
-      </c>
-      <c r="O16" s="1">
-        <v>10</v>
       </c>
       <c r="P16" s="1">
         <v>0</v>
@@ -15023,7 +15020,7 @@
         <v>31012</v>
       </c>
       <c r="D17" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="1">
         <v>10</v>
@@ -15053,10 +15050,10 @@
         <v>10</v>
       </c>
       <c r="N17" s="1">
+        <v>7</v>
+      </c>
+      <c r="O17" s="1">
         <v>9</v>
-      </c>
-      <c r="O17" s="1">
-        <v>10</v>
       </c>
       <c r="P17" s="1">
         <v>0</v>
@@ -15067,7 +15064,7 @@
         <v>31112</v>
       </c>
       <c r="D18" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="1">
         <v>10</v>
@@ -15097,10 +15094,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="1">
+        <v>7</v>
+      </c>
+      <c r="O18" s="1">
         <v>9</v>
-      </c>
-      <c r="O18" s="1">
-        <v>10</v>
       </c>
       <c r="P18" s="1">
         <v>0</v>
@@ -15108,10 +15105,10 @@
     </row>
     <row r="19" customHeight="1" spans="3:16">
       <c r="C19" s="1">
-        <v>31312</v>
+        <v>31212</v>
       </c>
       <c r="D19" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="1">
         <v>10</v>
@@ -15141,10 +15138,10 @@
         <v>0</v>
       </c>
       <c r="N19" s="1">
+        <v>7</v>
+      </c>
+      <c r="O19" s="1">
         <v>9</v>
-      </c>
-      <c r="O19" s="1">
-        <v>10</v>
       </c>
       <c r="P19" s="1">
         <v>0</v>
@@ -15156,10 +15153,10 @@
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C21" s="1">
-        <v>31008</v>
+        <v>31108</v>
       </c>
       <c r="D21" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" s="1">
         <v>20</v>
@@ -15189,10 +15186,10 @@
         <v>15</v>
       </c>
       <c r="N21" s="1">
+        <v>7</v>
+      </c>
+      <c r="O21" s="1">
         <v>9</v>
-      </c>
-      <c r="O21" s="1">
-        <v>10</v>
       </c>
       <c r="P21" s="1">
         <v>0</v>
@@ -15200,10 +15197,10 @@
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C22" s="1">
-        <v>31010</v>
+        <v>31110</v>
       </c>
       <c r="D22" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="1">
         <v>10</v>
@@ -15227,16 +15224,16 @@
         <v>358</v>
       </c>
       <c r="L22" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M22" s="1">
         <v>15</v>
       </c>
       <c r="N22" s="1">
+        <v>7</v>
+      </c>
+      <c r="O22" s="1">
         <v>9</v>
-      </c>
-      <c r="O22" s="1">
-        <v>10</v>
       </c>
       <c r="P22" s="1">
         <v>0</v>
@@ -15244,10 +15241,10 @@
     </row>
     <row r="23" customHeight="1" spans="3:16">
       <c r="C23" s="1">
-        <v>31012</v>
+        <v>31312</v>
       </c>
       <c r="D23" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" s="1">
         <v>10</v>
@@ -15277,58 +15274,19 @@
         <v>10</v>
       </c>
       <c r="N23" s="1">
+        <v>7</v>
+      </c>
+      <c r="O23" s="1">
         <v>9</v>
       </c>
-      <c r="O23" s="1">
-        <v>10</v>
-      </c>
       <c r="P23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="3:16">
-      <c r="C24" s="1">
-        <v>31012</v>
-      </c>
-      <c r="D24" s="1">
-        <v>4</v>
-      </c>
-      <c r="E24" s="1">
-        <v>10</v>
-      </c>
-      <c r="F24" s="1">
-        <v>10</v>
-      </c>
-      <c r="G24" s="1">
-        <v>1</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1012</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="L24" s="1">
-        <v>4</v>
-      </c>
-      <c r="M24" s="1">
-        <v>10</v>
-      </c>
-      <c r="N24" s="1">
-        <v>9</v>
-      </c>
-      <c r="O24" s="1">
-        <v>10</v>
-      </c>
-      <c r="P24" s="1">
-        <v>0</v>
-      </c>
+    <row r="24" customHeight="1" spans="8:10">
+      <c r="H24" s="3"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="3"/>
     </row>
     <row r="25" customHeight="1" spans="8:10">
       <c r="H25" s="3"/>
@@ -15339,7 +15297,7 @@
         <v>32001</v>
       </c>
       <c r="D26" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="1">
         <v>500</v>
@@ -15357,7 +15315,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>341</v>
@@ -15369,10 +15327,10 @@
         <v>15</v>
       </c>
       <c r="N26" s="1">
+        <v>7</v>
+      </c>
+      <c r="O26" s="1">
         <v>9</v>
-      </c>
-      <c r="O26" s="1">
-        <v>10</v>
       </c>
       <c r="P26" s="1">
         <v>0</v>
@@ -15383,7 +15341,7 @@
         <v>32002</v>
       </c>
       <c r="D27" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" s="1">
         <v>100</v>
@@ -15401,7 +15359,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>341</v>
@@ -15413,10 +15371,10 @@
         <v>15</v>
       </c>
       <c r="N27" s="1">
+        <v>7</v>
+      </c>
+      <c r="O27" s="1">
         <v>9</v>
-      </c>
-      <c r="O27" s="1">
-        <v>10</v>
       </c>
       <c r="P27" s="1">
         <v>0</v>
@@ -15427,7 +15385,7 @@
         <v>32003</v>
       </c>
       <c r="D28" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="1">
         <v>500</v>
@@ -15445,7 +15403,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>341</v>
@@ -15457,10 +15415,10 @@
         <v>15</v>
       </c>
       <c r="N28" s="1">
+        <v>7</v>
+      </c>
+      <c r="O28" s="1">
         <v>9</v>
-      </c>
-      <c r="O28" s="1">
-        <v>10</v>
       </c>
       <c r="P28" s="1">
         <v>0</v>
@@ -15471,7 +15429,7 @@
         <v>32004</v>
       </c>
       <c r="D29" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" s="1">
         <v>500</v>
@@ -15489,7 +15447,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>341</v>
@@ -15501,10 +15459,10 @@
         <v>15</v>
       </c>
       <c r="N29" s="1">
+        <v>7</v>
+      </c>
+      <c r="O29" s="1">
         <v>9</v>
-      </c>
-      <c r="O29" s="1">
-        <v>10</v>
       </c>
       <c r="P29" s="1">
         <v>0</v>
@@ -15515,7 +15473,7 @@
         <v>32005</v>
       </c>
       <c r="D30" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" s="1">
         <v>50</v>
@@ -15533,7 +15491,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>341</v>
@@ -15545,10 +15503,10 @@
         <v>15</v>
       </c>
       <c r="N30" s="1">
+        <v>7</v>
+      </c>
+      <c r="O30" s="1">
         <v>9</v>
-      </c>
-      <c r="O30" s="1">
-        <v>10</v>
       </c>
       <c r="P30" s="1">
         <v>0</v>
@@ -15559,7 +15517,7 @@
         <v>32006</v>
       </c>
       <c r="D31" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="1">
         <v>50</v>
@@ -15577,7 +15535,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>341</v>
@@ -15589,10 +15547,10 @@
         <v>15</v>
       </c>
       <c r="N31" s="1">
+        <v>7</v>
+      </c>
+      <c r="O31" s="1">
         <v>9</v>
-      </c>
-      <c r="O31" s="1">
-        <v>10</v>
       </c>
       <c r="P31" s="1">
         <v>0</v>
@@ -15603,7 +15561,7 @@
         <v>32007</v>
       </c>
       <c r="D32" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32" s="1">
         <v>500</v>
@@ -15621,7 +15579,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>341</v>
@@ -15633,10 +15591,10 @@
         <v>15</v>
       </c>
       <c r="N32" s="1">
+        <v>7</v>
+      </c>
+      <c r="O32" s="1">
         <v>9</v>
-      </c>
-      <c r="O32" s="1">
-        <v>10</v>
       </c>
       <c r="P32" s="1">
         <v>0</v>
@@ -15647,7 +15605,7 @@
         <v>32008</v>
       </c>
       <c r="D33" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" s="1">
         <v>20</v>
@@ -15665,7 +15623,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>341</v>
@@ -15677,10 +15635,10 @@
         <v>15</v>
       </c>
       <c r="N33" s="1">
+        <v>7</v>
+      </c>
+      <c r="O33" s="1">
         <v>9</v>
-      </c>
-      <c r="O33" s="1">
-        <v>10</v>
       </c>
       <c r="P33" s="1">
         <v>0</v>
@@ -15691,7 +15649,7 @@
         <v>32009</v>
       </c>
       <c r="D34" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" s="1">
         <v>30</v>
@@ -15709,7 +15667,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>341</v>
@@ -15721,10 +15679,10 @@
         <v>15</v>
       </c>
       <c r="N34" s="1">
+        <v>7</v>
+      </c>
+      <c r="O34" s="1">
         <v>9</v>
-      </c>
-      <c r="O34" s="1">
-        <v>10</v>
       </c>
       <c r="P34" s="1">
         <v>0</v>
@@ -15735,7 +15693,7 @@
         <v>32010</v>
       </c>
       <c r="D35" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="1">
         <v>10</v>
@@ -15753,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>341</v>
@@ -15765,10 +15723,10 @@
         <v>15</v>
       </c>
       <c r="N35" s="1">
+        <v>7</v>
+      </c>
+      <c r="O35" s="1">
         <v>9</v>
-      </c>
-      <c r="O35" s="1">
-        <v>10</v>
       </c>
       <c r="P35" s="1">
         <v>0</v>
@@ -15779,7 +15737,7 @@
         <v>32011</v>
       </c>
       <c r="D36" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="1">
         <v>10</v>
@@ -15797,7 +15755,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>341</v>
@@ -15809,10 +15767,10 @@
         <v>15</v>
       </c>
       <c r="N36" s="1">
+        <v>7</v>
+      </c>
+      <c r="O36" s="1">
         <v>9</v>
-      </c>
-      <c r="O36" s="1">
-        <v>10</v>
       </c>
       <c r="P36" s="1">
         <v>0</v>
@@ -15823,7 +15781,7 @@
         <v>32012</v>
       </c>
       <c r="D37" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" s="1">
         <v>10</v>
@@ -15841,7 +15799,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>287</v>
@@ -15853,10 +15811,10 @@
         <v>10</v>
       </c>
       <c r="N37" s="1">
+        <v>7</v>
+      </c>
+      <c r="O37" s="1">
         <v>9</v>
-      </c>
-      <c r="O37" s="1">
-        <v>10</v>
       </c>
       <c r="P37" s="1">
         <v>0</v>
@@ -15871,7 +15829,7 @@
         <v>32112</v>
       </c>
       <c r="D39" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" s="1">
         <v>10</v>
@@ -15889,10 +15847,10 @@
         <v>0</v>
       </c>
       <c r="J39" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="L39" s="1">
         <v>5</v>
@@ -15901,21 +15859,21 @@
         <v>0</v>
       </c>
       <c r="N39" s="1">
+        <v>7</v>
+      </c>
+      <c r="O39" s="1">
         <v>9</v>
-      </c>
-      <c r="O39" s="1">
-        <v>10</v>
       </c>
       <c r="P39" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C40" s="1">
-        <v>33008</v>
+        <v>32108</v>
       </c>
       <c r="D40" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40" s="1">
         <v>10</v>
@@ -15930,7 +15888,7 @@
         <v>2008</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>356</v>
@@ -15942,7 +15900,10 @@
         <v>0</v>
       </c>
       <c r="N40" s="1">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="O40" s="1">
+        <v>9</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="8:10">
@@ -15958,7 +15919,7 @@
         <v>33001</v>
       </c>
       <c r="D43" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" s="1">
         <v>500</v>
@@ -15976,7 +15937,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>341</v>
@@ -15988,10 +15949,10 @@
         <v>15</v>
       </c>
       <c r="N43" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O43" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P43" s="1">
         <v>0</v>
@@ -16002,7 +15963,7 @@
         <v>33002</v>
       </c>
       <c r="D44" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44" s="1">
         <v>100</v>
@@ -16020,7 +15981,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>341</v>
@@ -16032,10 +15993,10 @@
         <v>15</v>
       </c>
       <c r="N44" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O44" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P44" s="1">
         <v>0</v>
@@ -16046,7 +16007,7 @@
         <v>33003</v>
       </c>
       <c r="D45" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45" s="1">
         <v>500</v>
@@ -16064,7 +16025,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>341</v>
@@ -16076,10 +16037,10 @@
         <v>15</v>
       </c>
       <c r="N45" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O45" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P45" s="1">
         <v>0</v>
@@ -16090,7 +16051,7 @@
         <v>33004</v>
       </c>
       <c r="D46" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46" s="1">
         <v>500</v>
@@ -16108,7 +16069,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>341</v>
@@ -16120,10 +16081,10 @@
         <v>15</v>
       </c>
       <c r="N46" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O46" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P46" s="1">
         <v>0</v>
@@ -16134,7 +16095,7 @@
         <v>33005</v>
       </c>
       <c r="D47" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" s="1">
         <v>50</v>
@@ -16152,7 +16113,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>341</v>
@@ -16164,10 +16125,10 @@
         <v>15</v>
       </c>
       <c r="N47" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O47" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P47" s="1">
         <v>0</v>
@@ -16178,7 +16139,7 @@
         <v>33006</v>
       </c>
       <c r="D48" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48" s="1">
         <v>50</v>
@@ -16196,7 +16157,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>341</v>
@@ -16208,10 +16169,10 @@
         <v>15</v>
       </c>
       <c r="N48" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O48" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P48" s="1">
         <v>0</v>
@@ -16222,7 +16183,7 @@
         <v>33007</v>
       </c>
       <c r="D49" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49" s="1">
         <v>500</v>
@@ -16240,7 +16201,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>341</v>
@@ -16252,10 +16213,10 @@
         <v>15</v>
       </c>
       <c r="N49" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O49" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P49" s="1">
         <v>0</v>
@@ -16266,7 +16227,7 @@
         <v>33008</v>
       </c>
       <c r="D50" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E50" s="1">
         <v>20</v>
@@ -16284,7 +16245,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>341</v>
@@ -16296,10 +16257,10 @@
         <v>15</v>
       </c>
       <c r="N50" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O50" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P50" s="1">
         <v>0</v>
@@ -16310,7 +16271,7 @@
         <v>33009</v>
       </c>
       <c r="D51" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E51" s="1">
         <v>30</v>
@@ -16328,7 +16289,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>341</v>
@@ -16340,10 +16301,10 @@
         <v>15</v>
       </c>
       <c r="N51" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O51" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P51" s="1">
         <v>0</v>
@@ -16354,7 +16315,7 @@
         <v>33010</v>
       </c>
       <c r="D52" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E52" s="1">
         <v>10</v>
@@ -16372,7 +16333,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>341</v>
@@ -16384,10 +16345,10 @@
         <v>15</v>
       </c>
       <c r="N52" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O52" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P52" s="1">
         <v>0</v>
@@ -16398,7 +16359,7 @@
         <v>33011</v>
       </c>
       <c r="D53" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E53" s="1">
         <v>10</v>
@@ -16416,7 +16377,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>341</v>
@@ -16428,10 +16389,10 @@
         <v>15</v>
       </c>
       <c r="N53" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O53" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P53" s="1">
         <v>0</v>
@@ -16442,7 +16403,7 @@
         <v>33012</v>
       </c>
       <c r="D54" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E54" s="1">
         <v>10</v>
@@ -16460,7 +16421,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>287</v>
@@ -16472,10 +16433,10 @@
         <v>10</v>
       </c>
       <c r="N54" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O54" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P54" s="1">
         <v>0</v>
@@ -16486,7 +16447,7 @@
         <v>33112</v>
       </c>
       <c r="D55" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E55" s="1">
         <v>10</v>
@@ -16504,10 +16465,10 @@
         <v>0</v>
       </c>
       <c r="J55" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="K55" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="L55" s="1">
         <v>2</v>
@@ -16516,21 +16477,21 @@
         <v>0</v>
       </c>
       <c r="N55" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O55" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P55" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C57" s="1">
-        <v>33008</v>
+        <v>33108</v>
       </c>
       <c r="D57" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E57" s="1">
         <v>10</v>
@@ -16545,10 +16506,10 @@
         <v>3008</v>
       </c>
       <c r="J57" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="L57" s="1">
         <v>3</v>
@@ -16557,15 +16518,18 @@
         <v>0</v>
       </c>
       <c r="N57" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>7</v>
+      </c>
+      <c r="O57" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:16">
       <c r="C58" s="1">
-        <v>33008</v>
+        <v>33212</v>
       </c>
       <c r="D58" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E58" s="1">
         <v>10</v>
@@ -16577,30 +16541,39 @@
         <v>3</v>
       </c>
       <c r="H58" s="3">
-        <v>3008</v>
+        <v>3012</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L58" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M58" s="1">
         <v>0</v>
       </c>
       <c r="N58" s="1">
+        <v>7</v>
+      </c>
+      <c r="O58" s="1">
+        <v>7</v>
+      </c>
+      <c r="P58" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:16">
       <c r="C59" s="1">
-        <v>33112</v>
+        <v>33312</v>
       </c>
       <c r="D59" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E59" s="1">
         <v>10</v>
@@ -16618,68 +16591,24 @@
         <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L59" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M59" s="1">
         <v>0</v>
       </c>
       <c r="N59" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O59" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P59" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:16">
-      <c r="C60" s="1">
-        <v>33112</v>
-      </c>
-      <c r="D60" s="1">
-        <v>4</v>
-      </c>
-      <c r="E60" s="1">
-        <v>10</v>
-      </c>
-      <c r="F60" s="1">
-        <v>10</v>
-      </c>
-      <c r="G60" s="1">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3">
-        <v>3012</v>
-      </c>
-      <c r="I60" s="1">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="L60" s="1">
-        <v>2</v>
-      </c>
-      <c r="M60" s="1">
-        <v>0</v>
-      </c>
-      <c r="N60" s="1">
-        <v>9</v>
-      </c>
-      <c r="O60" s="1">
-        <v>10</v>
-      </c>
-      <c r="P60" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -452,7 +452,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="391">
   <si>
     <t>_ID</t>
   </si>
@@ -1168,22 +1168,10 @@
     <t>增加一行一列范围</t>
   </si>
   <si>
-    <t>火焰墙·废弃</t>
-  </si>
-  <si>
-    <t>此词条废弃了</t>
-  </si>
-  <si>
     <t>烈焰环·大大大</t>
   </si>
   <si>
-    <t>烈焰环·废弃</t>
-  </si>
-  <si>
     <t>冰爆术·大大大</t>
-  </si>
-  <si>
-    <t>冰爆术·废弃</t>
   </si>
   <si>
     <t>火球术·多重</t>
@@ -2927,7 +2915,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>54</v>
@@ -3105,7 +3093,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>54</v>
@@ -3194,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>54</v>
@@ -3283,7 +3271,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>54</v>
@@ -3372,7 +3360,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>74</v>
@@ -3550,7 +3538,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>74</v>
@@ -3639,7 +3627,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>74</v>
@@ -3728,7 +3716,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>74</v>
@@ -3817,7 +3805,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>85</v>
@@ -3995,7 +3983,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>85</v>
@@ -4084,7 +4072,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>85</v>
@@ -4173,7 +4161,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>85</v>
@@ -4262,7 +4250,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>96</v>
@@ -4351,7 +4339,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -4440,7 +4428,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>96</v>
@@ -4529,7 +4517,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>96</v>
@@ -4618,7 +4606,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>96</v>
@@ -4707,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>107</v>
@@ -4796,7 +4784,7 @@
         <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>112</v>
@@ -4885,7 +4873,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>115</v>
@@ -5063,7 +5051,7 @@
         <v>1</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>115</v>
@@ -5152,7 +5140,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>115</v>
@@ -5241,7 +5229,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>115</v>
@@ -5330,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>126</v>
@@ -5508,7 +5496,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>126</v>
@@ -5597,7 +5585,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>126</v>
@@ -5686,7 +5674,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>126</v>
@@ -5775,7 +5763,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>137</v>
@@ -5953,7 +5941,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>137</v>
@@ -6042,7 +6030,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>137</v>
@@ -6131,7 +6119,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>137</v>
@@ -6220,7 +6208,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>148</v>
@@ -6398,7 +6386,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>148</v>
@@ -6487,7 +6475,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>148</v>
@@ -6576,7 +6564,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>148</v>
@@ -6665,7 +6653,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>159</v>
@@ -6843,7 +6831,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>159</v>
@@ -6932,7 +6920,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>159</v>
@@ -7021,7 +7009,7 @@
         <v>1</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>159</v>
@@ -7110,7 +7098,7 @@
         <v>1</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>170</v>
@@ -7199,7 +7187,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>173</v>
@@ -7288,7 +7276,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>176</v>
@@ -7466,7 +7454,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>176</v>
@@ -7555,7 +7543,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>176</v>
@@ -7644,7 +7632,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>176</v>
@@ -7733,7 +7721,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>187</v>
@@ -7822,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>190</v>
@@ -7911,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>193</v>
@@ -8089,7 +8077,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>193</v>
@@ -8178,7 +8166,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>193</v>
@@ -8267,7 +8255,7 @@
         <v>1</v>
       </c>
       <c r="G66" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>193</v>
@@ -8356,7 +8344,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>204</v>
@@ -8445,7 +8433,7 @@
         <v>1</v>
       </c>
       <c r="G68" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>207</v>
@@ -8534,7 +8522,7 @@
         <v>1</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>210</v>
@@ -8623,7 +8611,7 @@
         <v>1</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>213</v>
@@ -9604,7 +9592,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AE34"/>
+  <dimension ref="C3:AE31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -9911,7 +9899,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="1">
         <v>2003</v>
@@ -9985,28 +9973,28 @@
     </row>
     <row r="7" customHeight="1" spans="3:31">
       <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>2004</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>238</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K7" s="1">
         <v>3</v>
@@ -10063,15 +10051,15 @@
         <v>0</v>
       </c>
       <c r="AD7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:31">
       <c r="C8" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -10083,13 +10071,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" s="1">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>237</v>
@@ -10157,10 +10145,10 @@
     </row>
     <row r="9" customHeight="1" spans="3:31">
       <c r="C9" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -10169,16 +10157,16 @@
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>2001</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="K9" s="1">
         <v>3</v>
@@ -10196,13 +10184,13 @@
         <v>0</v>
       </c>
       <c r="Q9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" s="1">
         <v>0</v>
@@ -10235,15 +10223,15 @@
         <v>0</v>
       </c>
       <c r="AD9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:31">
       <c r="C10" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -10255,16 +10243,16 @@
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" s="1">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>242</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K10" s="1">
         <v>3</v>
@@ -10282,10 +10270,10 @@
         <v>0</v>
       </c>
       <c r="Q10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="1">
         <v>1</v>
@@ -10329,10 +10317,10 @@
     </row>
     <row r="11" customHeight="1" spans="3:31">
       <c r="C11" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -10341,16 +10329,16 @@
         <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>243</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K11" s="1">
         <v>3</v>
@@ -10362,7 +10350,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
@@ -10371,10 +10359,10 @@
         <v>0</v>
       </c>
       <c r="R11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" s="1">
         <v>0</v>
@@ -10407,15 +10395,15 @@
         <v>0</v>
       </c>
       <c r="AD11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:31">
       <c r="C12" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -10427,19 +10415,19 @@
         <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" s="1">
-        <v>2001</v>
+        <v>3004</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K12" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -10501,7 +10489,7 @@
     </row>
     <row r="13" customHeight="1" spans="3:31">
       <c r="C13" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -10513,19 +10501,19 @@
         <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" s="1">
-        <v>2002</v>
+        <v>3007</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K13" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" s="1">
         <v>0</v>
@@ -10546,7 +10534,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" s="1">
         <v>0</v>
@@ -10587,7 +10575,7 @@
     </row>
     <row r="14" customHeight="1" spans="3:31">
       <c r="C14" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -10599,16 +10587,16 @@
         <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" s="1">
-        <v>1002</v>
+        <v>2002</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K14" s="1">
         <v>3</v>
@@ -10673,7 +10661,7 @@
     </row>
     <row r="15" customHeight="1" spans="3:31">
       <c r="C15" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -10685,19 +10673,19 @@
         <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" s="1">
-        <v>3004</v>
+        <v>2001</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>250</v>
       </c>
       <c r="K15" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="1">
         <v>0</v>
@@ -10706,13 +10694,13 @@
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="1">
         <v>0</v>
       </c>
       <c r="Q15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="1">
         <v>0</v>
@@ -10759,7 +10747,7 @@
     </row>
     <row r="16" customHeight="1" spans="3:31">
       <c r="C16" s="1">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -10771,19 +10759,19 @@
         <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1">
-        <v>3007</v>
+        <v>1005</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K16" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>
@@ -10795,10 +10783,10 @@
         <v>0</v>
       </c>
       <c r="P16" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="1">
         <v>0</v>
@@ -10845,7 +10833,7 @@
     </row>
     <row r="17" customHeight="1" spans="3:31">
       <c r="C17" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -10857,16 +10845,16 @@
         <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" s="1">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="K17" s="1">
         <v>3</v>
@@ -10878,10 +10866,10 @@
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q17" s="1">
         <v>0</v>
@@ -10931,7 +10919,7 @@
     </row>
     <row r="18" customHeight="1" spans="3:31">
       <c r="C18" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -10943,16 +10931,16 @@
         <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" s="1">
-        <v>2001</v>
+        <v>3005</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>255</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K18" s="1">
         <v>3</v>
@@ -10964,10 +10952,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q18" s="1">
         <v>0</v>
@@ -11017,7 +11005,7 @@
     </row>
     <row r="19" customHeight="1" spans="3:31">
       <c r="C19" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
@@ -11029,10 +11017,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" s="1">
-        <v>1005</v>
+        <v>3007</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>256</v>
@@ -11053,7 +11041,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="1">
         <v>0</v>
@@ -11089,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="AB19" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC19" s="1">
         <v>0</v>
@@ -11103,7 +11091,7 @@
     </row>
     <row r="20" customHeight="1" spans="3:31">
       <c r="C20" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -11115,19 +11103,19 @@
         <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="1">
-        <v>2005</v>
-      </c>
-      <c r="I20" s="1" t="s">
+        <v>2007</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>258</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K20" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -11139,7 +11127,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="1">
         <v>0</v>
@@ -11165,8 +11153,8 @@
       <c r="X20" s="1">
         <v>0</v>
       </c>
-      <c r="Y20" s="1">
-        <v>0</v>
+      <c r="Y20" s="6">
+        <v>20</v>
       </c>
       <c r="Z20" s="4">
         <v>0</v>
@@ -11189,7 +11177,7 @@
     </row>
     <row r="21" customHeight="1" spans="3:31">
       <c r="C21" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -11201,19 +11189,19 @@
         <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="1">
-        <v>3005</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>259</v>
+        <v>1007</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>260</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K21" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -11225,19 +11213,19 @@
         <v>0</v>
       </c>
       <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="6">
         <v>10</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
-      <c r="S21" s="1">
-        <v>0</v>
-      </c>
-      <c r="T21" s="1">
-        <v>0</v>
       </c>
       <c r="U21" s="1">
         <v>0</v>
@@ -11275,7 +11263,7 @@
     </row>
     <row r="22" customHeight="1" spans="3:31">
       <c r="C22" s="1">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -11287,16 +11275,16 @@
         <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" s="1">
-        <v>3007</v>
+        <v>3002</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="K22" s="1">
         <v>3</v>
@@ -11308,7 +11296,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="1">
         <v>0</v>
@@ -11347,7 +11335,7 @@
         <v>0</v>
       </c>
       <c r="AB22" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="1">
         <v>0</v>
@@ -11361,7 +11349,7 @@
     </row>
     <row r="23" customHeight="1" spans="3:31">
       <c r="C23" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -11373,16 +11361,16 @@
         <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="1">
-        <v>2007</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>262</v>
+        <v>1008</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>263</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K23" s="1">
         <v>4</v>
@@ -11408,8 +11396,8 @@
       <c r="S23" s="1">
         <v>0</v>
       </c>
-      <c r="T23" s="1">
-        <v>0</v>
+      <c r="T23" s="6">
+        <v>10</v>
       </c>
       <c r="U23" s="1">
         <v>0</v>
@@ -11423,8 +11411,8 @@
       <c r="X23" s="1">
         <v>0</v>
       </c>
-      <c r="Y23" s="6">
-        <v>20</v>
+      <c r="Y23" s="1">
+        <v>0</v>
       </c>
       <c r="Z23" s="4">
         <v>0</v>
@@ -11436,7 +11424,7 @@
         <v>0</v>
       </c>
       <c r="AC23" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD23" s="1">
         <v>1</v>
@@ -11447,7 +11435,7 @@
     </row>
     <row r="24" customHeight="1" spans="3:31">
       <c r="C24" s="1">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -11459,16 +11447,16 @@
         <v>1</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" s="1">
-        <v>1007</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>264</v>
+        <v>2008</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>265</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K24" s="1">
         <v>4</v>
@@ -11522,7 +11510,7 @@
         <v>0</v>
       </c>
       <c r="AC24" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD24" s="1">
         <v>1</v>
@@ -11533,7 +11521,7 @@
     </row>
     <row r="25" customHeight="1" spans="3:31">
       <c r="C25" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
@@ -11545,19 +11533,19 @@
         <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" s="1">
-        <v>3002</v>
+        <v>3008</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="K25" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
@@ -11566,7 +11554,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="1">
         <v>0</v>
@@ -11580,8 +11568,8 @@
       <c r="S25" s="1">
         <v>0</v>
       </c>
-      <c r="T25" s="1">
-        <v>0</v>
+      <c r="T25" s="6">
+        <v>10</v>
       </c>
       <c r="U25" s="1">
         <v>0</v>
@@ -11608,7 +11596,7 @@
         <v>0</v>
       </c>
       <c r="AC25" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD25" s="1">
         <v>1</v>
@@ -11619,7 +11607,7 @@
     </row>
     <row r="26" customHeight="1" spans="3:31">
       <c r="C26" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -11631,19 +11619,19 @@
         <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" s="1">
-        <v>1008</v>
+        <v>3002</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>268</v>
+        <v>66</v>
       </c>
       <c r="K26" s="1">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
@@ -11654,6 +11642,9 @@
       <c r="N26" s="1">
         <v>0</v>
       </c>
+      <c r="O26" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="P26" s="1">
         <v>0</v>
       </c>
@@ -11666,8 +11657,8 @@
       <c r="S26" s="1">
         <v>0</v>
       </c>
-      <c r="T26" s="6">
-        <v>10</v>
+      <c r="T26" s="1">
+        <v>0</v>
       </c>
       <c r="U26" s="1">
         <v>0</v>
@@ -11676,7 +11667,7 @@
         <v>0</v>
       </c>
       <c r="W26" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X26" s="1">
         <v>0</v>
@@ -11694,7 +11685,7 @@
         <v>0</v>
       </c>
       <c r="AC26" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="1">
         <v>1</v>
@@ -11705,7 +11696,7 @@
     </row>
     <row r="27" customHeight="1" spans="3:31">
       <c r="C27" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
@@ -11717,19 +11708,19 @@
         <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27" s="1">
-        <v>2008</v>
+        <v>3002</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>270</v>
+        <v>69</v>
       </c>
       <c r="K27" s="1">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="L27" s="1">
         <v>0</v>
@@ -11740,6 +11731,9 @@
       <c r="N27" s="1">
         <v>0</v>
       </c>
+      <c r="O27" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="P27" s="1">
         <v>0</v>
       </c>
@@ -11752,8 +11746,8 @@
       <c r="S27" s="1">
         <v>0</v>
       </c>
-      <c r="T27" s="6">
-        <v>10</v>
+      <c r="T27" s="1">
+        <v>0</v>
       </c>
       <c r="U27" s="1">
         <v>0</v>
@@ -11765,7 +11759,7 @@
         <v>0</v>
       </c>
       <c r="X27" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y27" s="1">
         <v>0</v>
@@ -11780,7 +11774,7 @@
         <v>0</v>
       </c>
       <c r="AC27" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD27" s="1">
         <v>1</v>
@@ -11791,7 +11785,7 @@
     </row>
     <row r="28" customHeight="1" spans="3:31">
       <c r="C28" s="1">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
@@ -11803,10 +11797,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="1">
-        <v>3008</v>
+        <v>1009</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>271</v>
@@ -11815,10 +11809,10 @@
         <v>272</v>
       </c>
       <c r="K28" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L28" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M28" s="1">
         <v>0</v>
@@ -11838,8 +11832,8 @@
       <c r="S28" s="1">
         <v>0</v>
       </c>
-      <c r="T28" s="6">
-        <v>10</v>
+      <c r="T28" s="1">
+        <v>0</v>
       </c>
       <c r="U28" s="1">
         <v>0</v>
@@ -11866,7 +11860,7 @@
         <v>0</v>
       </c>
       <c r="AC28" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD28" s="1">
         <v>1</v>
@@ -11877,7 +11871,7 @@
     </row>
     <row r="29" customHeight="1" spans="3:31">
       <c r="C29" s="1">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -11889,19 +11883,19 @@
         <v>1</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" s="1">
-        <v>3002</v>
+        <v>2009</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>273</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>66</v>
+        <v>274</v>
       </c>
       <c r="K29" s="1">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="L29" s="1">
         <v>0</v>
@@ -11912,9 +11906,6 @@
       <c r="N29" s="1">
         <v>0</v>
       </c>
-      <c r="O29" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="P29" s="1">
         <v>0</v>
       </c>
@@ -11922,10 +11913,10 @@
         <v>0</v>
       </c>
       <c r="R29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" s="1">
         <v>0</v>
@@ -11937,7 +11928,7 @@
         <v>0</v>
       </c>
       <c r="W29" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="X29" s="1">
         <v>0</v>
@@ -11966,7 +11957,7 @@
     </row>
     <row r="30" customHeight="1" spans="3:31">
       <c r="C30" s="1">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
@@ -11978,19 +11969,19 @@
         <v>1</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30" s="1">
-        <v>3002</v>
+        <v>3009</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>69</v>
+        <v>276</v>
       </c>
       <c r="K30" s="1">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="L30" s="1">
         <v>0</v>
@@ -12001,9 +11992,6 @@
       <c r="N30" s="1">
         <v>0</v>
       </c>
-      <c r="O30" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="P30" s="1">
         <v>0</v>
       </c>
@@ -12017,7 +12005,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U30" s="1">
         <v>0</v>
@@ -12029,7 +12017,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="1">
         <v>0</v>
@@ -12055,7 +12043,7 @@
     </row>
     <row r="31" customHeight="1" spans="3:31">
       <c r="C31" s="1">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
@@ -12067,22 +12055,22 @@
         <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31" s="1">
-        <v>1009</v>
+        <v>3002</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>276</v>
+        <v>72</v>
       </c>
       <c r="K31" s="1">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="L31" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M31" s="1">
         <v>0</v>
@@ -12090,6 +12078,9 @@
       <c r="N31" s="1">
         <v>0</v>
       </c>
+      <c r="O31" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="P31" s="1">
         <v>0</v>
       </c>
@@ -12118,7 +12109,7 @@
         <v>0</v>
       </c>
       <c r="Y31" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z31" s="4">
         <v>0</v>
@@ -12136,267 +12127,6 @@
         <v>1</v>
       </c>
       <c r="AE31" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:31">
-      <c r="C32" s="1">
-        <v>27</v>
-      </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1">
-        <v>2009</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1">
-        <v>0</v>
-      </c>
-      <c r="N32" s="1">
-        <v>0</v>
-      </c>
-      <c r="P32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="1">
-        <v>0</v>
-      </c>
-      <c r="R32" s="1">
-        <v>1</v>
-      </c>
-      <c r="S32" s="1">
-        <v>1</v>
-      </c>
-      <c r="T32" s="1">
-        <v>0</v>
-      </c>
-      <c r="U32" s="1">
-        <v>0</v>
-      </c>
-      <c r="V32" s="1">
-        <v>0</v>
-      </c>
-      <c r="W32" s="1">
-        <v>0</v>
-      </c>
-      <c r="X32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE32" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:31">
-      <c r="C33" s="1">
-        <v>28</v>
-      </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1">
-        <v>3009</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="K33" s="1">
-        <v>2</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0</v>
-      </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
-      <c r="N33" s="1">
-        <v>0</v>
-      </c>
-      <c r="P33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>0</v>
-      </c>
-      <c r="R33" s="1">
-        <v>0</v>
-      </c>
-      <c r="S33" s="1">
-        <v>0</v>
-      </c>
-      <c r="T33" s="1">
-        <v>50</v>
-      </c>
-      <c r="U33" s="1">
-        <v>0</v>
-      </c>
-      <c r="V33" s="1">
-        <v>0</v>
-      </c>
-      <c r="W33" s="1">
-        <v>0</v>
-      </c>
-      <c r="X33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE33" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:31">
-      <c r="C34" s="1">
-        <v>29</v>
-      </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1">
-        <v>3002</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K34" s="1">
-        <v>99</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
-      <c r="N34" s="1">
-        <v>0</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P34" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="1">
-        <v>0</v>
-      </c>
-      <c r="R34" s="1">
-        <v>0</v>
-      </c>
-      <c r="S34" s="1">
-        <v>0</v>
-      </c>
-      <c r="T34" s="1">
-        <v>0</v>
-      </c>
-      <c r="U34" s="1">
-        <v>0</v>
-      </c>
-      <c r="V34" s="1">
-        <v>0</v>
-      </c>
-      <c r="W34" s="1">
-        <v>0</v>
-      </c>
-      <c r="X34" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="1">
-        <v>20</v>
-      </c>
-      <c r="Z34" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE34" s="1">
         <v>5</v>
       </c>
     </row>
@@ -12452,19 +12182,19 @@
         <v>4</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>6</v>
@@ -12509,7 +12239,7 @@
         <v>33</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>6</v>
@@ -12590,10 +12320,10 @@
         <v>1001</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K6" s="1">
         <v>10</v>
@@ -12629,10 +12359,10 @@
         <v>1002</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K7" s="1">
         <v>10</v>
@@ -12668,10 +12398,10 @@
         <v>1003</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K8" s="1">
         <v>10</v>
@@ -12706,10 +12436,10 @@
         <v>1004</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K9" s="1">
         <v>10</v>
@@ -12744,10 +12474,10 @@
         <v>1005</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K10" s="1">
         <v>8</v>
@@ -12782,10 +12512,10 @@
         <v>1006</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K11" s="1">
         <v>8</v>
@@ -12820,10 +12550,10 @@
         <v>1007</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K12" s="1">
         <v>8</v>
@@ -12858,10 +12588,10 @@
         <v>1008</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K13" s="1">
         <v>8</v>
@@ -12896,10 +12626,10 @@
         <v>1009</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K14" s="1">
         <v>6</v>
@@ -12934,10 +12664,10 @@
         <v>1010</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K15" s="1">
         <v>6</v>
@@ -12972,10 +12702,10 @@
         <v>2001</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K17" s="1">
         <v>10</v>
@@ -13010,10 +12740,10 @@
         <v>2002</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K18" s="1">
         <v>10</v>
@@ -13048,10 +12778,10 @@
         <v>2003</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K19" s="1">
         <v>10</v>
@@ -13086,10 +12816,10 @@
         <v>2004</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K20" s="1">
         <v>10</v>
@@ -13124,10 +12854,10 @@
         <v>2005</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K21" s="1">
         <v>8</v>
@@ -13162,10 +12892,10 @@
         <v>2006</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K22" s="1">
         <v>8</v>
@@ -13200,10 +12930,10 @@
         <v>2007</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K23" s="1">
         <v>8</v>
@@ -13238,10 +12968,10 @@
         <v>2008</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K24" s="1">
         <v>8</v>
@@ -13276,10 +13006,10 @@
         <v>2009</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K25" s="1">
         <v>6</v>
@@ -13314,10 +13044,10 @@
         <v>2010</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K26" s="1">
         <v>6</v>
@@ -13352,10 +13082,10 @@
         <v>3001</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K28" s="1">
         <v>10</v>
@@ -13390,10 +13120,10 @@
         <v>3002</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K29" s="1">
         <v>10</v>
@@ -13428,10 +13158,10 @@
         <v>3003</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K30" s="1">
         <v>10</v>
@@ -13466,10 +13196,10 @@
         <v>3004</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K31" s="1">
         <v>10</v>
@@ -13504,10 +13234,10 @@
         <v>3005</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K32" s="1">
         <v>8</v>
@@ -13542,10 +13272,10 @@
         <v>3006</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K33" s="1">
         <v>8</v>
@@ -13580,10 +13310,10 @@
         <v>3007</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K34" s="1">
         <v>8</v>
@@ -13618,10 +13348,10 @@
         <v>3008</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K35" s="1">
         <v>8</v>
@@ -13656,10 +13386,10 @@
         <v>3009</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K36" s="1">
         <v>6</v>
@@ -13694,10 +13424,10 @@
         <v>3010</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K37" s="1">
         <v>6</v>
@@ -13764,22 +13494,22 @@
         <v>4</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>6</v>
@@ -13815,7 +13545,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>31</v>
@@ -13827,7 +13557,7 @@
         <v>33</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>6</v>
@@ -13914,10 +13644,10 @@
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="L6" s="1">
         <v>5</v>
@@ -13956,10 +13686,10 @@
         <v>2</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="L7" s="1">
         <v>5</v>
@@ -13998,10 +13728,10 @@
         <v>3</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="L8" s="1">
         <v>5</v>
@@ -14039,10 +13769,10 @@
         <v>4</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="L9" s="1">
         <v>5</v>
@@ -14080,10 +13810,10 @@
         <v>5</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -14121,10 +13851,10 @@
         <v>6</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -14162,10 +13892,10 @@
         <v>7</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="L12" s="1">
         <v>4</v>
@@ -14203,10 +13933,10 @@
         <v>8</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="L13" s="1">
         <v>3</v>
@@ -14244,10 +13974,10 @@
         <v>9</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="L14" s="1">
         <v>3</v>
@@ -14285,10 +14015,10 @@
         <v>10</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L15" s="1">
         <v>3</v>
@@ -14326,10 +14056,10 @@
         <v>11</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="L16" s="1">
         <v>2</v>
@@ -14396,22 +14126,22 @@
         <v>4</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>6</v>
@@ -14449,7 +14179,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>31</v>
@@ -14461,7 +14191,7 @@
         <v>33</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>6</v>
@@ -14552,10 +14282,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L6" s="1">
         <v>6</v>
@@ -14564,7 +14294,7 @@
         <v>15</v>
       </c>
       <c r="N6" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O6" s="1">
         <v>9</v>
@@ -14597,10 +14327,10 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L7" s="1">
         <v>6</v>
@@ -14609,7 +14339,7 @@
         <v>15</v>
       </c>
       <c r="N7" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O7" s="1">
         <v>9</v>
@@ -14642,10 +14372,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L8" s="1">
         <v>6</v>
@@ -14654,7 +14384,7 @@
         <v>15</v>
       </c>
       <c r="N8" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O8" s="1">
         <v>9</v>
@@ -14686,10 +14416,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L9" s="1">
         <v>6</v>
@@ -14698,7 +14428,7 @@
         <v>15</v>
       </c>
       <c r="N9" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O9" s="1">
         <v>9</v>
@@ -14730,10 +14460,10 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L10" s="1">
         <v>6</v>
@@ -14742,7 +14472,7 @@
         <v>15</v>
       </c>
       <c r="N10" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O10" s="1">
         <v>9</v>
@@ -14774,10 +14504,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L11" s="1">
         <v>6</v>
@@ -14786,7 +14516,7 @@
         <v>15</v>
       </c>
       <c r="N11" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O11" s="1">
         <v>9</v>
@@ -14818,10 +14548,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L12" s="1">
         <v>6</v>
@@ -14830,7 +14560,7 @@
         <v>15</v>
       </c>
       <c r="N12" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O12" s="1">
         <v>9</v>
@@ -14862,10 +14592,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L13" s="1">
         <v>6</v>
@@ -14874,7 +14604,7 @@
         <v>15</v>
       </c>
       <c r="N13" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O13" s="1">
         <v>9</v>
@@ -14906,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L14" s="1">
         <v>6</v>
@@ -14918,7 +14648,7 @@
         <v>15</v>
       </c>
       <c r="N14" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O14" s="1">
         <v>9</v>
@@ -14950,10 +14680,10 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L15" s="1">
         <v>6</v>
@@ -14962,7 +14692,7 @@
         <v>15</v>
       </c>
       <c r="N15" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O15" s="1">
         <v>9</v>
@@ -14994,10 +14724,10 @@
         <v>0</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L16" s="1">
         <v>6</v>
@@ -15006,7 +14736,7 @@
         <v>15</v>
       </c>
       <c r="N16" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O16" s="1">
         <v>9</v>
@@ -15038,10 +14768,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L17" s="1">
         <v>4</v>
@@ -15050,7 +14780,7 @@
         <v>10</v>
       </c>
       <c r="N17" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O17" s="1">
         <v>9</v>
@@ -15082,10 +14812,10 @@
         <v>0</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="L18" s="1">
         <v>2</v>
@@ -15094,7 +14824,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O18" s="1">
         <v>9</v>
@@ -15126,10 +14856,10 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="L19" s="1">
         <v>3</v>
@@ -15138,7 +14868,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O19" s="1">
         <v>9</v>
@@ -15174,10 +14904,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="L21" s="1">
         <v>6</v>
@@ -15186,7 +14916,7 @@
         <v>15</v>
       </c>
       <c r="N21" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O21" s="1">
         <v>9</v>
@@ -15218,10 +14948,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="L22" s="1">
         <v>4</v>
@@ -15230,7 +14960,7 @@
         <v>15</v>
       </c>
       <c r="N22" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O22" s="1">
         <v>9</v>
@@ -15262,10 +14992,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="L23" s="1">
         <v>4</v>
@@ -15274,7 +15004,7 @@
         <v>10</v>
       </c>
       <c r="N23" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O23" s="1">
         <v>9</v>
@@ -15315,10 +15045,10 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L26" s="1">
         <v>6</v>
@@ -15327,7 +15057,7 @@
         <v>15</v>
       </c>
       <c r="N26" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O26" s="1">
         <v>9</v>
@@ -15359,10 +15089,10 @@
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L27" s="1">
         <v>6</v>
@@ -15371,7 +15101,7 @@
         <v>15</v>
       </c>
       <c r="N27" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O27" s="1">
         <v>9</v>
@@ -15403,10 +15133,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L28" s="1">
         <v>6</v>
@@ -15415,7 +15145,7 @@
         <v>15</v>
       </c>
       <c r="N28" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O28" s="1">
         <v>9</v>
@@ -15447,10 +15177,10 @@
         <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L29" s="1">
         <v>6</v>
@@ -15459,7 +15189,7 @@
         <v>15</v>
       </c>
       <c r="N29" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O29" s="1">
         <v>9</v>
@@ -15491,10 +15221,10 @@
         <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L30" s="1">
         <v>6</v>
@@ -15503,7 +15233,7 @@
         <v>15</v>
       </c>
       <c r="N30" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O30" s="1">
         <v>9</v>
@@ -15535,10 +15265,10 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L31" s="1">
         <v>6</v>
@@ -15547,7 +15277,7 @@
         <v>15</v>
       </c>
       <c r="N31" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O31" s="1">
         <v>9</v>
@@ -15579,10 +15309,10 @@
         <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
@@ -15591,7 +15321,7 @@
         <v>15</v>
       </c>
       <c r="N32" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O32" s="1">
         <v>9</v>
@@ -15623,10 +15353,10 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
@@ -15635,7 +15365,7 @@
         <v>15</v>
       </c>
       <c r="N33" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O33" s="1">
         <v>9</v>
@@ -15667,10 +15397,10 @@
         <v>0</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
@@ -15679,7 +15409,7 @@
         <v>15</v>
       </c>
       <c r="N34" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O34" s="1">
         <v>9</v>
@@ -15711,10 +15441,10 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L35" s="1">
         <v>6</v>
@@ -15723,7 +15453,7 @@
         <v>15</v>
       </c>
       <c r="N35" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O35" s="1">
         <v>9</v>
@@ -15755,10 +15485,10 @@
         <v>0</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
@@ -15767,7 +15497,7 @@
         <v>15</v>
       </c>
       <c r="N36" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O36" s="1">
         <v>9</v>
@@ -15799,10 +15529,10 @@
         <v>0</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L37" s="1">
         <v>4</v>
@@ -15811,7 +15541,7 @@
         <v>10</v>
       </c>
       <c r="N37" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O37" s="1">
         <v>9</v>
@@ -15847,10 +15577,10 @@
         <v>0</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="L39" s="1">
         <v>5</v>
@@ -15859,7 +15589,7 @@
         <v>0</v>
       </c>
       <c r="N39" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O39" s="1">
         <v>9</v>
@@ -15888,10 +15618,10 @@
         <v>2008</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="L40" s="1">
         <v>3</v>
@@ -15900,7 +15630,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O40" s="1">
         <v>9</v>
@@ -15937,10 +15667,10 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L43" s="1">
         <v>6</v>
@@ -15949,10 +15679,10 @@
         <v>15</v>
       </c>
       <c r="N43" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O43" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P43" s="1">
         <v>0</v>
@@ -15981,10 +15711,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
@@ -15993,10 +15723,10 @@
         <v>15</v>
       </c>
       <c r="N44" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O44" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P44" s="1">
         <v>0</v>
@@ -16025,10 +15755,10 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L45" s="1">
         <v>6</v>
@@ -16037,10 +15767,10 @@
         <v>15</v>
       </c>
       <c r="N45" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O45" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P45" s="1">
         <v>0</v>
@@ -16069,10 +15799,10 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L46" s="1">
         <v>6</v>
@@ -16081,10 +15811,10 @@
         <v>15</v>
       </c>
       <c r="N46" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O46" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P46" s="1">
         <v>0</v>
@@ -16113,10 +15843,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L47" s="1">
         <v>6</v>
@@ -16125,10 +15855,10 @@
         <v>15</v>
       </c>
       <c r="N47" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O47" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P47" s="1">
         <v>0</v>
@@ -16157,10 +15887,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L48" s="1">
         <v>6</v>
@@ -16169,10 +15899,10 @@
         <v>15</v>
       </c>
       <c r="N48" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O48" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P48" s="1">
         <v>0</v>
@@ -16201,10 +15931,10 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L49" s="1">
         <v>6</v>
@@ -16213,10 +15943,10 @@
         <v>15</v>
       </c>
       <c r="N49" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O49" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P49" s="1">
         <v>0</v>
@@ -16245,10 +15975,10 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L50" s="1">
         <v>6</v>
@@ -16257,10 +15987,10 @@
         <v>15</v>
       </c>
       <c r="N50" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O50" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P50" s="1">
         <v>0</v>
@@ -16289,10 +16019,10 @@
         <v>0</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L51" s="1">
         <v>6</v>
@@ -16301,10 +16031,10 @@
         <v>15</v>
       </c>
       <c r="N51" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O51" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P51" s="1">
         <v>0</v>
@@ -16333,10 +16063,10 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L52" s="1">
         <v>6</v>
@@ -16345,10 +16075,10 @@
         <v>15</v>
       </c>
       <c r="N52" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O52" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P52" s="1">
         <v>0</v>
@@ -16377,10 +16107,10 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L53" s="1">
         <v>6</v>
@@ -16389,10 +16119,10 @@
         <v>15</v>
       </c>
       <c r="N53" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O53" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P53" s="1">
         <v>0</v>
@@ -16421,10 +16151,10 @@
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L54" s="1">
         <v>4</v>
@@ -16433,10 +16163,10 @@
         <v>10</v>
       </c>
       <c r="N54" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O54" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P54" s="1">
         <v>0</v>
@@ -16465,10 +16195,10 @@
         <v>0</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="L55" s="1">
         <v>2</v>
@@ -16477,16 +16207,16 @@
         <v>0</v>
       </c>
       <c r="N55" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O55" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P55" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C57" s="1">
         <v>33108</v>
       </c>
@@ -16506,10 +16236,10 @@
         <v>3008</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="L57" s="1">
         <v>3</v>
@@ -16518,10 +16248,13 @@
         <v>0</v>
       </c>
       <c r="N57" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O57" s="1">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:16">
@@ -16547,10 +16280,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="L58" s="1">
         <v>4</v>
@@ -16559,10 +16292,10 @@
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O58" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P58" s="1">
         <v>0</v>
@@ -16591,10 +16324,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="L59" s="1">
         <v>4</v>
@@ -16603,10 +16336,10 @@
         <v>0</v>
       </c>
       <c r="N59" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O59" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P59" s="1">
         <v>0</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -452,7 +452,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="395">
   <si>
     <t>_ID</t>
   </si>
@@ -1460,6 +1460,18 @@
   </si>
   <si>
     <t>提高十一阶全系技能系数10%系数增幅</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Miss</t>
   </si>
   <si>
     <t>基础剑术·大师</t>
@@ -9578,7 +9590,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E3 F3 C4:D4 E4 F4 C5:E5 F5 G3:H5 K3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F3 C4:F4 C5:F5 G3:H5 K3:N5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -12132,7 +12144,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 F3 E4 F4 E5 F5 G3:L5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -13444,7 +13456,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 F3 E4 F4 E5 F5 G3:K5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -14076,7 +14088,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 F3 E4 F4 E5 F5 G3:L5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -14152,8 +14164,12 @@
       <c r="P3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
+      <c r="Q3" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>337</v>
+      </c>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
@@ -14202,8 +14218,12 @@
       <c r="P4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
+      <c r="Q4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>339</v>
+      </c>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -14252,8 +14272,12 @@
       <c r="P5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
+      <c r="Q5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -14282,10 +14306,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L6" s="1">
         <v>6</v>
@@ -14300,6 +14324,12 @@
         <v>9</v>
       </c>
       <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
         <v>0</v>
       </c>
       <c r="S6" s="4"/>
@@ -14327,10 +14357,10 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L7" s="1">
         <v>6</v>
@@ -14347,9 +14377,15 @@
       <c r="P7" s="1">
         <v>0</v>
       </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
       <c r="S7" s="4"/>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C8" s="1">
         <v>31003</v>
       </c>
@@ -14372,10 +14408,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L8" s="1">
         <v>6</v>
@@ -14392,8 +14428,14 @@
       <c r="P8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C9" s="1">
         <v>31004</v>
       </c>
@@ -14416,10 +14458,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L9" s="1">
         <v>6</v>
@@ -14436,8 +14478,14 @@
       <c r="P9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C10" s="1">
         <v>31005</v>
       </c>
@@ -14460,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="L10" s="1">
         <v>6</v>
@@ -14480,8 +14528,14 @@
       <c r="P10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C11" s="1">
         <v>31006</v>
       </c>
@@ -14504,10 +14558,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L11" s="1">
         <v>6</v>
@@ -14524,8 +14578,14 @@
       <c r="P11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C12" s="1">
         <v>31007</v>
       </c>
@@ -14548,10 +14608,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L12" s="1">
         <v>6</v>
@@ -14568,8 +14628,14 @@
       <c r="P12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C13" s="1">
         <v>31008</v>
       </c>
@@ -14592,10 +14658,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L13" s="1">
         <v>6</v>
@@ -14612,8 +14678,14 @@
       <c r="P13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C14" s="1">
         <v>31009</v>
       </c>
@@ -14636,10 +14708,10 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L14" s="1">
         <v>6</v>
@@ -14656,8 +14728,14 @@
       <c r="P14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C15" s="1">
         <v>31010</v>
       </c>
@@ -14680,10 +14758,10 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L15" s="1">
         <v>6</v>
@@ -14700,8 +14778,14 @@
       <c r="P15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C16" s="1">
         <v>31011</v>
       </c>
@@ -14724,10 +14808,10 @@
         <v>0</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L16" s="1">
         <v>6</v>
@@ -14744,8 +14828,14 @@
       <c r="P16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:16">
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:18">
       <c r="C17" s="1">
         <v>31012</v>
       </c>
@@ -14768,7 +14858,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>283</v>
@@ -14788,8 +14878,14 @@
       <c r="P17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:16">
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:18">
       <c r="C18" s="1">
         <v>31112</v>
       </c>
@@ -14812,7 +14908,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>250</v>
@@ -14832,8 +14928,14 @@
       <c r="P18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:16">
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:18">
       <c r="C19" s="1">
         <v>31212</v>
       </c>
@@ -14856,7 +14958,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>241</v>
@@ -14874,6 +14976,12 @@
         <v>9</v>
       </c>
       <c r="P19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
         <v>0</v>
       </c>
     </row>
@@ -14881,7 +14989,7 @@
       <c r="H20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C21" s="1">
         <v>31108</v>
       </c>
@@ -14904,10 +15012,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="L21" s="1">
         <v>6</v>
@@ -14924,8 +15032,14 @@
       <c r="P21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C22" s="1">
         <v>31110</v>
       </c>
@@ -14948,10 +15062,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L22" s="1">
         <v>4</v>
@@ -14968,8 +15082,14 @@
       <c r="P22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:16">
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:18">
       <c r="C23" s="1">
         <v>31312</v>
       </c>
@@ -14992,10 +15112,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L23" s="1">
         <v>4</v>
@@ -15012,17 +15132,22 @@
       <c r="P23" s="1">
         <v>0</v>
       </c>
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" customHeight="1" spans="8:10">
       <c r="H24" s="3"/>
-      <c r="I24" s="1"/>
       <c r="J24" s="3"/>
     </row>
     <row r="25" customHeight="1" spans="8:10">
       <c r="H25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" customHeight="1" spans="3:16">
+    <row r="26" customHeight="1" spans="3:18">
       <c r="C26" s="1">
         <v>32001</v>
       </c>
@@ -15045,10 +15170,10 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L26" s="1">
         <v>6</v>
@@ -15065,8 +15190,14 @@
       <c r="P26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:16">
+      <c r="Q26" s="1">
+        <v>0</v>
+      </c>
+      <c r="R26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:18">
       <c r="C27" s="1">
         <v>32002</v>
       </c>
@@ -15089,10 +15220,10 @@
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L27" s="1">
         <v>6</v>
@@ -15109,8 +15240,14 @@
       <c r="P27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:16">
+      <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:18">
       <c r="C28" s="1">
         <v>32003</v>
       </c>
@@ -15133,10 +15270,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L28" s="1">
         <v>6</v>
@@ -15153,8 +15290,14 @@
       <c r="P28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:16">
+      <c r="Q28" s="1">
+        <v>0</v>
+      </c>
+      <c r="R28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:18">
       <c r="C29" s="1">
         <v>32004</v>
       </c>
@@ -15177,10 +15320,10 @@
         <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L29" s="1">
         <v>6</v>
@@ -15197,8 +15340,14 @@
       <c r="P29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:16">
+      <c r="Q29" s="1">
+        <v>0</v>
+      </c>
+      <c r="R29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:18">
       <c r="C30" s="1">
         <v>32005</v>
       </c>
@@ -15221,10 +15370,10 @@
         <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L30" s="1">
         <v>6</v>
@@ -15241,8 +15390,14 @@
       <c r="P30" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:16">
+      <c r="Q30" s="1">
+        <v>0</v>
+      </c>
+      <c r="R30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:18">
       <c r="C31" s="1">
         <v>32006</v>
       </c>
@@ -15265,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L31" s="1">
         <v>6</v>
@@ -15285,8 +15440,14 @@
       <c r="P31" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:16">
+      <c r="Q31" s="1">
+        <v>0</v>
+      </c>
+      <c r="R31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:18">
       <c r="C32" s="1">
         <v>32007</v>
       </c>
@@ -15309,10 +15470,10 @@
         <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
@@ -15329,8 +15490,14 @@
       <c r="P32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:16">
+      <c r="Q32" s="1">
+        <v>0</v>
+      </c>
+      <c r="R32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:18">
       <c r="C33" s="1">
         <v>32008</v>
       </c>
@@ -15353,10 +15520,10 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
@@ -15373,8 +15540,14 @@
       <c r="P33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:16">
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:18">
       <c r="C34" s="1">
         <v>32009</v>
       </c>
@@ -15397,10 +15570,10 @@
         <v>0</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
@@ -15417,8 +15590,14 @@
       <c r="P34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:16">
+      <c r="Q34" s="1">
+        <v>0</v>
+      </c>
+      <c r="R34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:18">
       <c r="C35" s="1">
         <v>32010</v>
       </c>
@@ -15441,10 +15620,10 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L35" s="1">
         <v>6</v>
@@ -15461,8 +15640,14 @@
       <c r="P35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:16">
+      <c r="Q35" s="1">
+        <v>0</v>
+      </c>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:18">
       <c r="C36" s="1">
         <v>32011</v>
       </c>
@@ -15485,10 +15670,10 @@
         <v>0</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
@@ -15505,8 +15690,14 @@
       <c r="P36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:16">
+      <c r="Q36" s="1">
+        <v>0</v>
+      </c>
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:18">
       <c r="C37" s="1">
         <v>32012</v>
       </c>
@@ -15529,7 +15720,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>283</v>
@@ -15547,6 +15738,12 @@
         <v>9</v>
       </c>
       <c r="P37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>0</v>
+      </c>
+      <c r="R37" s="1">
         <v>0</v>
       </c>
     </row>
@@ -15554,7 +15751,7 @@
       <c r="H38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" customHeight="1" spans="3:16">
+    <row r="39" customHeight="1" spans="3:18">
       <c r="C39" s="1">
         <v>32112</v>
       </c>
@@ -15577,10 +15774,10 @@
         <v>0</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="L39" s="1">
         <v>5</v>
@@ -15597,8 +15794,14 @@
       <c r="P39" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="Q39" s="1">
+        <v>0</v>
+      </c>
+      <c r="R39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C40" s="1">
         <v>32108</v>
       </c>
@@ -15618,10 +15821,10 @@
         <v>2008</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="L40" s="1">
         <v>3</v>
@@ -15634,6 +15837,12 @@
       </c>
       <c r="O40" s="1">
         <v>9</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>0</v>
+      </c>
+      <c r="R40" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="8:10">
@@ -15644,7 +15853,7 @@
       <c r="H42" s="3"/>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" customHeight="1" spans="3:16">
+    <row r="43" customHeight="1" spans="3:18">
       <c r="C43" s="1">
         <v>33001</v>
       </c>
@@ -15667,10 +15876,10 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L43" s="1">
         <v>6</v>
@@ -15687,8 +15896,14 @@
       <c r="P43" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:16">
+      <c r="Q43" s="1">
+        <v>0</v>
+      </c>
+      <c r="R43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:18">
       <c r="C44" s="1">
         <v>33002</v>
       </c>
@@ -15711,10 +15926,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
@@ -15731,8 +15946,14 @@
       <c r="P44" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:16">
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:18">
       <c r="C45" s="1">
         <v>33003</v>
       </c>
@@ -15755,10 +15976,10 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L45" s="1">
         <v>6</v>
@@ -15775,8 +15996,14 @@
       <c r="P45" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:16">
+      <c r="Q45" s="1">
+        <v>0</v>
+      </c>
+      <c r="R45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:18">
       <c r="C46" s="1">
         <v>33004</v>
       </c>
@@ -15799,10 +16026,10 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L46" s="1">
         <v>6</v>
@@ -15819,8 +16046,14 @@
       <c r="P46" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:16">
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:18">
       <c r="C47" s="1">
         <v>33005</v>
       </c>
@@ -15843,10 +16076,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L47" s="1">
         <v>6</v>
@@ -15863,8 +16096,14 @@
       <c r="P47" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:16">
+      <c r="Q47" s="1">
+        <v>0</v>
+      </c>
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:18">
       <c r="C48" s="1">
         <v>33006</v>
       </c>
@@ -15887,10 +16126,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L48" s="1">
         <v>6</v>
@@ -15907,8 +16146,14 @@
       <c r="P48" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:16">
+      <c r="Q48" s="1">
+        <v>0</v>
+      </c>
+      <c r="R48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:18">
       <c r="C49" s="1">
         <v>33007</v>
       </c>
@@ -15931,10 +16176,10 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L49" s="1">
         <v>6</v>
@@ -15951,8 +16196,14 @@
       <c r="P49" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:16">
+      <c r="Q49" s="1">
+        <v>0</v>
+      </c>
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:18">
       <c r="C50" s="1">
         <v>33008</v>
       </c>
@@ -15975,10 +16226,10 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L50" s="1">
         <v>6</v>
@@ -15995,8 +16246,14 @@
       <c r="P50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:16">
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:18">
       <c r="C51" s="1">
         <v>33009</v>
       </c>
@@ -16019,10 +16276,10 @@
         <v>0</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L51" s="1">
         <v>6</v>
@@ -16039,8 +16296,14 @@
       <c r="P51" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:16">
+      <c r="Q51" s="1">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:18">
       <c r="C52" s="1">
         <v>33010</v>
       </c>
@@ -16063,10 +16326,10 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L52" s="1">
         <v>6</v>
@@ -16083,8 +16346,14 @@
       <c r="P52" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:16">
+      <c r="Q52" s="1">
+        <v>0</v>
+      </c>
+      <c r="R52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:18">
       <c r="C53" s="1">
         <v>33011</v>
       </c>
@@ -16107,10 +16376,10 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L53" s="1">
         <v>6</v>
@@ -16127,8 +16396,14 @@
       <c r="P53" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:16">
+      <c r="Q53" s="1">
+        <v>0</v>
+      </c>
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:18">
       <c r="C54" s="1">
         <v>33012</v>
       </c>
@@ -16151,7 +16426,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>283</v>
@@ -16171,8 +16446,14 @@
       <c r="P54" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:16">
+      <c r="Q54" s="1">
+        <v>0</v>
+      </c>
+      <c r="R54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:18">
       <c r="C55" s="1">
         <v>33112</v>
       </c>
@@ -16195,10 +16476,10 @@
         <v>0</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="L55" s="1">
         <v>2</v>
@@ -16215,8 +16496,14 @@
       <c r="P55" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q55" s="1">
+        <v>0</v>
+      </c>
+      <c r="R55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C57" s="1">
         <v>33108</v>
       </c>
@@ -16236,10 +16523,10 @@
         <v>3008</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="L57" s="1">
         <v>3</v>
@@ -16256,8 +16543,14 @@
       <c r="P57" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:16">
+      <c r="Q57" s="1">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:18">
       <c r="C58" s="1">
         <v>33212</v>
       </c>
@@ -16280,10 +16573,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="L58" s="1">
         <v>4</v>
@@ -16300,8 +16593,14 @@
       <c r="P58" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:16">
+      <c r="Q58" s="1">
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:18">
       <c r="C59" s="1">
         <v>33312</v>
       </c>
@@ -16324,10 +16623,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="L59" s="1">
         <v>4</v>
@@ -16344,10 +16643,16 @@
       <c r="P59" s="1">
         <v>0</v>
       </c>
+      <c r="Q59" s="1">
+        <v>0</v>
+      </c>
+      <c r="R59" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 F3 E4 F4 E5 F5 G3:G5 H3:H5 I3:I5 J3:J5 C3:D5 K3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -447,12 +447,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="T3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0 以自己为圆心
+1 距离1格</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="394">
   <si>
     <t>_ID</t>
   </si>
@@ -1522,63 +1545,66 @@
     <t>战吼·急速</t>
   </si>
   <si>
+    <t>减少3秒CD时间</t>
+  </si>
+  <si>
+    <t>裂地斩·天目</t>
+  </si>
+  <si>
+    <t>此技能额外增加15%命中</t>
+  </si>
+  <si>
+    <t>剑二十三·天目</t>
+  </si>
+  <si>
+    <t>火球术·大师</t>
+  </si>
+  <si>
+    <t>落雷术·大师</t>
+  </si>
+  <si>
+    <t>火焰墙·大师</t>
+  </si>
+  <si>
+    <t>烈焰环·大师</t>
+  </si>
+  <si>
+    <t>法力盾·大师</t>
+  </si>
+  <si>
+    <t>法术精通·大师</t>
+  </si>
+  <si>
+    <t>冰爆术·大师</t>
+  </si>
+  <si>
+    <t>心灵传送·大师</t>
+  </si>
+  <si>
+    <t>毁灭流星·大师</t>
+  </si>
+  <si>
+    <t>分身术·大师</t>
+  </si>
+  <si>
+    <t>法师之魂·大师</t>
+  </si>
+  <si>
+    <t>魔尊附体·大师</t>
+  </si>
+  <si>
+    <t>魔尊附体·破限</t>
+  </si>
+  <si>
+    <t>增加30层叠加上限</t>
+  </si>
+  <si>
+    <t>心灵传送·急速</t>
+  </si>
+  <si>
     <t>减少3秒持续时间</t>
   </si>
   <si>
-    <t>裂地斩·天目</t>
-  </si>
-  <si>
-    <t>此技能额外增加20点命中</t>
-  </si>
-  <si>
-    <t>剑二十三·天目</t>
-  </si>
-  <si>
-    <t>火球术·大师</t>
-  </si>
-  <si>
-    <t>落雷术·大师</t>
-  </si>
-  <si>
-    <t>火焰墙·大师</t>
-  </si>
-  <si>
-    <t>烈焰环·大师</t>
-  </si>
-  <si>
-    <t>法力盾·大师</t>
-  </si>
-  <si>
-    <t>法术精通·大师</t>
-  </si>
-  <si>
-    <t>冰爆术·大师</t>
-  </si>
-  <si>
-    <t>心灵传送·大师</t>
-  </si>
-  <si>
-    <t>毁灭流星·大师</t>
-  </si>
-  <si>
-    <t>分身术·大师</t>
-  </si>
-  <si>
-    <t>法师之魂·大师</t>
-  </si>
-  <si>
-    <t>魔尊附体·大师</t>
-  </si>
-  <si>
-    <t>魔尊附体·破限</t>
-  </si>
-  <si>
-    <t>增加30层叠加上限</t>
-  </si>
-  <si>
-    <t>心灵传送·急速</t>
-  </si>
-  <si>
     <t>疗伤术·大师</t>
   </si>
   <si>
@@ -1615,12 +1641,6 @@
     <t>召唤白虎·大师</t>
   </si>
   <si>
-    <t>召唤白虎·复制</t>
-  </si>
-  <si>
-    <t>多召唤一只白虎</t>
-  </si>
-  <si>
     <t>隐身道法·急速</t>
   </si>
   <si>
@@ -1630,13 +1650,13 @@
     <t>召唤白虎·天目</t>
   </si>
   <si>
-    <t>白虎额外增加20点命中</t>
+    <t>白虎额外增加15%命中</t>
   </si>
   <si>
     <t>召唤白虎·迷踪</t>
   </si>
   <si>
-    <t>白虎额外增加20点闪避</t>
+    <t>白虎额外增加15%闪避</t>
   </si>
 </sst>
 </file>
@@ -9590,7 +9610,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F3 C4:F4 C5:F5 G3:H5 K3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:N5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -12144,7 +12164,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -13456,7 +13476,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -14088,7 +14108,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -14101,7 +14121,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:V59"/>
+  <dimension ref="C3:U58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -14113,15 +14133,16 @@
     <col min="13" max="13" width="13.25" style="1" customWidth="1"/>
     <col min="14" max="14" width="12.25" style="1" customWidth="1"/>
     <col min="15" max="15" width="13.75" style="1" customWidth="1"/>
-    <col min="16" max="16" width="7.50833333333333" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10.625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.625" style="1" customWidth="1"/>
-    <col min="19" max="21" width="13" style="1" customWidth="1"/>
-    <col min="22" max="22" width="7.375" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="1"/>
+    <col min="16" max="16" width="10.625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.16666666666667" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.58333333333333" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="9.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.66666666666667" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -14162,20 +14183,25 @@
         <v>7</v>
       </c>
       <c r="P3" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:22">
+      <c r="S3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
@@ -14216,20 +14242,25 @@
         <v>7</v>
       </c>
       <c r="P4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:22">
+      <c r="S4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C5" s="2" t="s">
         <v>52</v>
       </c>
@@ -14278,12 +14309,17 @@
       <c r="R5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="S5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C6" s="1">
         <v>31001</v>
       </c>
@@ -14323,18 +14359,8 @@
       <c r="O6" s="1">
         <v>9</v>
       </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4"/>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:19">
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C7" s="1">
         <v>31002</v>
       </c>
@@ -14374,18 +14400,8 @@
       <c r="O7" s="1">
         <v>9</v>
       </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C8" s="1">
         <v>31003</v>
       </c>
@@ -14425,17 +14441,8 @@
       <c r="O8" s="1">
         <v>9</v>
       </c>
-      <c r="P8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C9" s="1">
         <v>31004</v>
       </c>
@@ -14475,17 +14482,8 @@
       <c r="O9" s="1">
         <v>9</v>
       </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C10" s="1">
         <v>31005</v>
       </c>
@@ -14525,17 +14523,8 @@
       <c r="O10" s="1">
         <v>9</v>
       </c>
-      <c r="P10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C11" s="1">
         <v>31006</v>
       </c>
@@ -14575,17 +14564,8 @@
       <c r="O11" s="1">
         <v>9</v>
       </c>
-      <c r="P11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C12" s="1">
         <v>31007</v>
       </c>
@@ -14625,17 +14605,8 @@
       <c r="O12" s="1">
         <v>9</v>
       </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C13" s="1">
         <v>31008</v>
       </c>
@@ -14675,17 +14646,8 @@
       <c r="O13" s="1">
         <v>9</v>
       </c>
-      <c r="P13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C14" s="1">
         <v>31009</v>
       </c>
@@ -14725,17 +14687,8 @@
       <c r="O14" s="1">
         <v>9</v>
       </c>
-      <c r="P14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C15" s="1">
         <v>31010</v>
       </c>
@@ -14775,17 +14728,8 @@
       <c r="O15" s="1">
         <v>9</v>
       </c>
-      <c r="P15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:20">
       <c r="C16" s="1">
         <v>31011</v>
       </c>
@@ -14825,17 +14769,13 @@
       <c r="O16" s="1">
         <v>9</v>
       </c>
-      <c r="P16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>0</v>
-      </c>
-      <c r="R16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:18">
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="4"/>
+    </row>
+    <row r="17" customHeight="1" spans="3:20">
       <c r="C17" s="1">
         <v>31012</v>
       </c>
@@ -14875,17 +14815,13 @@
       <c r="O17" s="1">
         <v>9</v>
       </c>
-      <c r="P17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>0</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:18">
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="4"/>
+    </row>
+    <row r="18" customHeight="1" spans="3:20">
       <c r="C18" s="1">
         <v>31112</v>
       </c>
@@ -14925,17 +14861,15 @@
       <c r="O18" s="1">
         <v>9</v>
       </c>
-      <c r="P18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>0</v>
-      </c>
-      <c r="R18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:18">
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:21">
       <c r="C19" s="1">
         <v>31212</v>
       </c>
@@ -14975,21 +14909,21 @@
       <c r="O19" s="1">
         <v>9</v>
       </c>
-      <c r="P19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>0</v>
-      </c>
-      <c r="R19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="8:10">
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="8:20">
       <c r="H20" s="3"/>
       <c r="J20" s="3"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="T20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:20">
       <c r="C21" s="1">
         <v>31108</v>
       </c>
@@ -15018,10 +14952,10 @@
         <v>356</v>
       </c>
       <c r="L21" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M21" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N21" s="1">
         <v>9</v>
@@ -15029,17 +14963,15 @@
       <c r="O21" s="1">
         <v>9</v>
       </c>
-      <c r="P21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1">
+        <v>3</v>
+      </c>
+      <c r="T21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:20">
       <c r="C22" s="1">
         <v>31110</v>
       </c>
@@ -15071,7 +15003,7 @@
         <v>4</v>
       </c>
       <c r="M22" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N22" s="1">
         <v>9</v>
@@ -15080,16 +15012,14 @@
         <v>9</v>
       </c>
       <c r="P22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>0</v>
-      </c>
-      <c r="R22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:18">
+        <v>15</v>
+      </c>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="4"/>
+    </row>
+    <row r="23" customHeight="1" spans="3:20">
       <c r="C23" s="1">
         <v>31312</v>
       </c>
@@ -15121,7 +15051,7 @@
         <v>4</v>
       </c>
       <c r="M23" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N23" s="1">
         <v>9</v>
@@ -15130,24 +15060,24 @@
         <v>9</v>
       </c>
       <c r="P23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>0</v>
-      </c>
-      <c r="R23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="8:10">
+        <v>15</v>
+      </c>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="4"/>
+    </row>
+    <row r="24" customHeight="1" spans="8:20">
       <c r="H24" s="3"/>
       <c r="J24" s="3"/>
-    </row>
-    <row r="25" customHeight="1" spans="8:10">
+      <c r="T24" s="4"/>
+    </row>
+    <row r="25" customHeight="1" spans="8:20">
       <c r="H25" s="3"/>
       <c r="J25" s="3"/>
-    </row>
-    <row r="26" customHeight="1" spans="3:18">
+      <c r="T25" s="4"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:15">
       <c r="C26" s="1">
         <v>32001</v>
       </c>
@@ -15187,17 +15117,8 @@
       <c r="O26" s="1">
         <v>9</v>
       </c>
-      <c r="P26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>0</v>
-      </c>
-      <c r="R26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:18">
+    </row>
+    <row r="27" customHeight="1" spans="3:15">
       <c r="C27" s="1">
         <v>32002</v>
       </c>
@@ -15237,17 +15158,8 @@
       <c r="O27" s="1">
         <v>9</v>
       </c>
-      <c r="P27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
-      <c r="R27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:18">
+    </row>
+    <row r="28" customHeight="1" spans="3:15">
       <c r="C28" s="1">
         <v>32003</v>
       </c>
@@ -15287,17 +15199,8 @@
       <c r="O28" s="1">
         <v>9</v>
       </c>
-      <c r="P28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="1">
-        <v>0</v>
-      </c>
-      <c r="R28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:18">
+    </row>
+    <row r="29" customHeight="1" spans="3:15">
       <c r="C29" s="1">
         <v>32004</v>
       </c>
@@ -15337,17 +15240,8 @@
       <c r="O29" s="1">
         <v>9</v>
       </c>
-      <c r="P29" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="1">
-        <v>0</v>
-      </c>
-      <c r="R29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:18">
+    </row>
+    <row r="30" customHeight="1" spans="3:15">
       <c r="C30" s="1">
         <v>32005</v>
       </c>
@@ -15387,17 +15281,8 @@
       <c r="O30" s="1">
         <v>9</v>
       </c>
-      <c r="P30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="1">
-        <v>0</v>
-      </c>
-      <c r="R30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:18">
+    </row>
+    <row r="31" customHeight="1" spans="3:15">
       <c r="C31" s="1">
         <v>32006</v>
       </c>
@@ -15437,17 +15322,8 @@
       <c r="O31" s="1">
         <v>9</v>
       </c>
-      <c r="P31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="1">
-        <v>0</v>
-      </c>
-      <c r="R31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:18">
+    </row>
+    <row r="32" customHeight="1" spans="3:15">
       <c r="C32" s="1">
         <v>32007</v>
       </c>
@@ -15487,17 +15363,8 @@
       <c r="O32" s="1">
         <v>9</v>
       </c>
-      <c r="P32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="1">
-        <v>0</v>
-      </c>
-      <c r="R32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:18">
+    </row>
+    <row r="33" customHeight="1" spans="3:15">
       <c r="C33" s="1">
         <v>32008</v>
       </c>
@@ -15537,17 +15404,8 @@
       <c r="O33" s="1">
         <v>9</v>
       </c>
-      <c r="P33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>0</v>
-      </c>
-      <c r="R33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:18">
+    </row>
+    <row r="34" customHeight="1" spans="3:15">
       <c r="C34" s="1">
         <v>32009</v>
       </c>
@@ -15587,17 +15445,8 @@
       <c r="O34" s="1">
         <v>9</v>
       </c>
-      <c r="P34" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="1">
-        <v>0</v>
-      </c>
-      <c r="R34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:18">
+    </row>
+    <row r="35" customHeight="1" spans="3:15">
       <c r="C35" s="1">
         <v>32010</v>
       </c>
@@ -15637,17 +15486,8 @@
       <c r="O35" s="1">
         <v>9</v>
       </c>
-      <c r="P35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>0</v>
-      </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:18">
+    </row>
+    <row r="36" customHeight="1" spans="3:15">
       <c r="C36" s="1">
         <v>32011</v>
       </c>
@@ -15687,17 +15527,8 @@
       <c r="O36" s="1">
         <v>9</v>
       </c>
-      <c r="P36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>0</v>
-      </c>
-      <c r="R36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:18">
+    </row>
+    <row r="37" customHeight="1" spans="3:15">
       <c r="C37" s="1">
         <v>32012</v>
       </c>
@@ -15736,15 +15567,6 @@
       </c>
       <c r="O37" s="1">
         <v>9</v>
-      </c>
-      <c r="P37" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>0</v>
-      </c>
-      <c r="R37" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="8:10">
@@ -15791,17 +15613,13 @@
       <c r="O39" s="1">
         <v>9</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1">
         <v>30</v>
       </c>
-      <c r="Q39" s="1">
-        <v>0</v>
-      </c>
-      <c r="R39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:18">
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:19">
       <c r="C40" s="1">
         <v>32108</v>
       </c>
@@ -15824,7 +15642,7 @@
         <v>374</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="L40" s="1">
         <v>3</v>
@@ -15838,11 +15656,10 @@
       <c r="O40" s="1">
         <v>9</v>
       </c>
-      <c r="Q40" s="1">
-        <v>0</v>
-      </c>
-      <c r="R40" s="1">
-        <v>0</v>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="S40" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="8:10">
@@ -15853,7 +15670,7 @@
       <c r="H42" s="3"/>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" customHeight="1" spans="3:18">
+    <row r="43" customHeight="1" spans="3:15">
       <c r="C43" s="1">
         <v>33001</v>
       </c>
@@ -15876,7 +15693,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>341</v>
@@ -15893,17 +15710,8 @@
       <c r="O43" s="1">
         <v>9</v>
       </c>
-      <c r="P43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="1">
-        <v>0</v>
-      </c>
-      <c r="R43" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:18">
+    </row>
+    <row r="44" customHeight="1" spans="3:15">
       <c r="C44" s="1">
         <v>33002</v>
       </c>
@@ -15926,7 +15734,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>341</v>
@@ -15943,17 +15751,8 @@
       <c r="O44" s="1">
         <v>9</v>
       </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:18">
+    </row>
+    <row r="45" customHeight="1" spans="3:15">
       <c r="C45" s="1">
         <v>33003</v>
       </c>
@@ -15976,7 +15775,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>341</v>
@@ -15993,17 +15792,8 @@
       <c r="O45" s="1">
         <v>9</v>
       </c>
-      <c r="P45" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="1">
-        <v>0</v>
-      </c>
-      <c r="R45" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:18">
+    </row>
+    <row r="46" customHeight="1" spans="3:15">
       <c r="C46" s="1">
         <v>33004</v>
       </c>
@@ -16026,7 +15816,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>341</v>
@@ -16043,17 +15833,8 @@
       <c r="O46" s="1">
         <v>9</v>
       </c>
-      <c r="P46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>0</v>
-      </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:18">
+    </row>
+    <row r="47" customHeight="1" spans="3:15">
       <c r="C47" s="1">
         <v>33005</v>
       </c>
@@ -16076,7 +15857,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>341</v>
@@ -16093,17 +15874,8 @@
       <c r="O47" s="1">
         <v>9</v>
       </c>
-      <c r="P47" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="1">
-        <v>0</v>
-      </c>
-      <c r="R47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:18">
+    </row>
+    <row r="48" customHeight="1" spans="3:15">
       <c r="C48" s="1">
         <v>33006</v>
       </c>
@@ -16126,7 +15898,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>341</v>
@@ -16143,17 +15915,8 @@
       <c r="O48" s="1">
         <v>9</v>
       </c>
-      <c r="P48" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="1">
-        <v>0</v>
-      </c>
-      <c r="R48" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:18">
+    </row>
+    <row r="49" customHeight="1" spans="3:15">
       <c r="C49" s="1">
         <v>33007</v>
       </c>
@@ -16176,7 +15939,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>341</v>
@@ -16193,17 +15956,8 @@
       <c r="O49" s="1">
         <v>9</v>
       </c>
-      <c r="P49" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="1">
-        <v>0</v>
-      </c>
-      <c r="R49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:18">
+    </row>
+    <row r="50" customHeight="1" spans="3:15">
       <c r="C50" s="1">
         <v>33008</v>
       </c>
@@ -16226,7 +15980,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>341</v>
@@ -16243,17 +15997,8 @@
       <c r="O50" s="1">
         <v>9</v>
       </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="1">
-        <v>0</v>
-      </c>
-      <c r="R50" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:18">
+    </row>
+    <row r="51" customHeight="1" spans="3:15">
       <c r="C51" s="1">
         <v>33009</v>
       </c>
@@ -16276,7 +16021,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>341</v>
@@ -16293,17 +16038,8 @@
       <c r="O51" s="1">
         <v>9</v>
       </c>
-      <c r="P51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="1">
-        <v>0</v>
-      </c>
-      <c r="R51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:18">
+    </row>
+    <row r="52" customHeight="1" spans="3:15">
       <c r="C52" s="1">
         <v>33010</v>
       </c>
@@ -16326,7 +16062,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>341</v>
@@ -16343,17 +16079,8 @@
       <c r="O52" s="1">
         <v>9</v>
       </c>
-      <c r="P52" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="1">
-        <v>0</v>
-      </c>
-      <c r="R52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:18">
+    </row>
+    <row r="53" customHeight="1" spans="3:15">
       <c r="C53" s="1">
         <v>33011</v>
       </c>
@@ -16376,7 +16103,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>341</v>
@@ -16393,17 +16120,8 @@
       <c r="O53" s="1">
         <v>9</v>
       </c>
-      <c r="P53" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="1">
-        <v>0</v>
-      </c>
-      <c r="R53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:18">
+    </row>
+    <row r="54" customHeight="1" spans="3:15">
       <c r="C54" s="1">
         <v>33012</v>
       </c>
@@ -16426,7 +16144,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>283</v>
@@ -16443,69 +16161,55 @@
       <c r="O54" s="1">
         <v>9</v>
       </c>
-      <c r="P54" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="1">
-        <v>0</v>
-      </c>
-      <c r="R54" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:18">
-      <c r="C55" s="1">
-        <v>33112</v>
-      </c>
-      <c r="D55" s="1">
+    </row>
+    <row r="55" customFormat="1" customHeight="1"/>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C56" s="1">
+        <v>33108</v>
+      </c>
+      <c r="D56" s="1">
         <v>5</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E56" s="1">
         <v>10</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F56" s="1">
         <v>10</v>
       </c>
-      <c r="G55" s="1">
+      <c r="G56" s="1">
         <v>3</v>
       </c>
-      <c r="H55" s="3">
-        <v>3012</v>
-      </c>
-      <c r="I55" s="1">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="K55" s="1" t="s">
+      <c r="H56" s="3">
+        <v>3008</v>
+      </c>
+      <c r="J56" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="L55" s="1">
-        <v>2</v>
-      </c>
-      <c r="M55" s="1">
-        <v>0</v>
-      </c>
-      <c r="N55" s="1">
+      <c r="K56" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="L56" s="1">
+        <v>3</v>
+      </c>
+      <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
         <v>9</v>
       </c>
-      <c r="O55" s="1">
+      <c r="O56" s="1">
         <v>9</v>
       </c>
-      <c r="P55" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="1">
-        <v>0</v>
-      </c>
-      <c r="R55" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
+      <c r="S56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:16">
       <c r="C57" s="1">
-        <v>33108</v>
+        <v>33212</v>
       </c>
       <c r="D57" s="1">
         <v>5</v>
@@ -16520,16 +16224,19 @@
         <v>3</v>
       </c>
       <c r="H57" s="3">
-        <v>3008</v>
+        <v>3012</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L57" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M57" s="1">
         <v>0</v>
@@ -16541,18 +16248,12 @@
         <v>9</v>
       </c>
       <c r="P57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:17">
       <c r="C58" s="1">
-        <v>33212</v>
+        <v>33312</v>
       </c>
       <c r="D58" s="1">
         <v>5</v>
@@ -16573,10 +16274,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L58" s="1">
         <v>4</v>
@@ -16590,69 +16291,14 @@
       <c r="O58" s="1">
         <v>9</v>
       </c>
-      <c r="P58" s="1">
-        <v>0</v>
-      </c>
+      <c r="P58" s="1"/>
       <c r="Q58" s="1">
-        <v>0</v>
-      </c>
-      <c r="R58" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:18">
-      <c r="C59" s="1">
-        <v>33312</v>
-      </c>
-      <c r="D59" s="1">
-        <v>5</v>
-      </c>
-      <c r="E59" s="1">
-        <v>10</v>
-      </c>
-      <c r="F59" s="1">
-        <v>10</v>
-      </c>
-      <c r="G59" s="1">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3012</v>
-      </c>
-      <c r="I59" s="1">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="L59" s="1">
-        <v>4</v>
-      </c>
-      <c r="M59" s="1">
-        <v>0</v>
-      </c>
-      <c r="N59" s="1">
-        <v>9</v>
-      </c>
-      <c r="O59" s="1">
-        <v>9</v>
-      </c>
-      <c r="P59" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="1">
-        <v>0</v>
-      </c>
-      <c r="R59" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 C3:D5 E4:F5 G3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="S3:S5 C3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -14354,7 +14354,7 @@
         <v>15</v>
       </c>
       <c r="N6" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O6" s="1">
         <v>9</v>
@@ -14395,7 +14395,7 @@
         <v>15</v>
       </c>
       <c r="N7" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O7" s="1">
         <v>9</v>
@@ -14436,7 +14436,7 @@
         <v>15</v>
       </c>
       <c r="N8" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O8" s="1">
         <v>9</v>
@@ -14477,7 +14477,7 @@
         <v>15</v>
       </c>
       <c r="N9" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O9" s="1">
         <v>9</v>
@@ -14518,7 +14518,7 @@
         <v>15</v>
       </c>
       <c r="N10" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O10" s="1">
         <v>9</v>
@@ -14559,7 +14559,7 @@
         <v>15</v>
       </c>
       <c r="N11" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O11" s="1">
         <v>9</v>
@@ -14600,7 +14600,7 @@
         <v>15</v>
       </c>
       <c r="N12" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O12" s="1">
         <v>9</v>
@@ -14641,7 +14641,7 @@
         <v>15</v>
       </c>
       <c r="N13" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O13" s="1">
         <v>9</v>
@@ -14682,7 +14682,7 @@
         <v>15</v>
       </c>
       <c r="N14" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O14" s="1">
         <v>9</v>
@@ -14723,7 +14723,7 @@
         <v>15</v>
       </c>
       <c r="N15" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O15" s="1">
         <v>9</v>
@@ -14764,7 +14764,7 @@
         <v>15</v>
       </c>
       <c r="N16" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O16" s="1">
         <v>9</v>
@@ -14810,15 +14810,11 @@
         <v>10</v>
       </c>
       <c r="N17" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O17" s="1">
         <v>9</v>
       </c>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
       <c r="T17" s="4"/>
     </row>
     <row r="18" customHeight="1" spans="3:20">
@@ -14856,15 +14852,11 @@
         <v>0</v>
       </c>
       <c r="N18" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O18" s="1">
         <v>9</v>
       </c>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
       <c r="T18" s="4">
         <v>1</v>
       </c>
@@ -14904,15 +14896,11 @@
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O19" s="1">
         <v>9</v>
       </c>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
       <c r="T19" s="4"/>
       <c r="U19" s="1">
         <v>1</v>
@@ -14958,7 +14946,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O21" s="1">
         <v>9</v>
@@ -15006,7 +14994,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O22" s="1">
         <v>9</v>
@@ -15054,7 +15042,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O23" s="1">
         <v>9</v>
@@ -15062,9 +15050,6 @@
       <c r="P23" s="1">
         <v>15</v>
       </c>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
       <c r="T23" s="4"/>
     </row>
     <row r="24" customHeight="1" spans="8:20">
@@ -15112,7 +15097,7 @@
         <v>15</v>
       </c>
       <c r="N26" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O26" s="1">
         <v>9</v>
@@ -15153,7 +15138,7 @@
         <v>15</v>
       </c>
       <c r="N27" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O27" s="1">
         <v>9</v>
@@ -15194,7 +15179,7 @@
         <v>15</v>
       </c>
       <c r="N28" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O28" s="1">
         <v>9</v>
@@ -15235,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="N29" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O29" s="1">
         <v>9</v>
@@ -15276,7 +15261,7 @@
         <v>15</v>
       </c>
       <c r="N30" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O30" s="1">
         <v>9</v>
@@ -15317,7 +15302,7 @@
         <v>15</v>
       </c>
       <c r="N31" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O31" s="1">
         <v>9</v>
@@ -15358,7 +15343,7 @@
         <v>15</v>
       </c>
       <c r="N32" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O32" s="1">
         <v>9</v>
@@ -15399,7 +15384,7 @@
         <v>15</v>
       </c>
       <c r="N33" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O33" s="1">
         <v>9</v>
@@ -15440,7 +15425,7 @@
         <v>15</v>
       </c>
       <c r="N34" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O34" s="1">
         <v>9</v>
@@ -15481,7 +15466,7 @@
         <v>15</v>
       </c>
       <c r="N35" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O35" s="1">
         <v>9</v>
@@ -15522,7 +15507,7 @@
         <v>15</v>
       </c>
       <c r="N36" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O36" s="1">
         <v>9</v>
@@ -15563,7 +15548,7 @@
         <v>10</v>
       </c>
       <c r="N37" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O37" s="1">
         <v>9</v>
@@ -15608,13 +15593,11 @@
         <v>0</v>
       </c>
       <c r="N39" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O39" s="1">
         <v>9</v>
       </c>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
       <c r="R39" s="1">
         <v>30</v>
       </c>
@@ -15651,7 +15634,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O40" s="1">
         <v>9</v>
@@ -15705,7 +15688,7 @@
         <v>15</v>
       </c>
       <c r="N43" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O43" s="1">
         <v>9</v>
@@ -15746,7 +15729,7 @@
         <v>15</v>
       </c>
       <c r="N44" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O44" s="1">
         <v>9</v>
@@ -15787,7 +15770,7 @@
         <v>15</v>
       </c>
       <c r="N45" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O45" s="1">
         <v>9</v>
@@ -15828,7 +15811,7 @@
         <v>15</v>
       </c>
       <c r="N46" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O46" s="1">
         <v>9</v>
@@ -15869,7 +15852,7 @@
         <v>15</v>
       </c>
       <c r="N47" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O47" s="1">
         <v>9</v>
@@ -15910,7 +15893,7 @@
         <v>15</v>
       </c>
       <c r="N48" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O48" s="1">
         <v>9</v>
@@ -15951,7 +15934,7 @@
         <v>15</v>
       </c>
       <c r="N49" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O49" s="1">
         <v>9</v>
@@ -15992,7 +15975,7 @@
         <v>15</v>
       </c>
       <c r="N50" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O50" s="1">
         <v>9</v>
@@ -16033,7 +16016,7 @@
         <v>15</v>
       </c>
       <c r="N51" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O51" s="1">
         <v>9</v>
@@ -16074,7 +16057,7 @@
         <v>15</v>
       </c>
       <c r="N52" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O52" s="1">
         <v>9</v>
@@ -16115,7 +16098,7 @@
         <v>15</v>
       </c>
       <c r="N53" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O53" s="1">
         <v>9</v>
@@ -16156,7 +16139,7 @@
         <v>10</v>
       </c>
       <c r="N54" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O54" s="1">
         <v>9</v>
@@ -16195,7 +16178,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O56" s="1">
         <v>9</v>
@@ -16242,7 +16225,7 @@
         <v>0</v>
       </c>
       <c r="N57" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O57" s="1">
         <v>9</v>
@@ -16286,12 +16269,11 @@
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O58" s="1">
         <v>9</v>
       </c>
-      <c r="P58" s="1"/>
       <c r="Q58" s="1">
         <v>15</v>
       </c>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -14354,7 +14354,7 @@
         <v>15</v>
       </c>
       <c r="N6" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O6" s="1">
         <v>9</v>
@@ -14395,7 +14395,7 @@
         <v>15</v>
       </c>
       <c r="N7" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O7" s="1">
         <v>9</v>
@@ -14436,7 +14436,7 @@
         <v>15</v>
       </c>
       <c r="N8" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O8" s="1">
         <v>9</v>
@@ -14477,7 +14477,7 @@
         <v>15</v>
       </c>
       <c r="N9" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O9" s="1">
         <v>9</v>
@@ -14518,7 +14518,7 @@
         <v>15</v>
       </c>
       <c r="N10" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O10" s="1">
         <v>9</v>
@@ -14559,7 +14559,7 @@
         <v>15</v>
       </c>
       <c r="N11" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O11" s="1">
         <v>9</v>
@@ -14600,7 +14600,7 @@
         <v>15</v>
       </c>
       <c r="N12" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="1">
         <v>9</v>
@@ -14641,7 +14641,7 @@
         <v>15</v>
       </c>
       <c r="N13" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O13" s="1">
         <v>9</v>
@@ -14682,7 +14682,7 @@
         <v>15</v>
       </c>
       <c r="N14" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O14" s="1">
         <v>9</v>
@@ -14723,7 +14723,7 @@
         <v>15</v>
       </c>
       <c r="N15" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O15" s="1">
         <v>9</v>
@@ -14764,7 +14764,7 @@
         <v>15</v>
       </c>
       <c r="N16" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O16" s="1">
         <v>9</v>
@@ -14810,7 +14810,7 @@
         <v>10</v>
       </c>
       <c r="N17" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O17" s="1">
         <v>9</v>
@@ -14852,7 +14852,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O18" s="1">
         <v>9</v>
@@ -14896,7 +14896,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O19" s="1">
         <v>9</v>
@@ -14946,7 +14946,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O21" s="1">
         <v>9</v>
@@ -14994,7 +14994,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O22" s="1">
         <v>9</v>
@@ -15042,7 +15042,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O23" s="1">
         <v>9</v>
@@ -15097,7 +15097,7 @@
         <v>15</v>
       </c>
       <c r="N26" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O26" s="1">
         <v>9</v>
@@ -15138,7 +15138,7 @@
         <v>15</v>
       </c>
       <c r="N27" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O27" s="1">
         <v>9</v>
@@ -15179,7 +15179,7 @@
         <v>15</v>
       </c>
       <c r="N28" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O28" s="1">
         <v>9</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="N29" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O29" s="1">
         <v>9</v>
@@ -15261,7 +15261,7 @@
         <v>15</v>
       </c>
       <c r="N30" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O30" s="1">
         <v>9</v>
@@ -15302,7 +15302,7 @@
         <v>15</v>
       </c>
       <c r="N31" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O31" s="1">
         <v>9</v>
@@ -15343,7 +15343,7 @@
         <v>15</v>
       </c>
       <c r="N32" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O32" s="1">
         <v>9</v>
@@ -15384,7 +15384,7 @@
         <v>15</v>
       </c>
       <c r="N33" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O33" s="1">
         <v>9</v>
@@ -15425,7 +15425,7 @@
         <v>15</v>
       </c>
       <c r="N34" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O34" s="1">
         <v>9</v>
@@ -15466,7 +15466,7 @@
         <v>15</v>
       </c>
       <c r="N35" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O35" s="1">
         <v>9</v>
@@ -15507,7 +15507,7 @@
         <v>15</v>
       </c>
       <c r="N36" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O36" s="1">
         <v>9</v>
@@ -15548,7 +15548,7 @@
         <v>10</v>
       </c>
       <c r="N37" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O37" s="1">
         <v>9</v>
@@ -15593,7 +15593,7 @@
         <v>0</v>
       </c>
       <c r="N39" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O39" s="1">
         <v>9</v>
@@ -15634,7 +15634,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O40" s="1">
         <v>9</v>
@@ -15688,7 +15688,7 @@
         <v>15</v>
       </c>
       <c r="N43" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O43" s="1">
         <v>9</v>
@@ -15729,7 +15729,7 @@
         <v>15</v>
       </c>
       <c r="N44" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O44" s="1">
         <v>9</v>
@@ -15770,7 +15770,7 @@
         <v>15</v>
       </c>
       <c r="N45" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O45" s="1">
         <v>9</v>
@@ -15811,7 +15811,7 @@
         <v>15</v>
       </c>
       <c r="N46" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O46" s="1">
         <v>9</v>
@@ -15852,7 +15852,7 @@
         <v>15</v>
       </c>
       <c r="N47" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O47" s="1">
         <v>9</v>
@@ -15893,7 +15893,7 @@
         <v>15</v>
       </c>
       <c r="N48" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O48" s="1">
         <v>9</v>
@@ -15934,7 +15934,7 @@
         <v>15</v>
       </c>
       <c r="N49" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O49" s="1">
         <v>9</v>
@@ -15975,7 +15975,7 @@
         <v>15</v>
       </c>
       <c r="N50" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O50" s="1">
         <v>9</v>
@@ -16016,7 +16016,7 @@
         <v>15</v>
       </c>
       <c r="N51" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O51" s="1">
         <v>9</v>
@@ -16057,7 +16057,7 @@
         <v>15</v>
       </c>
       <c r="N52" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O52" s="1">
         <v>9</v>
@@ -16098,7 +16098,7 @@
         <v>15</v>
       </c>
       <c r="N53" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O53" s="1">
         <v>9</v>
@@ -16139,7 +16139,7 @@
         <v>10</v>
       </c>
       <c r="N54" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O54" s="1">
         <v>9</v>
@@ -16178,7 +16178,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O56" s="1">
         <v>9</v>
@@ -16225,7 +16225,7 @@
         <v>0</v>
       </c>
       <c r="N57" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O57" s="1">
         <v>9</v>
@@ -16269,7 +16269,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O58" s="1">
         <v>9</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -14327,7 +14327,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F6" s="1">
         <v>500</v>
@@ -14409,7 +14409,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F8" s="1">
         <v>500</v>
@@ -14450,7 +14450,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F9" s="1">
         <v>500</v>
@@ -14491,7 +14491,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F10" s="1">
         <v>50</v>
@@ -14532,7 +14532,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F11" s="1">
         <v>50</v>
@@ -14573,7 +14573,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F12" s="1">
         <v>500</v>
@@ -14614,7 +14614,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F13" s="1">
         <v>20</v>
@@ -14655,7 +14655,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F14" s="1">
         <v>30</v>
@@ -14696,7 +14696,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
@@ -14737,7 +14737,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F16" s="1">
         <v>10</v>
@@ -14783,7 +14783,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F17" s="1">
         <v>10</v>
@@ -14825,7 +14825,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F18" s="1">
         <v>10</v>
@@ -14869,7 +14869,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F19" s="1">
         <v>10</v>
@@ -14919,7 +14919,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F21" s="1">
         <v>20</v>
@@ -14967,7 +14967,7 @@
         <v>5</v>
       </c>
       <c r="E22" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F22" s="1">
         <v>10</v>
@@ -15015,7 +15015,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F23" s="1">
         <v>10</v>
@@ -15070,7 +15070,7 @@
         <v>5</v>
       </c>
       <c r="E26" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F26" s="1">
         <v>500</v>
@@ -15152,7 +15152,7 @@
         <v>5</v>
       </c>
       <c r="E28" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F28" s="1">
         <v>500</v>
@@ -15193,7 +15193,7 @@
         <v>5</v>
       </c>
       <c r="E29" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F29" s="1">
         <v>500</v>
@@ -15234,7 +15234,7 @@
         <v>5</v>
       </c>
       <c r="E30" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F30" s="1">
         <v>50</v>
@@ -15275,7 +15275,7 @@
         <v>5</v>
       </c>
       <c r="E31" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F31" s="1">
         <v>50</v>
@@ -15316,7 +15316,7 @@
         <v>5</v>
       </c>
       <c r="E32" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F32" s="1">
         <v>500</v>
@@ -15357,7 +15357,7 @@
         <v>5</v>
       </c>
       <c r="E33" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F33" s="1">
         <v>20</v>
@@ -15398,7 +15398,7 @@
         <v>5</v>
       </c>
       <c r="E34" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F34" s="1">
         <v>30</v>
@@ -15439,7 +15439,7 @@
         <v>5</v>
       </c>
       <c r="E35" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F35" s="1">
         <v>10</v>
@@ -15480,7 +15480,7 @@
         <v>5</v>
       </c>
       <c r="E36" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F36" s="1">
         <v>10</v>
@@ -15521,7 +15521,7 @@
         <v>5</v>
       </c>
       <c r="E37" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F37" s="1">
         <v>10</v>
@@ -15566,7 +15566,7 @@
         <v>5</v>
       </c>
       <c r="E39" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F39" s="1">
         <v>10</v>
@@ -15610,7 +15610,7 @@
         <v>5</v>
       </c>
       <c r="E40" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F40" s="1">
         <v>10</v>
@@ -15661,7 +15661,7 @@
         <v>5</v>
       </c>
       <c r="E43" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F43" s="1">
         <v>500</v>
@@ -15743,7 +15743,7 @@
         <v>5</v>
       </c>
       <c r="E45" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F45" s="1">
         <v>500</v>
@@ -15784,7 +15784,7 @@
         <v>5</v>
       </c>
       <c r="E46" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F46" s="1">
         <v>500</v>
@@ -15825,7 +15825,7 @@
         <v>5</v>
       </c>
       <c r="E47" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F47" s="1">
         <v>50</v>
@@ -15866,7 +15866,7 @@
         <v>5</v>
       </c>
       <c r="E48" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F48" s="1">
         <v>50</v>
@@ -15907,7 +15907,7 @@
         <v>5</v>
       </c>
       <c r="E49" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F49" s="1">
         <v>500</v>
@@ -15948,7 +15948,7 @@
         <v>5</v>
       </c>
       <c r="E50" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F50" s="1">
         <v>20</v>
@@ -15989,7 +15989,7 @@
         <v>5</v>
       </c>
       <c r="E51" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F51" s="1">
         <v>30</v>
@@ -16030,7 +16030,7 @@
         <v>5</v>
       </c>
       <c r="E52" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F52" s="1">
         <v>10</v>
@@ -16071,7 +16071,7 @@
         <v>5</v>
       </c>
       <c r="E53" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F53" s="1">
         <v>10</v>
@@ -16112,7 +16112,7 @@
         <v>5</v>
       </c>
       <c r="E54" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F54" s="1">
         <v>10</v>
@@ -16154,7 +16154,7 @@
         <v>5</v>
       </c>
       <c r="E56" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F56" s="1">
         <v>10</v>
@@ -16198,7 +16198,7 @@
         <v>5</v>
       </c>
       <c r="E57" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F57" s="1">
         <v>10</v>
@@ -16242,7 +16242,7 @@
         <v>5</v>
       </c>
       <c r="E58" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F58" s="1">
         <v>10</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -475,7 +475,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="393">
   <si>
     <t>_ID</t>
   </si>
@@ -1602,9 +1602,6 @@
     <t>心灵传送·急速</t>
   </si>
   <si>
-    <t>减少3秒持续时间</t>
-  </si>
-  <si>
     <t>疗伤术·大师</t>
   </si>
   <si>
@@ -1644,7 +1641,7 @@
     <t>隐身道法·急速</t>
   </si>
   <si>
-    <t>减少1秒持续时间</t>
+    <t>减少1秒CD时间</t>
   </si>
   <si>
     <t>召唤白虎·天目</t>
@@ -15625,7 +15622,7 @@
         <v>374</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="L40" s="1">
         <v>3</v>
@@ -15676,7 +15673,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>341</v>
@@ -15717,7 +15714,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>341</v>
@@ -15758,7 +15755,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>341</v>
@@ -15799,7 +15796,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>341</v>
@@ -15840,7 +15837,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>341</v>
@@ -15881,7 +15878,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>341</v>
@@ -15922,7 +15919,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>341</v>
@@ -15963,7 +15960,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>341</v>
@@ -16004,7 +16001,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>341</v>
@@ -16045,7 +16042,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>341</v>
@@ -16086,7 +16083,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>341</v>
@@ -16127,7 +16124,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>283</v>
@@ -16166,10 +16163,10 @@
         <v>3008</v>
       </c>
       <c r="J56" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="L56" s="1">
         <v>3</v>
@@ -16213,10 +16210,10 @@
         <v>0</v>
       </c>
       <c r="J57" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="L57" s="1">
         <v>4</v>
@@ -16257,10 +16254,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>393</v>
       </c>
       <c r="L58" s="1">
         <v>4</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -2841,7 +2841,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="3:31">
+    <row r="5" ht="14" spans="3:31">
       <c r="C5" s="2" t="s">
         <v>52</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>98</v>
       </c>
       <c r="D22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -1838,12 +1838,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -12364,7 +12364,7 @@
         <v>6</v>
       </c>
       <c r="N6" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R6" s="4"/>
     </row>
@@ -12403,7 +12403,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R7" s="4"/>
     </row>
@@ -12442,7 +12442,7 @@
         <v>6</v>
       </c>
       <c r="N8" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:14">
@@ -12480,7 +12480,7 @@
         <v>6</v>
       </c>
       <c r="N9" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:14">
@@ -12518,7 +12518,7 @@
         <v>6</v>
       </c>
       <c r="N10" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:14">
@@ -12556,7 +12556,7 @@
         <v>6</v>
       </c>
       <c r="N11" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:14">
@@ -12594,7 +12594,7 @@
         <v>6</v>
       </c>
       <c r="N12" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:14">
@@ -12746,7 +12746,7 @@
         <v>6</v>
       </c>
       <c r="N17" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:14">
@@ -12784,7 +12784,7 @@
         <v>6</v>
       </c>
       <c r="N18" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:14">
@@ -12822,7 +12822,7 @@
         <v>6</v>
       </c>
       <c r="N19" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:14">
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="N20" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:14">
@@ -12898,7 +12898,7 @@
         <v>6</v>
       </c>
       <c r="N21" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:14">
@@ -12936,7 +12936,7 @@
         <v>6</v>
       </c>
       <c r="N22" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:14">
@@ -12974,7 +12974,7 @@
         <v>6</v>
       </c>
       <c r="N23" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:14">
@@ -13126,7 +13126,7 @@
         <v>6</v>
       </c>
       <c r="N28" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:14">
@@ -13164,7 +13164,7 @@
         <v>6</v>
       </c>
       <c r="N29" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:14">
@@ -13202,7 +13202,7 @@
         <v>6</v>
       </c>
       <c r="N30" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:14">
@@ -13240,7 +13240,7 @@
         <v>6</v>
       </c>
       <c r="N31" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:14">
@@ -13278,7 +13278,7 @@
         <v>6</v>
       </c>
       <c r="N32" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:14">
@@ -13316,7 +13316,7 @@
         <v>6</v>
       </c>
       <c r="N33" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:14">
@@ -13354,7 +13354,7 @@
         <v>6</v>
       </c>
       <c r="N34" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:14">
@@ -13661,7 +13661,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="1">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -13685,10 +13685,10 @@
         <v>10</v>
       </c>
       <c r="N6" s="1">
+        <v>7</v>
+      </c>
+      <c r="O6" s="1">
         <v>8</v>
-      </c>
-      <c r="O6" s="1">
-        <v>9</v>
       </c>
       <c r="S6" s="4"/>
     </row>
@@ -13703,7 +13703,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -13727,10 +13727,10 @@
         <v>10</v>
       </c>
       <c r="N7" s="1">
+        <v>7</v>
+      </c>
+      <c r="O7" s="1">
         <v>8</v>
-      </c>
-      <c r="O7" s="1">
-        <v>9</v>
       </c>
       <c r="S7" s="4"/>
     </row>
@@ -13745,7 +13745,7 @@
         <v>200</v>
       </c>
       <c r="F8" s="1">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -13769,10 +13769,10 @@
         <v>10</v>
       </c>
       <c r="N8" s="1">
+        <v>7</v>
+      </c>
+      <c r="O8" s="1">
         <v>8</v>
-      </c>
-      <c r="O8" s="1">
-        <v>9</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -13786,7 +13786,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="1">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -13810,10 +13810,10 @@
         <v>10</v>
       </c>
       <c r="N9" s="1">
+        <v>7</v>
+      </c>
+      <c r="O9" s="1">
         <v>8</v>
-      </c>
-      <c r="O9" s="1">
-        <v>9</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -13827,7 +13827,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -13851,10 +13851,10 @@
         <v>10</v>
       </c>
       <c r="N10" s="1">
+        <v>7</v>
+      </c>
+      <c r="O10" s="1">
         <v>8</v>
-      </c>
-      <c r="O10" s="1">
-        <v>9</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -13868,7 +13868,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -13892,10 +13892,10 @@
         <v>10</v>
       </c>
       <c r="N11" s="1">
+        <v>7</v>
+      </c>
+      <c r="O11" s="1">
         <v>8</v>
-      </c>
-      <c r="O11" s="1">
-        <v>9</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -13909,7 +13909,7 @@
         <v>200</v>
       </c>
       <c r="F12" s="1">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -13933,10 +13933,10 @@
         <v>10</v>
       </c>
       <c r="N12" s="1">
+        <v>7</v>
+      </c>
+      <c r="O12" s="1">
         <v>8</v>
-      </c>
-      <c r="O12" s="1">
-        <v>9</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -13950,7 +13950,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -13974,10 +13974,10 @@
         <v>10</v>
       </c>
       <c r="N13" s="1">
+        <v>7</v>
+      </c>
+      <c r="O13" s="1">
         <v>8</v>
-      </c>
-      <c r="O13" s="1">
-        <v>9</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -13991,7 +13991,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="1">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -14015,10 +14015,10 @@
         <v>10</v>
       </c>
       <c r="N14" s="1">
+        <v>7</v>
+      </c>
+      <c r="O14" s="1">
         <v>8</v>
-      </c>
-      <c r="O14" s="1">
-        <v>9</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -14032,7 +14032,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -14056,10 +14056,10 @@
         <v>10</v>
       </c>
       <c r="N15" s="1">
+        <v>7</v>
+      </c>
+      <c r="O15" s="1">
         <v>8</v>
-      </c>
-      <c r="O15" s="1">
-        <v>9</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -14073,7 +14073,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -14097,10 +14097,10 @@
         <v>10</v>
       </c>
       <c r="N16" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O16" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -1838,12 +1838,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -13685,7 +13685,7 @@
         <v>10</v>
       </c>
       <c r="N6" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O6" s="1">
         <v>8</v>
@@ -13703,7 +13703,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -13727,7 +13727,7 @@
         <v>10</v>
       </c>
       <c r="N7" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O7" s="1">
         <v>8</v>
@@ -13769,7 +13769,7 @@
         <v>10</v>
       </c>
       <c r="N8" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O8" s="1">
         <v>8</v>
@@ -13810,7 +13810,7 @@
         <v>10</v>
       </c>
       <c r="N9" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O9" s="1">
         <v>8</v>
@@ -13827,7 +13827,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -13851,7 +13851,7 @@
         <v>10</v>
       </c>
       <c r="N10" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O10" s="1">
         <v>8</v>
@@ -13892,7 +13892,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O11" s="1">
         <v>8</v>
@@ -13933,7 +13933,7 @@
         <v>10</v>
       </c>
       <c r="N12" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O12" s="1">
         <v>8</v>
@@ -13950,7 +13950,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -13974,7 +13974,7 @@
         <v>10</v>
       </c>
       <c r="N13" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O13" s="1">
         <v>8</v>
@@ -13991,7 +13991,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -14015,7 +14015,7 @@
         <v>10</v>
       </c>
       <c r="N14" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O14" s="1">
         <v>8</v>
@@ -14056,7 +14056,7 @@
         <v>10</v>
       </c>
       <c r="N15" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O15" s="1">
         <v>8</v>
@@ -14073,7 +14073,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -14097,7 +14097,7 @@
         <v>10</v>
       </c>
       <c r="N16" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O16" s="1">
         <v>8</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -13703,7 +13703,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -13827,7 +13827,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -13868,7 +13868,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -14032,7 +14032,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -12608,7 +12608,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -12684,7 +12684,7 @@
         <v>20</v>
       </c>
       <c r="F15" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -12988,7 +12988,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G24" s="1">
         <v>2</v>
@@ -13064,7 +13064,7 @@
         <v>20</v>
       </c>
       <c r="F26" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
         <v>2</v>
@@ -13368,7 +13368,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G35" s="1">
         <v>3</v>
@@ -13444,7 +13444,7 @@
         <v>20</v>
       </c>
       <c r="F37" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G37" s="1">
         <v>3</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -12329,7 +12329,7 @@
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C6" s="1">
         <v>11001</v>
       </c>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C7" s="1">
         <v>11002</v>
       </c>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="R7" s="4"/>
     </row>
-    <row r="8" customHeight="1" spans="3:14">
+    <row r="8" customHeight="1" spans="3:21">
       <c r="C8" s="1">
         <v>11003</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:14">
+    <row r="9" customHeight="1" spans="3:21">
       <c r="C9" s="1">
         <v>11004</v>
       </c>
@@ -12483,7 +12483,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:14">
+    <row r="10" customHeight="1" spans="3:21">
       <c r="C10" s="1">
         <v>11005</v>
       </c>
@@ -12521,7 +12521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:14">
+    <row r="11" customHeight="1" spans="3:21">
       <c r="C11" s="1">
         <v>11006</v>
       </c>
@@ -12559,7 +12559,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:14">
+    <row r="12" customHeight="1" spans="3:21">
       <c r="C12" s="1">
         <v>11007</v>
       </c>
@@ -12597,7 +12597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:14">
+    <row r="13" customHeight="1" spans="3:21">
       <c r="C13" s="1">
         <v>11008</v>
       </c>
@@ -12635,7 +12635,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:14">
+    <row r="14" customHeight="1" spans="3:21">
       <c r="C14" s="1">
         <v>11009</v>
       </c>
@@ -12673,7 +12673,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:14">
+    <row r="15" customHeight="1" spans="3:21">
       <c r="C15" s="1">
         <v>11010</v>
       </c>
@@ -13650,7 +13650,7 @@
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:19">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C6" s="1">
         <v>21001</v>
       </c>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="S6" s="4"/>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:19">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C7" s="1">
         <v>21002</v>
       </c>
@@ -13734,7 +13734,7 @@
       </c>
       <c r="S7" s="4"/>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C8" s="1">
         <v>21003</v>
       </c>
@@ -13775,7 +13775,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C9" s="1">
         <v>21004</v>
       </c>
@@ -13816,7 +13816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C10" s="1">
         <v>21005</v>
       </c>
@@ -13857,7 +13857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C11" s="1">
         <v>21006</v>
       </c>
@@ -13898,7 +13898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C12" s="1">
         <v>21007</v>
       </c>
@@ -13939,7 +13939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C13" s="1">
         <v>21008</v>
       </c>
@@ -13980,7 +13980,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C14" s="1">
         <v>21009</v>
       </c>
@@ -14021,7 +14021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C15" s="1">
         <v>21010</v>
       </c>
@@ -14062,7 +14062,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C16" s="1">
         <v>21011</v>
       </c>
@@ -14316,7 +14316,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C6" s="1">
         <v>31001</v>
       </c>
@@ -14357,7 +14357,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C7" s="1">
         <v>31002</v>
       </c>
@@ -14368,7 +14368,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -14398,7 +14398,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C8" s="1">
         <v>31003</v>
       </c>
@@ -14439,7 +14439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C9" s="1">
         <v>31004</v>
       </c>
@@ -14480,7 +14480,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C10" s="1">
         <v>31005</v>
       </c>
@@ -14491,7 +14491,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -14521,7 +14521,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C11" s="1">
         <v>31006</v>
       </c>
@@ -14532,7 +14532,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -14562,7 +14562,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C12" s="1">
         <v>31007</v>
       </c>
@@ -14603,7 +14603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C13" s="1">
         <v>31008</v>
       </c>
@@ -14614,7 +14614,7 @@
         <v>100</v>
       </c>
       <c r="F13" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -14644,7 +14644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C14" s="1">
         <v>31009</v>
       </c>
@@ -14655,7 +14655,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="1">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -14685,7 +14685,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C15" s="1">
         <v>31010</v>
       </c>
@@ -14696,7 +14696,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -14726,7 +14726,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:20">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C16" s="1">
         <v>31011</v>
       </c>
@@ -14737,7 +14737,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -14772,7 +14772,7 @@
       <c r="S16" s="1"/>
       <c r="T16" s="4"/>
     </row>
-    <row r="17" customHeight="1" spans="3:20">
+    <row r="17" customHeight="1" spans="3:21">
       <c r="C17" s="1">
         <v>31012</v>
       </c>
@@ -14783,7 +14783,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -14814,7 +14814,7 @@
       </c>
       <c r="T17" s="4"/>
     </row>
-    <row r="18" customHeight="1" spans="3:20">
+    <row r="18" customHeight="1" spans="3:21">
       <c r="C18" s="1">
         <v>31112</v>
       </c>
@@ -14825,7 +14825,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -14869,7 +14869,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -14903,12 +14903,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="8:20">
+    <row r="20" customHeight="1" spans="3:21">
       <c r="H20" s="3"/>
       <c r="J20" s="3"/>
       <c r="T20" s="4"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:20">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C21" s="1">
         <v>31108</v>
       </c>
@@ -14919,7 +14919,7 @@
         <v>30</v>
       </c>
       <c r="F21" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="T21" s="4"/>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:20">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C22" s="1">
         <v>31110</v>
       </c>
@@ -14967,7 +14967,7 @@
         <v>30</v>
       </c>
       <c r="F22" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -15004,7 +15004,7 @@
       <c r="S22" s="1"/>
       <c r="T22" s="4"/>
     </row>
-    <row r="23" customHeight="1" spans="3:20">
+    <row r="23" customHeight="1" spans="3:21">
       <c r="C23" s="1">
         <v>31312</v>
       </c>
@@ -15015,7 +15015,7 @@
         <v>30</v>
       </c>
       <c r="F23" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -15049,17 +15049,17 @@
       </c>
       <c r="T23" s="4"/>
     </row>
-    <row r="24" customHeight="1" spans="8:20">
+    <row r="24" customHeight="1" spans="3:21">
       <c r="H24" s="3"/>
       <c r="J24" s="3"/>
       <c r="T24" s="4"/>
     </row>
-    <row r="25" customHeight="1" spans="8:20">
+    <row r="25" customHeight="1" spans="3:21">
       <c r="H25" s="3"/>
       <c r="J25" s="3"/>
       <c r="T25" s="4"/>
     </row>
-    <row r="26" customHeight="1" spans="3:15">
+    <row r="26" customHeight="1" spans="3:21">
       <c r="C26" s="1">
         <v>32001</v>
       </c>
@@ -15100,7 +15100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="3:15">
+    <row r="27" customHeight="1" spans="3:21">
       <c r="C27" s="1">
         <v>32002</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>100</v>
       </c>
       <c r="F27" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G27" s="1">
         <v>2</v>
@@ -15141,7 +15141,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="3:15">
+    <row r="28" customHeight="1" spans="3:21">
       <c r="C28" s="1">
         <v>32003</v>
       </c>
@@ -15182,7 +15182,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:15">
+    <row r="29" customHeight="1" spans="3:21">
       <c r="C29" s="1">
         <v>32004</v>
       </c>
@@ -15223,7 +15223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:15">
+    <row r="30" customHeight="1" spans="3:21">
       <c r="C30" s="1">
         <v>32005</v>
       </c>
@@ -15234,7 +15234,7 @@
         <v>100</v>
       </c>
       <c r="F30" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G30" s="1">
         <v>2</v>
@@ -15264,7 +15264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="3:15">
+    <row r="31" customHeight="1" spans="3:21">
       <c r="C31" s="1">
         <v>32006</v>
       </c>
@@ -15275,7 +15275,7 @@
         <v>100</v>
       </c>
       <c r="F31" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G31" s="1">
         <v>2</v>
@@ -15305,7 +15305,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:15">
+    <row r="32" customHeight="1" spans="3:21">
       <c r="C32" s="1">
         <v>32007</v>
       </c>
@@ -15346,7 +15346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="3:15">
+    <row r="33" customHeight="1" spans="3:19">
       <c r="C33" s="1">
         <v>32008</v>
       </c>
@@ -15357,7 +15357,7 @@
         <v>100</v>
       </c>
       <c r="F33" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
         <v>2</v>
@@ -15387,7 +15387,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="3:15">
+    <row r="34" customHeight="1" spans="3:19">
       <c r="C34" s="1">
         <v>32009</v>
       </c>
@@ -15398,7 +15398,7 @@
         <v>100</v>
       </c>
       <c r="F34" s="1">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="G34" s="1">
         <v>2</v>
@@ -15428,7 +15428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="3:15">
+    <row r="35" customHeight="1" spans="3:19">
       <c r="C35" s="1">
         <v>32010</v>
       </c>
@@ -15439,7 +15439,7 @@
         <v>100</v>
       </c>
       <c r="F35" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G35" s="1">
         <v>2</v>
@@ -15469,7 +15469,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="3:15">
+    <row r="36" customHeight="1" spans="3:19">
       <c r="C36" s="1">
         <v>32011</v>
       </c>
@@ -15480,7 +15480,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
@@ -15510,7 +15510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="3:15">
+    <row r="37" customHeight="1" spans="3:19">
       <c r="C37" s="1">
         <v>32012</v>
       </c>
@@ -15521,7 +15521,7 @@
         <v>50</v>
       </c>
       <c r="F37" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G37" s="1">
         <v>2</v>
@@ -15551,11 +15551,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="8:10">
+    <row r="38" customHeight="1" spans="3:19">
       <c r="H38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" customHeight="1" spans="3:18">
+    <row r="39" customHeight="1" spans="3:19">
       <c r="C39" s="1">
         <v>32112</v>
       </c>
@@ -15566,7 +15566,7 @@
         <v>30</v>
       </c>
       <c r="F39" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G39" s="1">
         <v>2</v>
@@ -15610,7 +15610,7 @@
         <v>30</v>
       </c>
       <c r="F40" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -15642,15 +15642,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="8:10">
+    <row r="41" customHeight="1" spans="3:19">
       <c r="H41" s="3"/>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" customHeight="1" spans="8:10">
+    <row r="42" customHeight="1" spans="3:19">
       <c r="H42" s="3"/>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" customHeight="1" spans="3:15">
+    <row r="43" customHeight="1" spans="3:19">
       <c r="C43" s="1">
         <v>33001</v>
       </c>
@@ -15691,7 +15691,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="3:15">
+    <row r="44" customHeight="1" spans="3:19">
       <c r="C44" s="1">
         <v>33002</v>
       </c>
@@ -15702,7 +15702,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G44" s="1">
         <v>3</v>
@@ -15732,7 +15732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="3:15">
+    <row r="45" customHeight="1" spans="3:19">
       <c r="C45" s="1">
         <v>33003</v>
       </c>
@@ -15773,7 +15773,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="3:15">
+    <row r="46" customHeight="1" spans="3:19">
       <c r="C46" s="1">
         <v>33004</v>
       </c>
@@ -15814,7 +15814,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="3:15">
+    <row r="47" customHeight="1" spans="3:19">
       <c r="C47" s="1">
         <v>33005</v>
       </c>
@@ -15825,7 +15825,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G47" s="1">
         <v>3</v>
@@ -15855,7 +15855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="3:15">
+    <row r="48" customHeight="1" spans="3:19">
       <c r="C48" s="1">
         <v>33006</v>
       </c>
@@ -15866,7 +15866,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G48" s="1">
         <v>3</v>
@@ -15896,7 +15896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="3:15">
+    <row r="49" customHeight="1" spans="3:19">
       <c r="C49" s="1">
         <v>33007</v>
       </c>
@@ -15937,7 +15937,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="3:15">
+    <row r="50" customHeight="1" spans="3:19">
       <c r="C50" s="1">
         <v>33008</v>
       </c>
@@ -15948,7 +15948,7 @@
         <v>100</v>
       </c>
       <c r="F50" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G50" s="1">
         <v>3</v>
@@ -15978,7 +15978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="3:15">
+    <row r="51" customHeight="1" spans="3:19">
       <c r="C51" s="1">
         <v>33009</v>
       </c>
@@ -15989,7 +15989,7 @@
         <v>100</v>
       </c>
       <c r="F51" s="1">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -16019,7 +16019,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="3:15">
+    <row r="52" customHeight="1" spans="3:19">
       <c r="C52" s="1">
         <v>33010</v>
       </c>
@@ -16030,7 +16030,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G52" s="1">
         <v>3</v>
@@ -16060,7 +16060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:15">
+    <row r="53" customHeight="1" spans="3:19">
       <c r="C53" s="1">
         <v>33011</v>
       </c>
@@ -16071,7 +16071,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G53" s="1">
         <v>3</v>
@@ -16101,7 +16101,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="3:15">
+    <row r="54" customHeight="1" spans="3:19">
       <c r="C54" s="1">
         <v>33012</v>
       </c>
@@ -16112,7 +16112,7 @@
         <v>50</v>
       </c>
       <c r="F54" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G54" s="1">
         <v>3</v>
@@ -16154,7 +16154,7 @@
         <v>30</v>
       </c>
       <c r="F56" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G56" s="1">
         <v>3</v>
@@ -16187,7 +16187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="3:16">
+    <row r="57" customHeight="1" spans="3:19">
       <c r="C57" s="1">
         <v>33212</v>
       </c>
@@ -16198,7 +16198,7 @@
         <v>30</v>
       </c>
       <c r="F57" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G57" s="1">
         <v>3</v>
@@ -16231,7 +16231,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="3:17">
+    <row r="58" customHeight="1" spans="3:19">
       <c r="C58" s="1">
         <v>33312</v>
       </c>
@@ -16242,7 +16242,7 @@
         <v>30</v>
       </c>
       <c r="F58" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="金装" sheetId="3" r:id="rId3"/>
     <sheet name="暗金" sheetId="4" r:id="rId4"/>
     <sheet name="混沌" sheetId="5" r:id="rId5"/>
+    <sheet name="虚无" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -474,8 +475,86 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+ID* 10 + level
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+攻击力系数（百分比），额外附加固定伤害值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0 以自己为圆心
+1 距离1格</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="428">
   <si>
     <t>_ID</t>
   </si>
@@ -1654,6 +1733,111 @@
   </si>
   <si>
     <t>白虎额外增加15%闪避</t>
+  </si>
+  <si>
+    <t>基础剑术·专家</t>
+  </si>
+  <si>
+    <t>流光剑法·专家</t>
+  </si>
+  <si>
+    <t>旋风斩·专家</t>
+  </si>
+  <si>
+    <t>腾空斩·专家</t>
+  </si>
+  <si>
+    <t>武神盾·专家</t>
+  </si>
+  <si>
+    <t>武力精通·专家</t>
+  </si>
+  <si>
+    <t>烈焰斩·专家</t>
+  </si>
+  <si>
+    <t>战吼·专家</t>
+  </si>
+  <si>
+    <t>裂天斩·专家</t>
+  </si>
+  <si>
+    <t>裂地斩·专家</t>
+  </si>
+  <si>
+    <t>战士之魂·专家</t>
+  </si>
+  <si>
+    <t>火球术·专家</t>
+  </si>
+  <si>
+    <t>落雷术·专家</t>
+  </si>
+  <si>
+    <t>火焰墙·专家</t>
+  </si>
+  <si>
+    <t>烈焰环·专家</t>
+  </si>
+  <si>
+    <t>法力盾·专家</t>
+  </si>
+  <si>
+    <t>法术精通·专家</t>
+  </si>
+  <si>
+    <t>冰爆术·专家</t>
+  </si>
+  <si>
+    <t>心灵传送·专家</t>
+  </si>
+  <si>
+    <t>毁灭流星·专家</t>
+  </si>
+  <si>
+    <t>分身术·专家</t>
+  </si>
+  <si>
+    <t>法师之魂·专家</t>
+  </si>
+  <si>
+    <t>魔尊附体·专家</t>
+  </si>
+  <si>
+    <t>疗伤术·专家</t>
+  </si>
+  <si>
+    <t>驱魔符·专家</t>
+  </si>
+  <si>
+    <t>毒咒术·专家</t>
+  </si>
+  <si>
+    <t>召唤小兵·专家</t>
+  </si>
+  <si>
+    <t>道力盾·专家</t>
+  </si>
+  <si>
+    <t>道力精通·专家</t>
+  </si>
+  <si>
+    <t>召唤魔兽·专家</t>
+  </si>
+  <si>
+    <t>隐身道法·专家</t>
+  </si>
+  <si>
+    <t>召唤月神·专家</t>
+  </si>
+  <si>
+    <t>无极道体·专家</t>
+  </si>
+  <si>
+    <t>道士之魂·专家</t>
+  </si>
+  <si>
+    <t>召唤白虎·专家</t>
   </si>
 </sst>
 </file>
@@ -1838,12 +2022,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -16285,4 +16469,1803 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C3:U58"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="7" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="15.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.16666666666667" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.58333333333333" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="9.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.66666666666667" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C6" s="1">
+        <v>41001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1">
+        <v>300</v>
+      </c>
+      <c r="F6" s="1">
+        <v>500</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1001</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L6" s="1">
+        <v>6</v>
+      </c>
+      <c r="M6" s="1">
+        <v>15</v>
+      </c>
+      <c r="N6" s="1">
+        <v>9</v>
+      </c>
+      <c r="O6" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C7" s="1">
+        <v>41002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1">
+        <v>25</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1002</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L7" s="1">
+        <v>6</v>
+      </c>
+      <c r="M7" s="1">
+        <v>15</v>
+      </c>
+      <c r="N7" s="1">
+        <v>9</v>
+      </c>
+      <c r="O7" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C8" s="1">
+        <v>41003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1">
+        <v>300</v>
+      </c>
+      <c r="F8" s="1">
+        <v>500</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1003</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L8" s="1">
+        <v>6</v>
+      </c>
+      <c r="M8" s="1">
+        <v>15</v>
+      </c>
+      <c r="N8" s="1">
+        <v>9</v>
+      </c>
+      <c r="O8" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C9" s="1">
+        <v>41004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>6</v>
+      </c>
+      <c r="E9" s="1">
+        <v>300</v>
+      </c>
+      <c r="F9" s="1">
+        <v>500</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1004</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L9" s="1">
+        <v>6</v>
+      </c>
+      <c r="M9" s="1">
+        <v>15</v>
+      </c>
+      <c r="N9" s="1">
+        <v>9</v>
+      </c>
+      <c r="O9" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C10" s="1">
+        <v>41005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>6</v>
+      </c>
+      <c r="E10" s="1">
+        <v>100</v>
+      </c>
+      <c r="F10" s="1">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1005</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L10" s="1">
+        <v>6</v>
+      </c>
+      <c r="M10" s="1">
+        <v>15</v>
+      </c>
+      <c r="N10" s="1">
+        <v>9</v>
+      </c>
+      <c r="O10" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C11" s="1">
+        <v>41006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>6</v>
+      </c>
+      <c r="E11" s="1">
+        <v>50</v>
+      </c>
+      <c r="F11" s="1">
+        <v>25</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1006</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L11" s="1">
+        <v>6</v>
+      </c>
+      <c r="M11" s="1">
+        <v>15</v>
+      </c>
+      <c r="N11" s="1">
+        <v>9</v>
+      </c>
+      <c r="O11" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C12" s="1">
+        <v>41007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>6</v>
+      </c>
+      <c r="E12" s="1">
+        <v>300</v>
+      </c>
+      <c r="F12" s="1">
+        <v>500</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1007</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L12" s="1">
+        <v>6</v>
+      </c>
+      <c r="M12" s="1">
+        <v>15</v>
+      </c>
+      <c r="N12" s="1">
+        <v>9</v>
+      </c>
+      <c r="O12" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C13" s="1">
+        <v>41008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>6</v>
+      </c>
+      <c r="E13" s="1">
+        <v>50</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L13" s="1">
+        <v>6</v>
+      </c>
+      <c r="M13" s="1">
+        <v>15</v>
+      </c>
+      <c r="N13" s="1">
+        <v>9</v>
+      </c>
+      <c r="O13" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C14" s="1">
+        <v>41009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>6</v>
+      </c>
+      <c r="E14" s="1">
+        <v>300</v>
+      </c>
+      <c r="F14" s="1">
+        <v>500</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1009</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L14" s="1">
+        <v>6</v>
+      </c>
+      <c r="M14" s="1">
+        <v>15</v>
+      </c>
+      <c r="N14" s="1">
+        <v>9</v>
+      </c>
+      <c r="O14" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C15" s="1">
+        <v>41010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>6</v>
+      </c>
+      <c r="E15" s="1">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1">
+        <v>5</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1010</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L15" s="1">
+        <v>6</v>
+      </c>
+      <c r="M15" s="1">
+        <v>15</v>
+      </c>
+      <c r="N15" s="1">
+        <v>9</v>
+      </c>
+      <c r="O15" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C16" s="1">
+        <v>41011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>6</v>
+      </c>
+      <c r="E16" s="1">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1">
+        <v>5</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1011</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L16" s="1">
+        <v>6</v>
+      </c>
+      <c r="M16" s="1">
+        <v>15</v>
+      </c>
+      <c r="N16" s="1">
+        <v>9</v>
+      </c>
+      <c r="O16" s="1">
+        <v>9</v>
+      </c>
+      <c r="T16" s="4"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C17" s="1">
+        <v>41012</v>
+      </c>
+      <c r="D17" s="1">
+        <v>6</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10</v>
+      </c>
+      <c r="F17" s="1">
+        <v>5</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1012</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="L17" s="1">
+        <v>4</v>
+      </c>
+      <c r="M17" s="1">
+        <v>10</v>
+      </c>
+      <c r="N17" s="1">
+        <v>9</v>
+      </c>
+      <c r="O17" s="1">
+        <v>9</v>
+      </c>
+      <c r="T17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H18" s="3"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="T18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H19" s="3"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="T19" s="4"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="T20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H21" s="3"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="T21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H22" s="3"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="T22" s="4"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H23" s="3"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="T23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="T24" s="4"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="T25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C26" s="1">
+        <v>42001</v>
+      </c>
+      <c r="D26" s="1">
+        <v>6</v>
+      </c>
+      <c r="E26" s="1">
+        <v>300</v>
+      </c>
+      <c r="F26" s="1">
+        <v>500</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2</v>
+      </c>
+      <c r="H26" s="3">
+        <v>2001</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L26" s="1">
+        <v>6</v>
+      </c>
+      <c r="M26" s="1">
+        <v>15</v>
+      </c>
+      <c r="N26" s="1">
+        <v>9</v>
+      </c>
+      <c r="O26" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C27" s="1">
+        <v>42002</v>
+      </c>
+      <c r="D27" s="1">
+        <v>6</v>
+      </c>
+      <c r="E27" s="1">
+        <v>50</v>
+      </c>
+      <c r="F27" s="1">
+        <v>25</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2</v>
+      </c>
+      <c r="H27" s="3">
+        <v>2002</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L27" s="1">
+        <v>6</v>
+      </c>
+      <c r="M27" s="1">
+        <v>15</v>
+      </c>
+      <c r="N27" s="1">
+        <v>9</v>
+      </c>
+      <c r="O27" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C28" s="1">
+        <v>42003</v>
+      </c>
+      <c r="D28" s="1">
+        <v>6</v>
+      </c>
+      <c r="E28" s="1">
+        <v>300</v>
+      </c>
+      <c r="F28" s="1">
+        <v>500</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+      <c r="H28" s="3">
+        <v>2003</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L28" s="1">
+        <v>6</v>
+      </c>
+      <c r="M28" s="1">
+        <v>15</v>
+      </c>
+      <c r="N28" s="1">
+        <v>9</v>
+      </c>
+      <c r="O28" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C29" s="1">
+        <v>42004</v>
+      </c>
+      <c r="D29" s="1">
+        <v>6</v>
+      </c>
+      <c r="E29" s="1">
+        <v>300</v>
+      </c>
+      <c r="F29" s="1">
+        <v>500</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+      <c r="H29" s="3">
+        <v>2004</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L29" s="1">
+        <v>6</v>
+      </c>
+      <c r="M29" s="1">
+        <v>15</v>
+      </c>
+      <c r="N29" s="1">
+        <v>9</v>
+      </c>
+      <c r="O29" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C30" s="1">
+        <v>42005</v>
+      </c>
+      <c r="D30" s="1">
+        <v>6</v>
+      </c>
+      <c r="E30" s="1">
+        <v>100</v>
+      </c>
+      <c r="F30" s="1">
+        <v>25</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2</v>
+      </c>
+      <c r="H30" s="3">
+        <v>2005</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L30" s="1">
+        <v>6</v>
+      </c>
+      <c r="M30" s="1">
+        <v>15</v>
+      </c>
+      <c r="N30" s="1">
+        <v>9</v>
+      </c>
+      <c r="O30" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C31" s="1">
+        <v>42006</v>
+      </c>
+      <c r="D31" s="1">
+        <v>6</v>
+      </c>
+      <c r="E31" s="1">
+        <v>50</v>
+      </c>
+      <c r="F31" s="1">
+        <v>25</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
+      <c r="H31" s="3">
+        <v>2006</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L31" s="1">
+        <v>6</v>
+      </c>
+      <c r="M31" s="1">
+        <v>15</v>
+      </c>
+      <c r="N31" s="1">
+        <v>9</v>
+      </c>
+      <c r="O31" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C32" s="1">
+        <v>42007</v>
+      </c>
+      <c r="D32" s="1">
+        <v>6</v>
+      </c>
+      <c r="E32" s="1">
+        <v>300</v>
+      </c>
+      <c r="F32" s="1">
+        <v>500</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2</v>
+      </c>
+      <c r="H32" s="3">
+        <v>2007</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L32" s="1">
+        <v>6</v>
+      </c>
+      <c r="M32" s="1">
+        <v>15</v>
+      </c>
+      <c r="N32" s="1">
+        <v>9</v>
+      </c>
+      <c r="O32" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C33" s="1">
+        <v>42008</v>
+      </c>
+      <c r="D33" s="1">
+        <v>6</v>
+      </c>
+      <c r="E33" s="1">
+        <v>50</v>
+      </c>
+      <c r="F33" s="1">
+        <v>10</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2</v>
+      </c>
+      <c r="H33" s="3">
+        <v>2008</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L33" s="1">
+        <v>6</v>
+      </c>
+      <c r="M33" s="1">
+        <v>15</v>
+      </c>
+      <c r="N33" s="1">
+        <v>9</v>
+      </c>
+      <c r="O33" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C34" s="1">
+        <v>42009</v>
+      </c>
+      <c r="D34" s="1">
+        <v>6</v>
+      </c>
+      <c r="E34" s="1">
+        <v>300</v>
+      </c>
+      <c r="F34" s="1">
+        <v>500</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2</v>
+      </c>
+      <c r="H34" s="3">
+        <v>2009</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L34" s="1">
+        <v>6</v>
+      </c>
+      <c r="M34" s="1">
+        <v>15</v>
+      </c>
+      <c r="N34" s="1">
+        <v>9</v>
+      </c>
+      <c r="O34" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C35" s="1">
+        <v>42010</v>
+      </c>
+      <c r="D35" s="1">
+        <v>6</v>
+      </c>
+      <c r="E35" s="1">
+        <v>10</v>
+      </c>
+      <c r="F35" s="1">
+        <v>5</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2</v>
+      </c>
+      <c r="H35" s="3">
+        <v>2010</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L35" s="1">
+        <v>6</v>
+      </c>
+      <c r="M35" s="1">
+        <v>15</v>
+      </c>
+      <c r="N35" s="1">
+        <v>9</v>
+      </c>
+      <c r="O35" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C36" s="1">
+        <v>42011</v>
+      </c>
+      <c r="D36" s="1">
+        <v>6</v>
+      </c>
+      <c r="E36" s="1">
+        <v>10</v>
+      </c>
+      <c r="F36" s="1">
+        <v>5</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
+      <c r="H36" s="3">
+        <v>2011</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L36" s="1">
+        <v>6</v>
+      </c>
+      <c r="M36" s="1">
+        <v>15</v>
+      </c>
+      <c r="N36" s="1">
+        <v>9</v>
+      </c>
+      <c r="O36" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C37" s="1">
+        <v>42012</v>
+      </c>
+      <c r="D37" s="1">
+        <v>6</v>
+      </c>
+      <c r="E37" s="1">
+        <v>10</v>
+      </c>
+      <c r="F37" s="1">
+        <v>5</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
+      <c r="H37" s="3">
+        <v>2012</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="L37" s="1">
+        <v>4</v>
+      </c>
+      <c r="M37" s="1">
+        <v>10</v>
+      </c>
+      <c r="N37" s="1">
+        <v>9</v>
+      </c>
+      <c r="O37" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="H38" s="3"/>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="H39" s="3"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="H40" s="3"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="H41" s="3"/>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="H42" s="3"/>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C43" s="1">
+        <v>43001</v>
+      </c>
+      <c r="D43" s="1">
+        <v>6</v>
+      </c>
+      <c r="E43" s="1">
+        <v>300</v>
+      </c>
+      <c r="F43" s="1">
+        <v>500</v>
+      </c>
+      <c r="G43" s="1">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
+        <v>3001</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L43" s="1">
+        <v>6</v>
+      </c>
+      <c r="M43" s="1">
+        <v>15</v>
+      </c>
+      <c r="N43" s="1">
+        <v>9</v>
+      </c>
+      <c r="O43" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C44" s="1">
+        <v>43002</v>
+      </c>
+      <c r="D44" s="1">
+        <v>6</v>
+      </c>
+      <c r="E44" s="1">
+        <v>50</v>
+      </c>
+      <c r="F44" s="1">
+        <v>25</v>
+      </c>
+      <c r="G44" s="1">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3">
+        <v>3002</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L44" s="1">
+        <v>6</v>
+      </c>
+      <c r="M44" s="1">
+        <v>15</v>
+      </c>
+      <c r="N44" s="1">
+        <v>9</v>
+      </c>
+      <c r="O44" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C45" s="1">
+        <v>43003</v>
+      </c>
+      <c r="D45" s="1">
+        <v>6</v>
+      </c>
+      <c r="E45" s="1">
+        <v>300</v>
+      </c>
+      <c r="F45" s="1">
+        <v>500</v>
+      </c>
+      <c r="G45" s="1">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
+        <v>3003</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L45" s="1">
+        <v>6</v>
+      </c>
+      <c r="M45" s="1">
+        <v>15</v>
+      </c>
+      <c r="N45" s="1">
+        <v>9</v>
+      </c>
+      <c r="O45" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C46" s="1">
+        <v>43004</v>
+      </c>
+      <c r="D46" s="1">
+        <v>6</v>
+      </c>
+      <c r="E46" s="1">
+        <v>300</v>
+      </c>
+      <c r="F46" s="1">
+        <v>500</v>
+      </c>
+      <c r="G46" s="1">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3">
+        <v>3004</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L46" s="1">
+        <v>6</v>
+      </c>
+      <c r="M46" s="1">
+        <v>15</v>
+      </c>
+      <c r="N46" s="1">
+        <v>9</v>
+      </c>
+      <c r="O46" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C47" s="1">
+        <v>43005</v>
+      </c>
+      <c r="D47" s="1">
+        <v>6</v>
+      </c>
+      <c r="E47" s="1">
+        <v>100</v>
+      </c>
+      <c r="F47" s="1">
+        <v>25</v>
+      </c>
+      <c r="G47" s="1">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
+        <v>3005</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L47" s="1">
+        <v>6</v>
+      </c>
+      <c r="M47" s="1">
+        <v>15</v>
+      </c>
+      <c r="N47" s="1">
+        <v>9</v>
+      </c>
+      <c r="O47" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C48" s="1">
+        <v>43006</v>
+      </c>
+      <c r="D48" s="1">
+        <v>6</v>
+      </c>
+      <c r="E48" s="1">
+        <v>50</v>
+      </c>
+      <c r="F48" s="1">
+        <v>25</v>
+      </c>
+      <c r="G48" s="1">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3">
+        <v>3006</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L48" s="1">
+        <v>6</v>
+      </c>
+      <c r="M48" s="1">
+        <v>15</v>
+      </c>
+      <c r="N48" s="1">
+        <v>9</v>
+      </c>
+      <c r="O48" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C49" s="1">
+        <v>43007</v>
+      </c>
+      <c r="D49" s="1">
+        <v>6</v>
+      </c>
+      <c r="E49" s="1">
+        <v>300</v>
+      </c>
+      <c r="F49" s="1">
+        <v>500</v>
+      </c>
+      <c r="G49" s="1">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3">
+        <v>3007</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L49" s="1">
+        <v>6</v>
+      </c>
+      <c r="M49" s="1">
+        <v>15</v>
+      </c>
+      <c r="N49" s="1">
+        <v>9</v>
+      </c>
+      <c r="O49" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C50" s="1">
+        <v>43008</v>
+      </c>
+      <c r="D50" s="1">
+        <v>6</v>
+      </c>
+      <c r="E50" s="1">
+        <v>50</v>
+      </c>
+      <c r="F50" s="1">
+        <v>10</v>
+      </c>
+      <c r="G50" s="1">
+        <v>3</v>
+      </c>
+      <c r="H50" s="3">
+        <v>3008</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L50" s="1">
+        <v>6</v>
+      </c>
+      <c r="M50" s="1">
+        <v>15</v>
+      </c>
+      <c r="N50" s="1">
+        <v>9</v>
+      </c>
+      <c r="O50" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C51" s="1">
+        <v>43009</v>
+      </c>
+      <c r="D51" s="1">
+        <v>6</v>
+      </c>
+      <c r="E51" s="1">
+        <v>300</v>
+      </c>
+      <c r="F51" s="1">
+        <v>500</v>
+      </c>
+      <c r="G51" s="1">
+        <v>3</v>
+      </c>
+      <c r="H51" s="3">
+        <v>3009</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L51" s="1">
+        <v>6</v>
+      </c>
+      <c r="M51" s="1">
+        <v>15</v>
+      </c>
+      <c r="N51" s="1">
+        <v>9</v>
+      </c>
+      <c r="O51" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C52" s="1">
+        <v>43010</v>
+      </c>
+      <c r="D52" s="1">
+        <v>6</v>
+      </c>
+      <c r="E52" s="1">
+        <v>10</v>
+      </c>
+      <c r="F52" s="1">
+        <v>5</v>
+      </c>
+      <c r="G52" s="1">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
+        <v>3010</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L52" s="1">
+        <v>6</v>
+      </c>
+      <c r="M52" s="1">
+        <v>15</v>
+      </c>
+      <c r="N52" s="1">
+        <v>9</v>
+      </c>
+      <c r="O52" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C53" s="1">
+        <v>43011</v>
+      </c>
+      <c r="D53" s="1">
+        <v>6</v>
+      </c>
+      <c r="E53" s="1">
+        <v>10</v>
+      </c>
+      <c r="F53" s="1">
+        <v>5</v>
+      </c>
+      <c r="G53" s="1">
+        <v>3</v>
+      </c>
+      <c r="H53" s="3">
+        <v>3011</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L53" s="1">
+        <v>6</v>
+      </c>
+      <c r="M53" s="1">
+        <v>15</v>
+      </c>
+      <c r="N53" s="1">
+        <v>9</v>
+      </c>
+      <c r="O53" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C54" s="1">
+        <v>43012</v>
+      </c>
+      <c r="D54" s="1">
+        <v>6</v>
+      </c>
+      <c r="E54" s="1">
+        <v>10</v>
+      </c>
+      <c r="F54" s="1">
+        <v>5</v>
+      </c>
+      <c r="G54" s="1">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3">
+        <v>3012</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="L54" s="1">
+        <v>4</v>
+      </c>
+      <c r="M54" s="1">
+        <v>10</v>
+      </c>
+      <c r="N54" s="1">
+        <v>9</v>
+      </c>
+      <c r="O54" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" customHeight="1"/>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="H56" s="3"/>
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="H57" s="3"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="3"/>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="H58" s="3"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="S3:S5 C3:L5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -2022,12 +2022,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -16707,10 +16707,10 @@
         <v>15</v>
       </c>
       <c r="N6" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:21">
@@ -16748,10 +16748,10 @@
         <v>15</v>
       </c>
       <c r="N7" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O7" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:21">
@@ -16789,10 +16789,10 @@
         <v>15</v>
       </c>
       <c r="N8" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O8" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:21">
@@ -16830,10 +16830,10 @@
         <v>15</v>
       </c>
       <c r="N9" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O9" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:21">
@@ -16871,10 +16871,10 @@
         <v>15</v>
       </c>
       <c r="N10" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O10" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:21">
@@ -16912,10 +16912,10 @@
         <v>15</v>
       </c>
       <c r="N11" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O11" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:21">
@@ -16953,10 +16953,10 @@
         <v>15</v>
       </c>
       <c r="N12" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O12" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:21">
@@ -16994,10 +16994,10 @@
         <v>15</v>
       </c>
       <c r="N13" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O13" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:21">
@@ -17035,10 +17035,10 @@
         <v>15</v>
       </c>
       <c r="N14" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O14" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:21">
@@ -17076,10 +17076,10 @@
         <v>15</v>
       </c>
       <c r="N15" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O15" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:21">
@@ -17117,10 +17117,10 @@
         <v>15</v>
       </c>
       <c r="N16" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O16" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" s="4"/>
     </row>
@@ -17159,10 +17159,10 @@
         <v>10</v>
       </c>
       <c r="N17" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O17" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" s="4"/>
     </row>
@@ -17273,10 +17273,10 @@
         <v>15</v>
       </c>
       <c r="N26" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O26" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:20">
@@ -17314,10 +17314,10 @@
         <v>15</v>
       </c>
       <c r="N27" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O27" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:20">
@@ -17355,10 +17355,10 @@
         <v>15</v>
       </c>
       <c r="N28" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O28" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:20">
@@ -17396,10 +17396,10 @@
         <v>15</v>
       </c>
       <c r="N29" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O29" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:20">
@@ -17437,10 +17437,10 @@
         <v>15</v>
       </c>
       <c r="N30" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O30" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:20">
@@ -17478,10 +17478,10 @@
         <v>15</v>
       </c>
       <c r="N31" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O31" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:20">
@@ -17519,10 +17519,10 @@
         <v>15</v>
       </c>
       <c r="N32" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O32" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -17560,10 +17560,10 @@
         <v>15</v>
       </c>
       <c r="N33" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O33" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -17601,10 +17601,10 @@
         <v>15</v>
       </c>
       <c r="N34" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O34" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -17642,10 +17642,10 @@
         <v>15</v>
       </c>
       <c r="N35" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O35" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -17683,10 +17683,10 @@
         <v>15</v>
       </c>
       <c r="N36" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O36" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -17724,10 +17724,10 @@
         <v>10</v>
       </c>
       <c r="N37" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O37" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -17786,10 +17786,10 @@
         <v>15</v>
       </c>
       <c r="N43" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O43" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -17827,10 +17827,10 @@
         <v>15</v>
       </c>
       <c r="N44" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O44" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -17868,10 +17868,10 @@
         <v>15</v>
       </c>
       <c r="N45" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O45" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -17909,10 +17909,10 @@
         <v>15</v>
       </c>
       <c r="N46" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O46" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -17950,10 +17950,10 @@
         <v>15</v>
       </c>
       <c r="N47" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O47" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -17991,10 +17991,10 @@
         <v>15</v>
       </c>
       <c r="N48" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O48" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -18032,10 +18032,10 @@
         <v>15</v>
       </c>
       <c r="N49" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O49" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -18073,10 +18073,10 @@
         <v>15</v>
       </c>
       <c r="N50" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O50" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -18114,10 +18114,10 @@
         <v>15</v>
       </c>
       <c r="N51" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O51" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -18155,10 +18155,10 @@
         <v>15</v>
       </c>
       <c r="N52" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O52" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -18196,10 +18196,10 @@
         <v>15</v>
       </c>
       <c r="N53" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O53" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -18237,10 +18237,10 @@
         <v>10</v>
       </c>
       <c r="N54" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O54" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1"/>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -554,7 +554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="438">
   <si>
     <t>_ID</t>
   </si>
@@ -1768,6 +1768,18 @@
     <t>战士之魂·专家</t>
   </si>
   <si>
+    <t>流光剑法·天目Ⅱ</t>
+  </si>
+  <si>
+    <t>此技能额外增加25%命中</t>
+  </si>
+  <si>
+    <t>裂地斩·天目Ⅱ</t>
+  </si>
+  <si>
+    <t>剑二十三·天目Ⅱ</t>
+  </si>
+  <si>
     <t>火球术·专家</t>
   </si>
   <si>
@@ -1804,6 +1816,15 @@
     <t>魔尊附体·专家</t>
   </si>
   <si>
+    <t>落雷术·天目Ⅱ</t>
+  </si>
+  <si>
+    <t>魔尊附体·破限Ⅱ</t>
+  </si>
+  <si>
+    <t>增加40层叠加上限</t>
+  </si>
+  <si>
     <t>疗伤术·专家</t>
   </si>
   <si>
@@ -1838,6 +1859,15 @@
   </si>
   <si>
     <t>召唤白虎·专家</t>
+  </si>
+  <si>
+    <t>驱魔符·天目Ⅱ</t>
+  </si>
+  <si>
+    <t>召唤白虎·天目Ⅱ</t>
+  </si>
+  <si>
+    <t>白虎额外增加25%命中</t>
   </si>
 </sst>
 </file>
@@ -2022,12 +2052,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -17178,30 +17208,137 @@
       <c r="T18" s="4"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:20">
-      <c r="H19" s="3"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="T19" s="4"/>
+      <c r="C19" s="1">
+        <v>41102</v>
+      </c>
+      <c r="D19" s="1">
+        <v>6</v>
+      </c>
+      <c r="E19" s="1">
+        <v>10</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1002</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="L19" s="1">
+        <v>4</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>10</v>
+      </c>
+      <c r="O19" s="1">
+        <v>10</v>
+      </c>
+      <c r="P19" s="1">
+        <v>25</v>
+      </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:20">
-      <c r="H20" s="3"/>
-      <c r="J20" s="3"/>
+      <c r="C20" s="1">
+        <v>41110</v>
+      </c>
+      <c r="D20" s="1">
+        <v>6</v>
+      </c>
+      <c r="E20" s="1">
+        <v>10</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1010</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="L20" s="1">
+        <v>4</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>10</v>
+      </c>
+      <c r="O20" s="1">
+        <v>10</v>
+      </c>
+      <c r="P20" s="1">
+        <v>25</v>
+      </c>
       <c r="T20" s="4"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:20">
-      <c r="H21" s="3"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
+      <c r="C21" s="1">
+        <v>41112</v>
+      </c>
+      <c r="D21" s="1">
+        <v>6</v>
+      </c>
+      <c r="E21" s="1">
+        <v>10</v>
+      </c>
+      <c r="F21" s="1">
+        <v>5</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1012</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="L21" s="1">
+        <v>4</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>10</v>
+      </c>
+      <c r="O21" s="1">
+        <v>10</v>
+      </c>
+      <c r="P21" s="1">
+        <v>25</v>
+      </c>
       <c r="T21" s="4"/>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:20">
@@ -17261,7 +17398,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>341</v>
@@ -17302,7 +17439,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>341</v>
@@ -17343,7 +17480,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>341</v>
@@ -17384,7 +17521,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>341</v>
@@ -17425,7 +17562,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>341</v>
@@ -17466,7 +17603,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>341</v>
@@ -17507,7 +17644,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>341</v>
@@ -17525,7 +17662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C33" s="1">
         <v>42008</v>
       </c>
@@ -17548,7 +17685,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>341</v>
@@ -17566,7 +17703,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C34" s="1">
         <v>42009</v>
       </c>
@@ -17589,7 +17726,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>341</v>
@@ -17607,7 +17744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C35" s="1">
         <v>42010</v>
       </c>
@@ -17630,7 +17767,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>341</v>
@@ -17648,7 +17785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C36" s="1">
         <v>42011</v>
       </c>
@@ -17671,7 +17808,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>341</v>
@@ -17689,7 +17826,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C37" s="1">
         <v>42012</v>
       </c>
@@ -17712,7 +17849,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>283</v>
@@ -17730,28 +17867,107 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="H38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="H39" s="3"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="3"/>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="H40" s="3"/>
-      <c r="J40" s="3"/>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C39" s="1">
+        <v>42102</v>
+      </c>
+      <c r="D39" s="1">
+        <v>6</v>
+      </c>
+      <c r="E39" s="1">
+        <v>10</v>
+      </c>
+      <c r="F39" s="1">
+        <v>5</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2</v>
+      </c>
+      <c r="H39" s="3">
+        <v>2002</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="L39" s="1">
+        <v>4</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>10</v>
+      </c>
+      <c r="O39" s="1">
+        <v>10</v>
+      </c>
+      <c r="P39" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C40" s="1">
+        <v>42112</v>
+      </c>
+      <c r="D40" s="1">
+        <v>6</v>
+      </c>
+      <c r="E40" s="1">
+        <v>10</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2</v>
+      </c>
+      <c r="H40" s="3">
+        <v>2012</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="L40" s="1">
+        <v>4</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1">
+        <v>10</v>
+      </c>
+      <c r="O40" s="1">
+        <v>10</v>
+      </c>
+      <c r="R40" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="H41" s="3"/>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="H42" s="3"/>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C43" s="1">
         <v>43001</v>
       </c>
@@ -17774,7 +17990,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>341</v>
@@ -17792,7 +18008,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C44" s="1">
         <v>43002</v>
       </c>
@@ -17815,7 +18031,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>341</v>
@@ -17833,7 +18049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C45" s="1">
         <v>43003</v>
       </c>
@@ -17856,7 +18072,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>341</v>
@@ -17874,7 +18090,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C46" s="1">
         <v>43004</v>
       </c>
@@ -17897,7 +18113,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>341</v>
@@ -17915,7 +18131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C47" s="1">
         <v>43005</v>
       </c>
@@ -17938,7 +18154,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>341</v>
@@ -17956,7 +18172,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C48" s="1">
         <v>43006</v>
       </c>
@@ -17979,7 +18195,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>341</v>
@@ -17997,7 +18213,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C49" s="1">
         <v>43007</v>
       </c>
@@ -18020,7 +18236,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>341</v>
@@ -18038,7 +18254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C50" s="1">
         <v>43008</v>
       </c>
@@ -18061,7 +18277,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>341</v>
@@ -18079,7 +18295,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C51" s="1">
         <v>43009</v>
       </c>
@@ -18102,7 +18318,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>341</v>
@@ -18120,7 +18336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C52" s="1">
         <v>43010</v>
       </c>
@@ -18143,7 +18359,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>341</v>
@@ -18161,7 +18377,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C53" s="1">
         <v>43011</v>
       </c>
@@ -18184,7 +18400,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>341</v>
@@ -18202,7 +18418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C54" s="1">
         <v>43012</v>
       </c>
@@ -18225,7 +18441,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>283</v>
@@ -18244,16 +18460,95 @@
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1"/>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="H56" s="3"/>
-      <c r="J56" s="3"/>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="H57" s="3"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="3"/>
-    </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C56" s="1">
+        <v>43102</v>
+      </c>
+      <c r="D56" s="1">
+        <v>6</v>
+      </c>
+      <c r="E56" s="1">
+        <v>10</v>
+      </c>
+      <c r="F56" s="1">
+        <v>5</v>
+      </c>
+      <c r="G56" s="1">
+        <v>3</v>
+      </c>
+      <c r="H56" s="3">
+        <v>3002</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="L56" s="1">
+        <v>4</v>
+      </c>
+      <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>10</v>
+      </c>
+      <c r="O56" s="1">
+        <v>10</v>
+      </c>
+      <c r="P56" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C57" s="1">
+        <v>43112</v>
+      </c>
+      <c r="D57" s="1">
+        <v>6</v>
+      </c>
+      <c r="E57" s="1">
+        <v>10</v>
+      </c>
+      <c r="F57" s="1">
+        <v>5</v>
+      </c>
+      <c r="G57" s="1">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3">
+        <v>3012</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="L57" s="1">
+        <v>4</v>
+      </c>
+      <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>10</v>
+      </c>
+      <c r="O57" s="1">
+        <v>10</v>
+      </c>
+      <c r="P57" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="H58" s="3"/>
       <c r="I58" s="1"/>
       <c r="J58" s="3"/>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -554,7 +554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="440">
   <si>
     <t>_ID</t>
   </si>
@@ -1738,6 +1738,9 @@
     <t>基础剑术·专家</t>
   </si>
   <si>
+    <t>提高此技能系数25%系数增幅</t>
+  </si>
+  <si>
     <t>流光剑法·专家</t>
   </si>
   <si>
@@ -1766,6 +1769,9 @@
   </si>
   <si>
     <t>战士之魂·专家</t>
+  </si>
+  <si>
+    <t>剑二十三·专家</t>
   </si>
   <si>
     <t>流光剑法·天目Ⅱ</t>
@@ -2052,12 +2058,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -16728,13 +16734,13 @@
         <v>393</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L6" s="1">
         <v>6</v>
       </c>
       <c r="M6" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N6" s="1">
         <v>10</v>
@@ -16751,7 +16757,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F7" s="1">
         <v>25</v>
@@ -16766,16 +16772,16 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>341</v>
       </c>
       <c r="L7" s="1">
         <v>6</v>
       </c>
       <c r="M7" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N7" s="1">
         <v>10</v>
@@ -16807,16 +16813,16 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L8" s="1">
         <v>6</v>
       </c>
       <c r="M8" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N8" s="1">
         <v>10</v>
@@ -16848,16 +16854,16 @@
         <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L9" s="1">
         <v>6</v>
       </c>
       <c r="M9" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N9" s="1">
         <v>10</v>
@@ -16874,7 +16880,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F10" s="1">
         <v>25</v>
@@ -16889,16 +16895,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L10" s="1">
         <v>6</v>
       </c>
       <c r="M10" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N10" s="1">
         <v>10</v>
@@ -16915,7 +16921,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -16930,16 +16936,16 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L11" s="1">
         <v>6</v>
       </c>
       <c r="M11" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N11" s="1">
         <v>10</v>
@@ -16971,16 +16977,16 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L12" s="1">
         <v>6</v>
       </c>
       <c r="M12" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N12" s="1">
         <v>10</v>
@@ -17012,16 +17018,16 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L13" s="1">
         <v>6</v>
       </c>
       <c r="M13" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N13" s="1">
         <v>10</v>
@@ -17053,16 +17059,16 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L14" s="1">
         <v>6</v>
       </c>
       <c r="M14" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N14" s="1">
         <v>10</v>
@@ -17094,16 +17100,16 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L15" s="1">
         <v>6</v>
       </c>
       <c r="M15" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N15" s="1">
         <v>10</v>
@@ -17135,16 +17141,16 @@
         <v>0</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L16" s="1">
         <v>6</v>
       </c>
       <c r="M16" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N16" s="1">
         <v>10</v>
@@ -17177,16 +17183,16 @@
         <v>0</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>352</v>
+        <v>405</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>283</v>
+        <v>341</v>
       </c>
       <c r="L17" s="1">
         <v>4</v>
       </c>
       <c r="M17" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N17" s="1">
         <v>10</v>
@@ -17230,10 +17236,10 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L19" s="1">
         <v>4</v>
@@ -17274,10 +17280,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L20" s="1">
         <v>4</v>
@@ -17319,10 +17325,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="L21" s="1">
         <v>4</v>
@@ -17398,16 +17404,16 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L26" s="1">
         <v>6</v>
       </c>
       <c r="M26" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N26" s="1">
         <v>10</v>
@@ -17424,7 +17430,7 @@
         <v>6</v>
       </c>
       <c r="E27" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F27" s="1">
         <v>25</v>
@@ -17439,16 +17445,16 @@
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L27" s="1">
         <v>6</v>
       </c>
       <c r="M27" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N27" s="1">
         <v>10</v>
@@ -17480,16 +17486,16 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L28" s="1">
         <v>6</v>
       </c>
       <c r="M28" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N28" s="1">
         <v>10</v>
@@ -17521,16 +17527,16 @@
         <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L29" s="1">
         <v>6</v>
       </c>
       <c r="M29" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N29" s="1">
         <v>10</v>
@@ -17547,7 +17553,7 @@
         <v>6</v>
       </c>
       <c r="E30" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F30" s="1">
         <v>25</v>
@@ -17562,16 +17568,16 @@
         <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L30" s="1">
         <v>6</v>
       </c>
       <c r="M30" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N30" s="1">
         <v>10</v>
@@ -17588,7 +17594,7 @@
         <v>6</v>
       </c>
       <c r="E31" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F31" s="1">
         <v>25</v>
@@ -17603,16 +17609,16 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L31" s="1">
         <v>6</v>
       </c>
       <c r="M31" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N31" s="1">
         <v>10</v>
@@ -17644,16 +17650,16 @@
         <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N32" s="1">
         <v>10</v>
@@ -17685,16 +17691,16 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N33" s="1">
         <v>10</v>
@@ -17726,16 +17732,16 @@
         <v>0</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N34" s="1">
         <v>10</v>
@@ -17767,16 +17773,16 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L35" s="1">
         <v>6</v>
       </c>
       <c r="M35" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N35" s="1">
         <v>10</v>
@@ -17808,16 +17814,16 @@
         <v>0</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
       </c>
       <c r="M36" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N36" s="1">
         <v>10</v>
@@ -17849,16 +17855,16 @@
         <v>0</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>283</v>
+        <v>341</v>
       </c>
       <c r="L37" s="1">
         <v>4</v>
       </c>
       <c r="M37" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N37" s="1">
         <v>10</v>
@@ -17894,10 +17900,10 @@
         <v>0</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L39" s="1">
         <v>4</v>
@@ -17938,10 +17944,10 @@
         <v>0</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L40" s="1">
         <v>4</v>
@@ -17990,16 +17996,16 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L43" s="1">
         <v>6</v>
       </c>
       <c r="M43" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N43" s="1">
         <v>10</v>
@@ -18016,7 +18022,7 @@
         <v>6</v>
       </c>
       <c r="E44" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F44" s="1">
         <v>25</v>
@@ -18031,16 +18037,16 @@
         <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
       </c>
       <c r="M44" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N44" s="1">
         <v>10</v>
@@ -18072,16 +18078,16 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L45" s="1">
         <v>6</v>
       </c>
       <c r="M45" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N45" s="1">
         <v>10</v>
@@ -18113,16 +18119,16 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L46" s="1">
         <v>6</v>
       </c>
       <c r="M46" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N46" s="1">
         <v>10</v>
@@ -18139,7 +18145,7 @@
         <v>6</v>
       </c>
       <c r="E47" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F47" s="1">
         <v>25</v>
@@ -18154,16 +18160,16 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L47" s="1">
         <v>6</v>
       </c>
       <c r="M47" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N47" s="1">
         <v>10</v>
@@ -18180,7 +18186,7 @@
         <v>6</v>
       </c>
       <c r="E48" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F48" s="1">
         <v>25</v>
@@ -18195,16 +18201,16 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L48" s="1">
         <v>6</v>
       </c>
       <c r="M48" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N48" s="1">
         <v>10</v>
@@ -18236,16 +18242,16 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L49" s="1">
         <v>6</v>
       </c>
       <c r="M49" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N49" s="1">
         <v>10</v>
@@ -18277,16 +18283,16 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L50" s="1">
         <v>6</v>
       </c>
       <c r="M50" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N50" s="1">
         <v>10</v>
@@ -18318,16 +18324,16 @@
         <v>0</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L51" s="1">
         <v>6</v>
       </c>
       <c r="M51" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N51" s="1">
         <v>10</v>
@@ -18359,16 +18365,16 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L52" s="1">
         <v>6</v>
       </c>
       <c r="M52" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N52" s="1">
         <v>10</v>
@@ -18400,16 +18406,16 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L53" s="1">
         <v>6</v>
       </c>
       <c r="M53" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N53" s="1">
         <v>10</v>
@@ -18441,16 +18447,16 @@
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>283</v>
+        <v>341</v>
       </c>
       <c r="L54" s="1">
         <v>4</v>
       </c>
       <c r="M54" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N54" s="1">
         <v>10</v>
@@ -18483,10 +18489,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L56" s="1">
         <v>4</v>
@@ -18527,10 +18533,10 @@
         <v>0</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L57" s="1">
         <v>4</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -2058,12 +2058,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -16757,7 +16757,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F7" s="1">
         <v>25</v>
@@ -16921,7 +16921,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -17085,7 +17085,7 @@
         <v>6</v>
       </c>
       <c r="E15" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1">
         <v>5</v>
@@ -17168,7 +17168,7 @@
         <v>6</v>
       </c>
       <c r="E17" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F17" s="1">
         <v>5</v>
@@ -17221,7 +17221,7 @@
         <v>6</v>
       </c>
       <c r="E19" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F19" s="1">
         <v>5</v>
@@ -17310,7 +17310,7 @@
         <v>6</v>
       </c>
       <c r="E21" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F21" s="1">
         <v>5</v>
@@ -17430,7 +17430,7 @@
         <v>6</v>
       </c>
       <c r="E27" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F27" s="1">
         <v>25</v>
@@ -17594,7 +17594,7 @@
         <v>6</v>
       </c>
       <c r="E31" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F31" s="1">
         <v>25</v>
@@ -17758,7 +17758,7 @@
         <v>6</v>
       </c>
       <c r="E35" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1">
         <v>5</v>
@@ -17840,7 +17840,7 @@
         <v>6</v>
       </c>
       <c r="E37" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F37" s="1">
         <v>5</v>
@@ -17885,7 +17885,7 @@
         <v>6</v>
       </c>
       <c r="E39" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F39" s="1">
         <v>5</v>
@@ -17929,7 +17929,7 @@
         <v>6</v>
       </c>
       <c r="E40" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F40" s="1">
         <v>5</v>
@@ -18022,7 +18022,7 @@
         <v>6</v>
       </c>
       <c r="E44" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F44" s="1">
         <v>25</v>
@@ -18186,7 +18186,7 @@
         <v>6</v>
       </c>
       <c r="E48" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F48" s="1">
         <v>25</v>
@@ -18350,7 +18350,7 @@
         <v>6</v>
       </c>
       <c r="E52" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F52" s="1">
         <v>5</v>
@@ -18432,7 +18432,7 @@
         <v>6</v>
       </c>
       <c r="E54" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F54" s="1">
         <v>5</v>
@@ -18474,7 +18474,7 @@
         <v>6</v>
       </c>
       <c r="E56" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F56" s="1">
         <v>5</v>
@@ -18518,7 +18518,7 @@
         <v>6</v>
       </c>
       <c r="E57" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F57" s="1">
         <v>5</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -2058,12 +2058,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -13923,7 +13923,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -14047,7 +14047,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -14170,7 +14170,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -14211,7 +14211,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -14252,7 +14252,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -14293,7 +14293,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -14954,7 +14954,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F16" s="1">
         <v>5</v>
@@ -15000,7 +15000,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F17" s="1">
         <v>5</v>
@@ -15042,7 +15042,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F18" s="1">
         <v>5</v>
@@ -15086,7 +15086,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F19" s="1">
         <v>5</v>
@@ -15136,7 +15136,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F21" s="1">
         <v>5</v>
@@ -15184,7 +15184,7 @@
         <v>5</v>
       </c>
       <c r="E22" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F22" s="1">
         <v>5</v>
@@ -15232,7 +15232,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F23" s="1">
         <v>5</v>
@@ -15697,7 +15697,7 @@
         <v>5</v>
       </c>
       <c r="E36" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F36" s="1">
         <v>5</v>
@@ -15738,7 +15738,7 @@
         <v>5</v>
       </c>
       <c r="E37" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F37" s="1">
         <v>5</v>
@@ -15783,7 +15783,7 @@
         <v>5</v>
       </c>
       <c r="E39" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F39" s="1">
         <v>5</v>
@@ -15827,7 +15827,7 @@
         <v>5</v>
       </c>
       <c r="E40" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F40" s="1">
         <v>5</v>
@@ -16288,7 +16288,7 @@
         <v>5</v>
       </c>
       <c r="E53" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F53" s="1">
         <v>5</v>
@@ -16329,7 +16329,7 @@
         <v>5</v>
       </c>
       <c r="E54" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F54" s="1">
         <v>5</v>
@@ -16371,7 +16371,7 @@
         <v>5</v>
       </c>
       <c r="E56" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F56" s="1">
         <v>5</v>
@@ -16415,7 +16415,7 @@
         <v>5</v>
       </c>
       <c r="E57" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F57" s="1">
         <v>5</v>
@@ -16459,7 +16459,7 @@
         <v>5</v>
       </c>
       <c r="E58" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1">
         <v>5</v>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -2058,12 +2058,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -16880,7 +16880,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F10" s="1">
         <v>25</v>
@@ -17003,7 +17003,7 @@
         <v>6</v>
       </c>
       <c r="E13" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F13" s="1">
         <v>10</v>
@@ -17085,7 +17085,7 @@
         <v>6</v>
       </c>
       <c r="E15" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F15" s="1">
         <v>5</v>
@@ -17126,7 +17126,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F16" s="1">
         <v>5</v>
@@ -17168,7 +17168,7 @@
         <v>6</v>
       </c>
       <c r="E17" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F17" s="1">
         <v>5</v>
@@ -17265,7 +17265,7 @@
         <v>6</v>
       </c>
       <c r="E20" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F20" s="1">
         <v>5</v>
@@ -17310,7 +17310,7 @@
         <v>6</v>
       </c>
       <c r="E21" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F21" s="1">
         <v>5</v>
@@ -17553,7 +17553,7 @@
         <v>6</v>
       </c>
       <c r="E30" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F30" s="1">
         <v>25</v>
@@ -17676,7 +17676,7 @@
         <v>6</v>
       </c>
       <c r="E33" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F33" s="1">
         <v>10</v>
@@ -17758,7 +17758,7 @@
         <v>6</v>
       </c>
       <c r="E35" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F35" s="1">
         <v>5</v>
@@ -17799,7 +17799,7 @@
         <v>6</v>
       </c>
       <c r="E36" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F36" s="1">
         <v>5</v>
@@ -17840,7 +17840,7 @@
         <v>6</v>
       </c>
       <c r="E37" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F37" s="1">
         <v>5</v>
@@ -17929,7 +17929,7 @@
         <v>6</v>
       </c>
       <c r="E40" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F40" s="1">
         <v>5</v>
@@ -18145,7 +18145,7 @@
         <v>6</v>
       </c>
       <c r="E47" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F47" s="1">
         <v>25</v>
@@ -18350,7 +18350,7 @@
         <v>6</v>
       </c>
       <c r="E52" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F52" s="1">
         <v>5</v>
@@ -18391,7 +18391,7 @@
         <v>6</v>
       </c>
       <c r="E53" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F53" s="1">
         <v>5</v>
@@ -18432,7 +18432,7 @@
         <v>6</v>
       </c>
       <c r="E54" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F54" s="1">
         <v>5</v>
@@ -18518,7 +18518,7 @@
         <v>6</v>
       </c>
       <c r="E57" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F57" s="1">
         <v>5</v>
